--- a/obligaciones/inputs/SEGUMIENTO INSTALACIONES Y CAMBIO DE MEDIDORES.xlsx
+++ b/obligaciones/inputs/SEGUMIENTO INSTALACIONES Y CAMBIO DE MEDIDORES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilde\PycharmProjects\jass_system\obligaciones\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF55FF2-85C2-46A1-96CD-0BF1914D5F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080E01AF-DEFE-418C-902F-A3CC705CB2ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28230" yWindow="570" windowWidth="14610" windowHeight="15480" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NUEVAS INSTALACIONES" sheetId="1" r:id="rId1"/>
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="167">
   <si>
     <t>NOMBRES</t>
   </si>
@@ -584,6 +584,9 @@
   </si>
   <si>
     <t>RAMON REQUEZ MENDOZA</t>
+  </si>
+  <si>
+    <t>MARIANELA RIVERA VITARTE</t>
   </si>
 </sst>
 </file>
@@ -597,7 +600,7 @@
     <numFmt numFmtId="167" formatCode="yyyy\-mm"/>
     <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1168,7 +1171,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AN30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="6.81640625" customWidth="1"/>
@@ -1188,7 +1191,7 @@
     <col min="40" max="40" width="26.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="14.5" customHeight="1">
+    <row r="1" spans="1:40" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1307,7 +1310,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:40" ht="14.5" hidden="1" customHeight="1">
+    <row r="2" spans="1:40" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
@@ -1366,7 +1369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:40" ht="14.5" hidden="1" customHeight="1">
+    <row r="3" spans="1:40" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>11</v>
       </c>
@@ -1420,7 +1423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:40" ht="14.5" hidden="1" customHeight="1">
+    <row r="4" spans="1:40" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="14" t="s">
         <v>12</v>
       </c>
@@ -1474,7 +1477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:40" ht="14.5" customHeight="1">
+    <row r="5" spans="1:40" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
         <v>14</v>
       </c>
@@ -1548,7 +1551,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="6" spans="1:40" ht="14.5" hidden="1" customHeight="1">
+    <row r="6" spans="1:40" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="14" t="s">
         <v>16</v>
       </c>
@@ -1613,7 +1616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:40" ht="14.5" hidden="1" customHeight="1">
+    <row r="7" spans="1:40" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
         <v>18</v>
       </c>
@@ -1670,7 +1673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:40" ht="14.5" customHeight="1">
+    <row r="8" spans="1:40" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>19</v>
       </c>
@@ -1733,7 +1736,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="9" spans="1:40" ht="14.5" hidden="1" customHeight="1">
+    <row r="9" spans="1:40" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>20</v>
       </c>
@@ -1787,7 +1790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:40" ht="14.5" hidden="1" customHeight="1">
+    <row r="10" spans="1:40" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>22</v>
       </c>
@@ -1847,7 +1850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:40" ht="14.5" hidden="1" customHeight="1">
+    <row r="11" spans="1:40" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
         <v>24</v>
       </c>
@@ -1901,7 +1904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:40" ht="14.5" hidden="1" customHeight="1">
+    <row r="12" spans="1:40" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
         <v>26</v>
       </c>
@@ -1960,7 +1963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:40" ht="14.5" hidden="1" customHeight="1">
+    <row r="13" spans="1:40" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
         <v>28</v>
       </c>
@@ -2021,7 +2024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:40" ht="14.5" hidden="1" customHeight="1">
+    <row r="14" spans="1:40" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="14" t="s">
         <v>30</v>
       </c>
@@ -2079,7 +2082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:40" ht="14.5" hidden="1" customHeight="1">
+    <row r="15" spans="1:40" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
         <v>32</v>
       </c>
@@ -2137,7 +2140,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:40" ht="14.5" hidden="1" customHeight="1">
+    <row r="16" spans="1:40" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
         <v>34</v>
       </c>
@@ -2202,7 +2205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:39" ht="14.5" hidden="1" customHeight="1">
+    <row r="17" spans="1:39" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="15" t="s">
         <v>35</v>
       </c>
@@ -2270,7 +2273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:39" ht="14.5" hidden="1" customHeight="1">
+    <row r="18" spans="1:39" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
         <v>37</v>
       </c>
@@ -2330,7 +2333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:39" ht="14.5" hidden="1" customHeight="1">
+    <row r="19" spans="1:39" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>39</v>
       </c>
@@ -2389,7 +2392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:39" ht="14.5" hidden="1" customHeight="1">
+    <row r="20" spans="1:39" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
         <v>40</v>
       </c>
@@ -2468,7 +2471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:39" ht="14.5" customHeight="1">
+    <row r="21" spans="1:39" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="14" t="s">
         <v>42</v>
       </c>
@@ -2525,7 +2528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:39" ht="14.5" customHeight="1">
+    <row r="22" spans="1:39" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="58" t="s">
         <v>44</v>
       </c>
@@ -2587,7 +2590,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:39" ht="14.5" customHeight="1">
+    <row r="23" spans="1:39" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
@@ -2631,7 +2634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:39" ht="14.5" customHeight="1">
+    <row r="24" spans="1:39" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
@@ -2675,7 +2678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:39" ht="14.5" customHeight="1">
+    <row r="25" spans="1:39" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
@@ -2719,7 +2722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:39" ht="14.5" customHeight="1">
+    <row r="26" spans="1:39" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
@@ -2763,7 +2766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:39" ht="14.5" customHeight="1">
+    <row r="27" spans="1:39" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
@@ -2807,7 +2810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:39" ht="14.5" customHeight="1">
+    <row r="28" spans="1:39" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D28" s="9">
         <f>SUM(D2:D27)</f>
         <v>950</v>
@@ -2920,8 +2923,8 @@
         <v>655</v>
       </c>
     </row>
-    <row r="29" spans="1:39" ht="14.5" customHeight="1"/>
-    <row r="30" spans="1:39" ht="14.5">
+    <row r="29" spans="1:39" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="1:39" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>46</v>
       </c>
@@ -2975,13 +2978,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AW21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="31.08984375" customWidth="1"/>
     <col min="2" max="2" width="33.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" ht="14.5" customHeight="1">
+    <row r="1" spans="1:49" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17"/>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -3020,7 +3023,7 @@
       <c r="AJ1" s="30"/>
       <c r="AK1" s="30"/>
     </row>
-    <row r="2" spans="1:49" ht="14.5" customHeight="1">
+    <row r="2" spans="1:49" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18"/>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -3059,7 +3062,7 @@
       <c r="AJ2" s="30"/>
       <c r="AK2" s="30"/>
     </row>
-    <row r="3" spans="1:49" ht="29" customHeight="1">
+    <row r="3" spans="1:49" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
         <v>0</v>
       </c>
@@ -3170,7 +3173,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="14.5" hidden="1" customHeight="1">
+    <row r="4" spans="1:49" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="25" t="s">
         <v>51</v>
       </c>
@@ -3233,7 +3236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:49" ht="14.5" customHeight="1">
+    <row r="5" spans="1:49" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="28" t="s">
         <v>52</v>
       </c>
@@ -3288,7 +3291,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="6" spans="1:49" ht="14.5" hidden="1" customHeight="1">
+    <row r="6" spans="1:49" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="28" t="s">
         <v>53</v>
       </c>
@@ -3355,7 +3358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:49" ht="14.5" customHeight="1">
+    <row r="7" spans="1:49" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="28" t="s">
         <v>55</v>
       </c>
@@ -3411,7 +3414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:49" ht="14.5" hidden="1" customHeight="1">
+    <row r="8" spans="1:49" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="28" t="s">
         <v>57</v>
       </c>
@@ -3466,7 +3469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:49" ht="14.5" hidden="1" customHeight="1">
+    <row r="9" spans="1:49" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="28" t="s">
         <v>59</v>
       </c>
@@ -3529,7 +3532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:49" ht="14.5" customHeight="1">
+    <row r="10" spans="1:49" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="31" t="s">
         <v>62</v>
       </c>
@@ -3596,7 +3599,7 @@
       <c r="AV10" s="12"/>
       <c r="AW10" s="12"/>
     </row>
-    <row r="11" spans="1:49" ht="14.5" hidden="1" customHeight="1">
+    <row r="11" spans="1:49" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="28" t="s">
         <v>64</v>
       </c>
@@ -3655,7 +3658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:49" ht="14.5" customHeight="1">
+    <row r="12" spans="1:49" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="28" t="s">
         <v>65</v>
       </c>
@@ -3713,7 +3716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:49" ht="14.5" hidden="1" customHeight="1">
+    <row r="13" spans="1:49" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="28" t="s">
         <v>68</v>
       </c>
@@ -3780,7 +3783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:49" ht="14.25" hidden="1" customHeight="1">
+    <row r="14" spans="1:49" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="28" t="s">
         <v>69</v>
       </c>
@@ -3845,7 +3848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:49" ht="14.5" hidden="1" customHeight="1">
+    <row r="15" spans="1:49" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="28" t="s">
         <v>70</v>
       </c>
@@ -3912,7 +3915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:49" ht="14.5" hidden="1" customHeight="1">
+    <row r="16" spans="1:49" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="28" t="s">
         <v>71</v>
       </c>
@@ -3966,7 +3969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:38" ht="14.5" customHeight="1">
+    <row r="17" spans="1:38" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="28" t="s">
         <v>72</v>
       </c>
@@ -4027,7 +4030,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="18" spans="1:38" ht="14.5" hidden="1" customHeight="1">
+    <row r="18" spans="1:38" ht="14.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="28" t="s">
         <v>73</v>
       </c>
@@ -4092,7 +4095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:38" ht="14.5" customHeight="1">
+    <row r="19" spans="1:38" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="31" t="s">
         <v>74</v>
       </c>
@@ -4145,7 +4148,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="20" spans="1:38" ht="14.5" customHeight="1">
+    <row r="20" spans="1:38" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="36" t="s">
         <v>75</v>
       </c>
@@ -4197,7 +4200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:38" ht="14.5" customHeight="1">
+    <row r="21" spans="1:38" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F21" s="39">
         <f t="shared" ref="F21:R21" si="2">SUM(F4:F20)</f>
         <v>0</v>
@@ -4300,7 +4303,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AK1031"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="41.7265625" customWidth="1"/>
     <col min="2" max="2" width="5.26953125" customWidth="1"/>
@@ -4311,7 +4314,7 @@
     <col min="23" max="24" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -4351,7 +4354,7 @@
       <c r="AJ1" s="49"/>
       <c r="AK1" s="49"/>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4457,7 +4460,7 @@
       </c>
       <c r="AK2" s="49"/>
     </row>
-    <row r="3" spans="1:37">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A3" s="41" t="s">
         <v>81</v>
       </c>
@@ -4542,7 +4545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:37">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A4" s="44" t="s">
         <v>82</v>
       </c>
@@ -4610,7 +4613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A5" s="46" t="s">
         <v>83</v>
       </c>
@@ -4672,7 +4675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A6" s="44" t="s">
         <v>85</v>
       </c>
@@ -4728,7 +4731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:37">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A7" s="44" t="s">
         <v>86</v>
       </c>
@@ -4784,7 +4787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:37">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A8" s="41" t="s">
         <v>87</v>
       </c>
@@ -4860,7 +4863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:37">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A9" s="41" t="s">
         <v>89</v>
       </c>
@@ -4925,7 +4928,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="10" spans="1:37">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A10" s="41" t="s">
         <v>90</v>
       </c>
@@ -5003,7 +5006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:37">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A11" s="41" t="s">
         <v>91</v>
       </c>
@@ -5073,7 +5076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:37">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A12" s="41" t="s">
         <v>92</v>
       </c>
@@ -5149,7 +5152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:37">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A13" s="41" t="s">
         <v>93</v>
       </c>
@@ -5228,7 +5231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:37">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A14" s="41" t="s">
         <v>94</v>
       </c>
@@ -5301,7 +5304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:37">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A15" s="41" t="s">
         <v>96</v>
       </c>
@@ -5380,7 +5383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:37">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A16" s="41" t="s">
         <v>97</v>
       </c>
@@ -5453,7 +5456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:37">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A17" s="41" t="s">
         <v>98</v>
       </c>
@@ -5521,7 +5524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:37">
+    <row r="18" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A18" s="41" t="s">
         <v>100</v>
       </c>
@@ -5608,7 +5611,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:37">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A19" s="41" t="s">
         <v>102</v>
       </c>
@@ -5685,7 +5688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:37">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A20" s="44" t="s">
         <v>103</v>
       </c>
@@ -5768,7 +5771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:37">
+    <row r="21" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A21" s="44" t="s">
         <v>104</v>
       </c>
@@ -5845,7 +5848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:37">
+    <row r="22" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A22" s="44" t="s">
         <v>105</v>
       </c>
@@ -5915,7 +5918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:37">
+    <row r="23" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A23" s="44" t="s">
         <v>106</v>
       </c>
@@ -5979,7 +5982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:37">
+    <row r="24" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A24" s="44" t="s">
         <v>108</v>
       </c>
@@ -6047,7 +6050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:37">
+    <row r="25" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A25" s="44" t="s">
         <v>109</v>
       </c>
@@ -6121,7 +6124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:37">
+    <row r="26" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A26" s="57" t="s">
         <v>110</v>
       </c>
@@ -6178,7 +6181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:37">
+    <row r="27" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A27" s="44" t="s">
         <v>111</v>
       </c>
@@ -6232,7 +6235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:37">
+    <row r="28" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A28" s="44" t="s">
         <v>113</v>
       </c>
@@ -6278,7 +6281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:37">
+    <row r="29" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A29" s="14" t="s">
         <v>114</v>
       </c>
@@ -6324,7 +6327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:37">
+    <row r="30" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A30" s="14" t="s">
         <v>115</v>
       </c>
@@ -6364,7 +6367,7 @@
       <c r="AD30" s="49"/>
       <c r="AK30" s="49"/>
     </row>
-    <row r="31" spans="1:37">
+    <row r="31" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A31" s="14" t="s">
         <v>117</v>
       </c>
@@ -6404,7 +6407,7 @@
       <c r="AD31" s="49"/>
       <c r="AK31" s="49"/>
     </row>
-    <row r="32" spans="1:37">
+    <row r="32" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A32" s="14" t="s">
         <v>118</v>
       </c>
@@ -6444,7 +6447,7 @@
       <c r="AD32" s="49"/>
       <c r="AK32" s="49"/>
     </row>
-    <row r="33" spans="1:37">
+    <row r="33" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A33" s="14" t="s">
         <v>119</v>
       </c>
@@ -6486,7 +6489,7 @@
       <c r="AD33" s="49"/>
       <c r="AK33" s="49"/>
     </row>
-    <row r="34" spans="1:37">
+    <row r="34" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A34" s="14" t="s">
         <v>121</v>
       </c>
@@ -6528,7 +6531,7 @@
       <c r="AD34" s="49"/>
       <c r="AK34" s="49"/>
     </row>
-    <row r="35" spans="1:37">
+    <row r="35" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A35" s="14" t="s">
         <v>122</v>
       </c>
@@ -6570,7 +6573,7 @@
       <c r="AD35" s="49"/>
       <c r="AK35" s="49"/>
     </row>
-    <row r="36" spans="1:37">
+    <row r="36" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A36" s="14" t="s">
         <v>124</v>
       </c>
@@ -6612,7 +6615,7 @@
       <c r="AD36" s="49"/>
       <c r="AK36" s="49"/>
     </row>
-    <row r="37" spans="1:37">
+    <row r="37" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A37" s="14" t="s">
         <v>126</v>
       </c>
@@ -6652,7 +6655,7 @@
       <c r="AD37" s="49"/>
       <c r="AK37" s="49"/>
     </row>
-    <row r="38" spans="1:37">
+    <row r="38" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A38" s="14" t="s">
         <v>127</v>
       </c>
@@ -6692,7 +6695,7 @@
       <c r="AD38" s="49"/>
       <c r="AK38" s="49"/>
     </row>
-    <row r="39" spans="1:37">
+    <row r="39" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A39" s="14" t="s">
         <v>128</v>
       </c>
@@ -6732,7 +6735,7 @@
       <c r="AD39" s="49"/>
       <c r="AK39" s="49"/>
     </row>
-    <row r="40" spans="1:37">
+    <row r="40" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A40" s="14" t="s">
         <v>64</v>
       </c>
@@ -6772,7 +6775,7 @@
       <c r="AD40" s="49"/>
       <c r="AK40" s="49"/>
     </row>
-    <row r="41" spans="1:37">
+    <row r="41" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A41" s="14" t="s">
         <v>129</v>
       </c>
@@ -6812,7 +6815,7 @@
       <c r="AD41" s="49"/>
       <c r="AK41" s="49"/>
     </row>
-    <row r="42" spans="1:37">
+    <row r="42" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A42" s="14" t="s">
         <v>130</v>
       </c>
@@ -6852,7 +6855,7 @@
       <c r="AD42" s="49"/>
       <c r="AK42" s="49"/>
     </row>
-    <row r="43" spans="1:37">
+    <row r="43" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A43" s="14" t="s">
         <v>131</v>
       </c>
@@ -6892,7 +6895,7 @@
       <c r="AD43" s="49"/>
       <c r="AK43" s="49"/>
     </row>
-    <row r="44" spans="1:37">
+    <row r="44" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A44" s="14" t="s">
         <v>132</v>
       </c>
@@ -6932,7 +6935,7 @@
       <c r="AD44" s="49"/>
       <c r="AK44" s="49"/>
     </row>
-    <row r="45" spans="1:37">
+    <row r="45" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A45" s="14" t="s">
         <v>133</v>
       </c>
@@ -7023,7 +7026,7 @@
       </c>
       <c r="AK45" s="49"/>
     </row>
-    <row r="46" spans="1:37">
+    <row r="46" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A46" s="14" t="s">
         <v>134</v>
       </c>
@@ -7041,7 +7044,7 @@
       <c r="U46" s="49"/>
       <c r="V46" s="49"/>
     </row>
-    <row r="47" spans="1:37">
+    <row r="47" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A47" s="14" t="s">
         <v>135</v>
       </c>
@@ -7059,7 +7062,7 @@
       <c r="U47" s="49"/>
       <c r="V47" s="49"/>
     </row>
-    <row r="48" spans="1:37">
+    <row r="48" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A48" s="14" t="s">
         <v>136</v>
       </c>
@@ -7077,7 +7080,7 @@
       <c r="U48" s="49"/>
       <c r="V48" s="49"/>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A49" s="14" t="s">
         <v>137</v>
       </c>
@@ -7095,7 +7098,7 @@
       <c r="U49" s="49"/>
       <c r="V49" s="49"/>
     </row>
-    <row r="50" spans="1:22">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A50" s="14" t="s">
         <v>138</v>
       </c>
@@ -7113,7 +7116,7 @@
       <c r="U50" s="49"/>
       <c r="V50" s="49"/>
     </row>
-    <row r="51" spans="1:22">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A51" s="14" t="s">
         <v>139</v>
       </c>
@@ -7131,7 +7134,7 @@
       <c r="U51" s="49"/>
       <c r="V51" s="49"/>
     </row>
-    <row r="52" spans="1:22">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A52" s="14" t="s">
         <v>140</v>
       </c>
@@ -7149,7 +7152,7 @@
       <c r="U52" s="49"/>
       <c r="V52" s="49"/>
     </row>
-    <row r="53" spans="1:22">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A53" s="14" t="s">
         <v>141</v>
       </c>
@@ -7167,7 +7170,7 @@
       <c r="U53" s="49"/>
       <c r="V53" s="49"/>
     </row>
-    <row r="54" spans="1:22">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A54" s="14" t="s">
         <v>142</v>
       </c>
@@ -7185,7 +7188,7 @@
       <c r="U54" s="49"/>
       <c r="V54" s="49"/>
     </row>
-    <row r="55" spans="1:22">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A55" s="14" t="s">
         <v>143</v>
       </c>
@@ -7203,7 +7206,7 @@
       <c r="U55" s="49"/>
       <c r="V55" s="49"/>
     </row>
-    <row r="56" spans="1:22">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A56" s="14" t="s">
         <v>144</v>
       </c>
@@ -7221,7 +7224,7 @@
       <c r="U56" s="49"/>
       <c r="V56" s="49"/>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A57" s="14" t="s">
         <v>145</v>
       </c>
@@ -7239,7 +7242,7 @@
       <c r="U57" s="49"/>
       <c r="V57" s="49"/>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A58" s="14" t="s">
         <v>146</v>
       </c>
@@ -7257,7 +7260,7 @@
       <c r="U58" s="49"/>
       <c r="V58" s="49"/>
     </row>
-    <row r="59" spans="1:22">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A59" s="14" t="s">
         <v>147</v>
       </c>
@@ -7275,7 +7278,7 @@
       <c r="U59" s="49"/>
       <c r="V59" s="49"/>
     </row>
-    <row r="60" spans="1:22">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A60" s="14" t="s">
         <v>148</v>
       </c>
@@ -7293,7 +7296,7 @@
       <c r="U60" s="49"/>
       <c r="V60" s="49"/>
     </row>
-    <row r="61" spans="1:22">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A61" s="14" t="s">
         <v>149</v>
       </c>
@@ -7311,7 +7314,7 @@
       <c r="U61" s="49"/>
       <c r="V61" s="49"/>
     </row>
-    <row r="62" spans="1:22">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A62" s="14" t="s">
         <v>150</v>
       </c>
@@ -7329,7 +7332,7 @@
       <c r="U62" s="49"/>
       <c r="V62" s="49"/>
     </row>
-    <row r="63" spans="1:22">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A63" s="14" t="s">
         <v>152</v>
       </c>
@@ -7347,7 +7350,7 @@
       <c r="U63" s="49"/>
       <c r="V63" s="49"/>
     </row>
-    <row r="64" spans="1:22">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A64" s="14" t="s">
         <v>153</v>
       </c>
@@ -7365,7 +7368,7 @@
       <c r="U64" s="49"/>
       <c r="V64" s="49"/>
     </row>
-    <row r="65" spans="1:37">
+    <row r="65" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A65" s="14" t="s">
         <v>154</v>
       </c>
@@ -7383,7 +7386,7 @@
       <c r="U65" s="49"/>
       <c r="V65" s="49"/>
     </row>
-    <row r="66" spans="1:37">
+    <row r="66" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A66" s="11" t="s">
         <v>155</v>
       </c>
@@ -7430,7 +7433,7 @@
       <c r="AJ66" s="12"/>
       <c r="AK66" s="12"/>
     </row>
-    <row r="67" spans="1:37">
+    <row r="67" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A67" s="14" t="s">
         <v>134</v>
       </c>
@@ -7452,7 +7455,7 @@
       <c r="U67" s="49"/>
       <c r="V67" s="49"/>
     </row>
-    <row r="68" spans="1:37">
+    <row r="68" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A68" s="14" t="s">
         <v>34</v>
       </c>
@@ -7470,7 +7473,7 @@
       <c r="U68" s="49"/>
       <c r="V68" s="49"/>
     </row>
-    <row r="69" spans="1:37">
+    <row r="69" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A69" s="14" t="s">
         <v>156</v>
       </c>
@@ -7488,7 +7491,7 @@
       <c r="U69" s="49"/>
       <c r="V69" s="49"/>
     </row>
-    <row r="70" spans="1:37">
+    <row r="70" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A70" s="52" t="s">
         <v>93</v>
       </c>
@@ -7506,7 +7509,7 @@
       <c r="U70" s="49"/>
       <c r="V70" s="49"/>
     </row>
-    <row r="71" spans="1:37">
+    <row r="71" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A71" s="14" t="s">
         <v>157</v>
       </c>
@@ -7524,7 +7527,7 @@
       <c r="U71" s="49"/>
       <c r="V71" s="49"/>
     </row>
-    <row r="72" spans="1:37">
+    <row r="72" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A72" s="14" t="s">
         <v>158</v>
       </c>
@@ -7542,7 +7545,7 @@
       <c r="U72" s="49"/>
       <c r="V72" s="49"/>
     </row>
-    <row r="73" spans="1:37">
+    <row r="73" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A73" s="14" t="s">
         <v>159</v>
       </c>
@@ -7560,7 +7563,7 @@
       <c r="U73" s="49"/>
       <c r="V73" s="49"/>
     </row>
-    <row r="74" spans="1:37">
+    <row r="74" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A74" s="14" t="s">
         <v>160</v>
       </c>
@@ -7578,7 +7581,7 @@
       <c r="U74" s="49"/>
       <c r="V74" s="49"/>
     </row>
-    <row r="75" spans="1:37">
+    <row r="75" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A75" s="54" t="s">
         <v>161</v>
       </c>
@@ -7595,7 +7598,7 @@
       <c r="U75" s="49"/>
       <c r="V75" s="49"/>
     </row>
-    <row r="76" spans="1:37">
+    <row r="76" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A76" s="54" t="s">
         <v>162</v>
       </c>
@@ -7612,7 +7615,7 @@
       <c r="U76" s="49"/>
       <c r="V76" s="49"/>
     </row>
-    <row r="77" spans="1:37">
+    <row r="77" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A77" s="54" t="s">
         <v>163</v>
       </c>
@@ -7629,7 +7632,7 @@
       <c r="U77" s="49"/>
       <c r="V77" s="49"/>
     </row>
-    <row r="78" spans="1:37">
+    <row r="78" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A78" s="54" t="s">
         <v>164</v>
       </c>
@@ -7650,7 +7653,7 @@
       <c r="U78" s="49"/>
       <c r="V78" s="49"/>
     </row>
-    <row r="79" spans="1:37">
+    <row r="79" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A79" s="54"/>
       <c r="B79" s="55"/>
       <c r="C79" s="55"/>
@@ -7663,7 +7666,7 @@
       <c r="U79" s="49"/>
       <c r="V79" s="49"/>
     </row>
-    <row r="80" spans="1:37">
+    <row r="80" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A80" s="54" t="s">
         <v>5</v>
       </c>
@@ -7681,5707 +7684,5707 @@
       <c r="U80" s="49"/>
       <c r="V80" s="49"/>
     </row>
-    <row r="81" spans="19:22">
+    <row r="81" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S81" s="49"/>
       <c r="T81" s="49"/>
       <c r="U81" s="49"/>
       <c r="V81" s="49"/>
     </row>
-    <row r="82" spans="19:22">
+    <row r="82" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S82" s="49"/>
       <c r="T82" s="49"/>
       <c r="U82" s="49"/>
       <c r="V82" s="49"/>
     </row>
-    <row r="83" spans="19:22">
+    <row r="83" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S83" s="49"/>
       <c r="T83" s="49"/>
       <c r="U83" s="49"/>
       <c r="V83" s="49"/>
     </row>
-    <row r="84" spans="19:22">
+    <row r="84" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S84" s="49"/>
       <c r="T84" s="49"/>
       <c r="U84" s="49"/>
       <c r="V84" s="49"/>
     </row>
-    <row r="85" spans="19:22">
+    <row r="85" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S85" s="49"/>
       <c r="T85" s="49"/>
       <c r="U85" s="49"/>
       <c r="V85" s="49"/>
     </row>
-    <row r="86" spans="19:22">
+    <row r="86" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S86" s="49"/>
       <c r="T86" s="49"/>
       <c r="U86" s="49"/>
       <c r="V86" s="49"/>
     </row>
-    <row r="87" spans="19:22">
+    <row r="87" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S87" s="49"/>
       <c r="T87" s="49"/>
       <c r="U87" s="49"/>
       <c r="V87" s="49"/>
     </row>
-    <row r="88" spans="19:22">
+    <row r="88" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S88" s="49"/>
       <c r="T88" s="49"/>
       <c r="U88" s="49"/>
       <c r="V88" s="49"/>
     </row>
-    <row r="89" spans="19:22">
+    <row r="89" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S89" s="49"/>
       <c r="T89" s="49"/>
       <c r="U89" s="49"/>
       <c r="V89" s="49"/>
     </row>
-    <row r="90" spans="19:22">
+    <row r="90" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S90" s="49"/>
       <c r="T90" s="49"/>
       <c r="U90" s="49"/>
       <c r="V90" s="49"/>
     </row>
-    <row r="91" spans="19:22">
+    <row r="91" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S91" s="49"/>
       <c r="T91" s="49"/>
       <c r="U91" s="49"/>
       <c r="V91" s="49"/>
     </row>
-    <row r="92" spans="19:22">
+    <row r="92" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S92" s="49"/>
       <c r="T92" s="49"/>
       <c r="U92" s="49"/>
       <c r="V92" s="49"/>
     </row>
-    <row r="93" spans="19:22">
+    <row r="93" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S93" s="49"/>
       <c r="T93" s="49"/>
       <c r="U93" s="49"/>
       <c r="V93" s="49"/>
     </row>
-    <row r="94" spans="19:22">
+    <row r="94" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S94" s="49"/>
       <c r="T94" s="49"/>
       <c r="U94" s="49"/>
       <c r="V94" s="49"/>
     </row>
-    <row r="95" spans="19:22">
+    <row r="95" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S95" s="49"/>
       <c r="T95" s="49"/>
       <c r="U95" s="49"/>
       <c r="V95" s="49"/>
     </row>
-    <row r="96" spans="19:22">
+    <row r="96" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S96" s="49"/>
       <c r="T96" s="49"/>
       <c r="U96" s="49"/>
       <c r="V96" s="49"/>
     </row>
-    <row r="97" spans="19:22">
+    <row r="97" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S97" s="49"/>
       <c r="T97" s="49"/>
       <c r="U97" s="49"/>
       <c r="V97" s="49"/>
     </row>
-    <row r="98" spans="19:22">
+    <row r="98" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S98" s="49"/>
       <c r="T98" s="49"/>
       <c r="U98" s="49"/>
       <c r="V98" s="49"/>
     </row>
-    <row r="99" spans="19:22">
+    <row r="99" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S99" s="49"/>
       <c r="T99" s="49"/>
       <c r="U99" s="49"/>
       <c r="V99" s="49"/>
     </row>
-    <row r="100" spans="19:22">
+    <row r="100" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S100" s="49"/>
       <c r="T100" s="49"/>
       <c r="U100" s="49"/>
       <c r="V100" s="49"/>
     </row>
-    <row r="101" spans="19:22">
+    <row r="101" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S101" s="49"/>
       <c r="T101" s="49"/>
       <c r="U101" s="49"/>
       <c r="V101" s="49"/>
     </row>
-    <row r="102" spans="19:22">
+    <row r="102" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S102" s="49"/>
       <c r="T102" s="49"/>
       <c r="U102" s="49"/>
       <c r="V102" s="49"/>
     </row>
-    <row r="103" spans="19:22">
+    <row r="103" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S103" s="49"/>
       <c r="T103" s="49"/>
       <c r="U103" s="49"/>
       <c r="V103" s="49"/>
     </row>
-    <row r="104" spans="19:22">
+    <row r="104" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S104" s="49"/>
       <c r="T104" s="49"/>
       <c r="U104" s="49"/>
       <c r="V104" s="49"/>
     </row>
-    <row r="105" spans="19:22">
+    <row r="105" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S105" s="49"/>
       <c r="T105" s="49"/>
       <c r="U105" s="49"/>
       <c r="V105" s="49"/>
     </row>
-    <row r="106" spans="19:22">
+    <row r="106" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S106" s="49"/>
       <c r="T106" s="49"/>
       <c r="U106" s="49"/>
       <c r="V106" s="49"/>
     </row>
-    <row r="107" spans="19:22">
+    <row r="107" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S107" s="49"/>
       <c r="T107" s="49"/>
       <c r="U107" s="49"/>
       <c r="V107" s="49"/>
     </row>
-    <row r="108" spans="19:22">
+    <row r="108" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S108" s="49"/>
       <c r="T108" s="49"/>
       <c r="U108" s="49"/>
       <c r="V108" s="49"/>
     </row>
-    <row r="109" spans="19:22">
+    <row r="109" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S109" s="49"/>
       <c r="T109" s="49"/>
       <c r="U109" s="49"/>
       <c r="V109" s="49"/>
     </row>
-    <row r="110" spans="19:22">
+    <row r="110" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S110" s="49"/>
       <c r="T110" s="49"/>
       <c r="U110" s="49"/>
       <c r="V110" s="49"/>
     </row>
-    <row r="111" spans="19:22">
+    <row r="111" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S111" s="49"/>
       <c r="T111" s="49"/>
       <c r="U111" s="49"/>
       <c r="V111" s="49"/>
     </row>
-    <row r="112" spans="19:22">
+    <row r="112" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S112" s="49"/>
       <c r="T112" s="49"/>
       <c r="U112" s="49"/>
       <c r="V112" s="49"/>
     </row>
-    <row r="113" spans="19:22">
+    <row r="113" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S113" s="49"/>
       <c r="T113" s="49"/>
       <c r="U113" s="49"/>
       <c r="V113" s="49"/>
     </row>
-    <row r="114" spans="19:22">
+    <row r="114" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S114" s="49"/>
       <c r="T114" s="49"/>
       <c r="U114" s="49"/>
       <c r="V114" s="49"/>
     </row>
-    <row r="115" spans="19:22">
+    <row r="115" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S115" s="49"/>
       <c r="T115" s="49"/>
       <c r="U115" s="49"/>
       <c r="V115" s="49"/>
     </row>
-    <row r="116" spans="19:22">
+    <row r="116" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S116" s="49"/>
       <c r="T116" s="49"/>
       <c r="U116" s="49"/>
       <c r="V116" s="49"/>
     </row>
-    <row r="117" spans="19:22">
+    <row r="117" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S117" s="49"/>
       <c r="T117" s="49"/>
       <c r="U117" s="49"/>
       <c r="V117" s="49"/>
     </row>
-    <row r="118" spans="19:22">
+    <row r="118" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S118" s="49"/>
       <c r="T118" s="49"/>
       <c r="U118" s="49"/>
       <c r="V118" s="49"/>
     </row>
-    <row r="119" spans="19:22">
+    <row r="119" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S119" s="49"/>
       <c r="T119" s="49"/>
       <c r="U119" s="49"/>
       <c r="V119" s="49"/>
     </row>
-    <row r="120" spans="19:22">
+    <row r="120" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S120" s="49"/>
       <c r="T120" s="49"/>
       <c r="U120" s="49"/>
       <c r="V120" s="49"/>
     </row>
-    <row r="121" spans="19:22">
+    <row r="121" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S121" s="49"/>
       <c r="T121" s="49"/>
       <c r="U121" s="49"/>
       <c r="V121" s="49"/>
     </row>
-    <row r="122" spans="19:22">
+    <row r="122" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S122" s="49"/>
       <c r="T122" s="49"/>
       <c r="U122" s="49"/>
       <c r="V122" s="49"/>
     </row>
-    <row r="123" spans="19:22">
+    <row r="123" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S123" s="49"/>
       <c r="T123" s="49"/>
       <c r="U123" s="49"/>
       <c r="V123" s="49"/>
     </row>
-    <row r="124" spans="19:22">
+    <row r="124" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S124" s="49"/>
       <c r="T124" s="49"/>
       <c r="U124" s="49"/>
       <c r="V124" s="49"/>
     </row>
-    <row r="125" spans="19:22">
+    <row r="125" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S125" s="49"/>
       <c r="T125" s="49"/>
       <c r="U125" s="49"/>
       <c r="V125" s="49"/>
     </row>
-    <row r="126" spans="19:22">
+    <row r="126" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S126" s="49"/>
       <c r="T126" s="49"/>
       <c r="U126" s="49"/>
       <c r="V126" s="49"/>
     </row>
-    <row r="127" spans="19:22">
+    <row r="127" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S127" s="49"/>
       <c r="T127" s="49"/>
       <c r="U127" s="49"/>
       <c r="V127" s="49"/>
     </row>
-    <row r="128" spans="19:22">
+    <row r="128" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S128" s="49"/>
       <c r="T128" s="49"/>
       <c r="U128" s="49"/>
       <c r="V128" s="49"/>
     </row>
-    <row r="129" spans="19:22">
+    <row r="129" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S129" s="49"/>
       <c r="T129" s="49"/>
       <c r="U129" s="49"/>
       <c r="V129" s="49"/>
     </row>
-    <row r="130" spans="19:22">
+    <row r="130" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S130" s="49"/>
       <c r="T130" s="49"/>
       <c r="U130" s="49"/>
       <c r="V130" s="49"/>
     </row>
-    <row r="131" spans="19:22">
+    <row r="131" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S131" s="49"/>
       <c r="T131" s="49"/>
       <c r="U131" s="49"/>
       <c r="V131" s="49"/>
     </row>
-    <row r="132" spans="19:22">
+    <row r="132" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S132" s="49"/>
       <c r="T132" s="49"/>
       <c r="U132" s="49"/>
       <c r="V132" s="49"/>
     </row>
-    <row r="133" spans="19:22">
+    <row r="133" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S133" s="49"/>
       <c r="T133" s="49"/>
       <c r="U133" s="49"/>
       <c r="V133" s="49"/>
     </row>
-    <row r="134" spans="19:22">
+    <row r="134" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S134" s="49"/>
       <c r="T134" s="49"/>
       <c r="U134" s="49"/>
       <c r="V134" s="49"/>
     </row>
-    <row r="135" spans="19:22">
+    <row r="135" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S135" s="49"/>
       <c r="T135" s="49"/>
       <c r="U135" s="49"/>
       <c r="V135" s="49"/>
     </row>
-    <row r="136" spans="19:22">
+    <row r="136" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S136" s="49"/>
       <c r="T136" s="49"/>
       <c r="U136" s="49"/>
       <c r="V136" s="49"/>
     </row>
-    <row r="137" spans="19:22">
+    <row r="137" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S137" s="49"/>
       <c r="T137" s="49"/>
       <c r="U137" s="49"/>
       <c r="V137" s="49"/>
     </row>
-    <row r="138" spans="19:22">
+    <row r="138" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S138" s="49"/>
       <c r="T138" s="49"/>
       <c r="U138" s="49"/>
       <c r="V138" s="49"/>
     </row>
-    <row r="139" spans="19:22">
+    <row r="139" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S139" s="49"/>
       <c r="T139" s="49"/>
       <c r="U139" s="49"/>
       <c r="V139" s="49"/>
     </row>
-    <row r="140" spans="19:22">
+    <row r="140" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S140" s="49"/>
       <c r="T140" s="49"/>
       <c r="U140" s="49"/>
       <c r="V140" s="49"/>
     </row>
-    <row r="141" spans="19:22">
+    <row r="141" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S141" s="49"/>
       <c r="T141" s="49"/>
       <c r="U141" s="49"/>
       <c r="V141" s="49"/>
     </row>
-    <row r="142" spans="19:22">
+    <row r="142" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S142" s="49"/>
       <c r="T142" s="49"/>
       <c r="U142" s="49"/>
       <c r="V142" s="49"/>
     </row>
-    <row r="143" spans="19:22">
+    <row r="143" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S143" s="49"/>
       <c r="T143" s="49"/>
       <c r="U143" s="49"/>
       <c r="V143" s="49"/>
     </row>
-    <row r="144" spans="19:22">
+    <row r="144" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S144" s="49"/>
       <c r="T144" s="49"/>
       <c r="U144" s="49"/>
       <c r="V144" s="49"/>
     </row>
-    <row r="145" spans="19:22">
+    <row r="145" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S145" s="49"/>
       <c r="T145" s="49"/>
       <c r="U145" s="49"/>
       <c r="V145" s="49"/>
     </row>
-    <row r="146" spans="19:22">
+    <row r="146" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S146" s="49"/>
       <c r="T146" s="49"/>
       <c r="U146" s="49"/>
       <c r="V146" s="49"/>
     </row>
-    <row r="147" spans="19:22">
+    <row r="147" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S147" s="49"/>
       <c r="T147" s="49"/>
       <c r="U147" s="49"/>
       <c r="V147" s="49"/>
     </row>
-    <row r="148" spans="19:22">
+    <row r="148" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S148" s="49"/>
       <c r="T148" s="49"/>
       <c r="U148" s="49"/>
       <c r="V148" s="49"/>
     </row>
-    <row r="149" spans="19:22">
+    <row r="149" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S149" s="49"/>
       <c r="T149" s="49"/>
       <c r="U149" s="49"/>
       <c r="V149" s="49"/>
     </row>
-    <row r="150" spans="19:22">
+    <row r="150" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S150" s="49"/>
       <c r="T150" s="49"/>
       <c r="U150" s="49"/>
       <c r="V150" s="49"/>
     </row>
-    <row r="151" spans="19:22">
+    <row r="151" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S151" s="49"/>
       <c r="T151" s="49"/>
       <c r="U151" s="49"/>
       <c r="V151" s="49"/>
     </row>
-    <row r="152" spans="19:22">
+    <row r="152" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S152" s="49"/>
       <c r="T152" s="49"/>
       <c r="U152" s="49"/>
       <c r="V152" s="49"/>
     </row>
-    <row r="153" spans="19:22">
+    <row r="153" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S153" s="49"/>
       <c r="T153" s="49"/>
       <c r="U153" s="49"/>
       <c r="V153" s="49"/>
     </row>
-    <row r="154" spans="19:22">
+    <row r="154" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S154" s="49"/>
       <c r="T154" s="49"/>
       <c r="U154" s="49"/>
       <c r="V154" s="49"/>
     </row>
-    <row r="155" spans="19:22">
+    <row r="155" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S155" s="49"/>
       <c r="T155" s="49"/>
       <c r="U155" s="49"/>
       <c r="V155" s="49"/>
     </row>
-    <row r="156" spans="19:22">
+    <row r="156" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S156" s="49"/>
       <c r="T156" s="49"/>
       <c r="U156" s="49"/>
       <c r="V156" s="49"/>
     </row>
-    <row r="157" spans="19:22">
+    <row r="157" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S157" s="49"/>
       <c r="T157" s="49"/>
       <c r="U157" s="49"/>
       <c r="V157" s="49"/>
     </row>
-    <row r="158" spans="19:22">
+    <row r="158" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S158" s="49"/>
       <c r="T158" s="49"/>
       <c r="U158" s="49"/>
       <c r="V158" s="49"/>
     </row>
-    <row r="159" spans="19:22">
+    <row r="159" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S159" s="49"/>
       <c r="T159" s="49"/>
       <c r="U159" s="49"/>
       <c r="V159" s="49"/>
     </row>
-    <row r="160" spans="19:22">
+    <row r="160" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S160" s="49"/>
       <c r="T160" s="49"/>
       <c r="U160" s="49"/>
       <c r="V160" s="49"/>
     </row>
-    <row r="161" spans="19:22">
+    <row r="161" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S161" s="49"/>
       <c r="T161" s="49"/>
       <c r="U161" s="49"/>
       <c r="V161" s="49"/>
     </row>
-    <row r="162" spans="19:22">
+    <row r="162" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S162" s="49"/>
       <c r="T162" s="49"/>
       <c r="U162" s="49"/>
       <c r="V162" s="49"/>
     </row>
-    <row r="163" spans="19:22">
+    <row r="163" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S163" s="49"/>
       <c r="T163" s="49"/>
       <c r="U163" s="49"/>
       <c r="V163" s="49"/>
     </row>
-    <row r="164" spans="19:22">
+    <row r="164" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S164" s="49"/>
       <c r="T164" s="49"/>
       <c r="U164" s="49"/>
       <c r="V164" s="49"/>
     </row>
-    <row r="165" spans="19:22">
+    <row r="165" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S165" s="49"/>
       <c r="T165" s="49"/>
       <c r="U165" s="49"/>
       <c r="V165" s="49"/>
     </row>
-    <row r="166" spans="19:22">
+    <row r="166" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S166" s="49"/>
       <c r="T166" s="49"/>
       <c r="U166" s="49"/>
       <c r="V166" s="49"/>
     </row>
-    <row r="167" spans="19:22">
+    <row r="167" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S167" s="49"/>
       <c r="T167" s="49"/>
       <c r="U167" s="49"/>
       <c r="V167" s="49"/>
     </row>
-    <row r="168" spans="19:22">
+    <row r="168" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S168" s="49"/>
       <c r="T168" s="49"/>
       <c r="U168" s="49"/>
       <c r="V168" s="49"/>
     </row>
-    <row r="169" spans="19:22">
+    <row r="169" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S169" s="49"/>
       <c r="T169" s="49"/>
       <c r="U169" s="49"/>
       <c r="V169" s="49"/>
     </row>
-    <row r="170" spans="19:22">
+    <row r="170" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S170" s="49"/>
       <c r="T170" s="49"/>
       <c r="U170" s="49"/>
       <c r="V170" s="49"/>
     </row>
-    <row r="171" spans="19:22">
+    <row r="171" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S171" s="49"/>
       <c r="T171" s="49"/>
       <c r="U171" s="49"/>
       <c r="V171" s="49"/>
     </row>
-    <row r="172" spans="19:22">
+    <row r="172" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S172" s="49"/>
       <c r="T172" s="49"/>
       <c r="U172" s="49"/>
       <c r="V172" s="49"/>
     </row>
-    <row r="173" spans="19:22">
+    <row r="173" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S173" s="49"/>
       <c r="T173" s="49"/>
       <c r="U173" s="49"/>
       <c r="V173" s="49"/>
     </row>
-    <row r="174" spans="19:22">
+    <row r="174" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S174" s="49"/>
       <c r="T174" s="49"/>
       <c r="U174" s="49"/>
       <c r="V174" s="49"/>
     </row>
-    <row r="175" spans="19:22">
+    <row r="175" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S175" s="49"/>
       <c r="T175" s="49"/>
       <c r="U175" s="49"/>
       <c r="V175" s="49"/>
     </row>
-    <row r="176" spans="19:22">
+    <row r="176" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S176" s="49"/>
       <c r="T176" s="49"/>
       <c r="U176" s="49"/>
       <c r="V176" s="49"/>
     </row>
-    <row r="177" spans="19:22">
+    <row r="177" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S177" s="49"/>
       <c r="T177" s="49"/>
       <c r="U177" s="49"/>
       <c r="V177" s="49"/>
     </row>
-    <row r="178" spans="19:22">
+    <row r="178" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S178" s="49"/>
       <c r="T178" s="49"/>
       <c r="U178" s="49"/>
       <c r="V178" s="49"/>
     </row>
-    <row r="179" spans="19:22">
+    <row r="179" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S179" s="49"/>
       <c r="T179" s="49"/>
       <c r="U179" s="49"/>
       <c r="V179" s="49"/>
     </row>
-    <row r="180" spans="19:22">
+    <row r="180" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S180" s="49"/>
       <c r="T180" s="49"/>
       <c r="U180" s="49"/>
       <c r="V180" s="49"/>
     </row>
-    <row r="181" spans="19:22">
+    <row r="181" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S181" s="49"/>
       <c r="T181" s="49"/>
       <c r="U181" s="49"/>
       <c r="V181" s="49"/>
     </row>
-    <row r="182" spans="19:22">
+    <row r="182" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S182" s="49"/>
       <c r="T182" s="49"/>
       <c r="U182" s="49"/>
       <c r="V182" s="49"/>
     </row>
-    <row r="183" spans="19:22">
+    <row r="183" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S183" s="49"/>
       <c r="T183" s="49"/>
       <c r="U183" s="49"/>
       <c r="V183" s="49"/>
     </row>
-    <row r="184" spans="19:22">
+    <row r="184" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S184" s="49"/>
       <c r="T184" s="49"/>
       <c r="U184" s="49"/>
       <c r="V184" s="49"/>
     </row>
-    <row r="185" spans="19:22">
+    <row r="185" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S185" s="49"/>
       <c r="T185" s="49"/>
       <c r="U185" s="49"/>
       <c r="V185" s="49"/>
     </row>
-    <row r="186" spans="19:22">
+    <row r="186" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S186" s="49"/>
       <c r="T186" s="49"/>
       <c r="U186" s="49"/>
       <c r="V186" s="49"/>
     </row>
-    <row r="187" spans="19:22">
+    <row r="187" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S187" s="49"/>
       <c r="T187" s="49"/>
       <c r="U187" s="49"/>
       <c r="V187" s="49"/>
     </row>
-    <row r="188" spans="19:22">
+    <row r="188" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S188" s="49"/>
       <c r="T188" s="49"/>
       <c r="U188" s="49"/>
       <c r="V188" s="49"/>
     </row>
-    <row r="189" spans="19:22">
+    <row r="189" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S189" s="49"/>
       <c r="T189" s="49"/>
       <c r="U189" s="49"/>
       <c r="V189" s="49"/>
     </row>
-    <row r="190" spans="19:22">
+    <row r="190" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S190" s="49"/>
       <c r="T190" s="49"/>
       <c r="U190" s="49"/>
       <c r="V190" s="49"/>
     </row>
-    <row r="191" spans="19:22">
+    <row r="191" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S191" s="49"/>
       <c r="T191" s="49"/>
       <c r="U191" s="49"/>
       <c r="V191" s="49"/>
     </row>
-    <row r="192" spans="19:22">
+    <row r="192" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S192" s="49"/>
       <c r="T192" s="49"/>
       <c r="U192" s="49"/>
       <c r="V192" s="49"/>
     </row>
-    <row r="193" spans="19:22">
+    <row r="193" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S193" s="49"/>
       <c r="T193" s="49"/>
       <c r="U193" s="49"/>
       <c r="V193" s="49"/>
     </row>
-    <row r="194" spans="19:22">
+    <row r="194" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S194" s="49"/>
       <c r="T194" s="49"/>
       <c r="U194" s="49"/>
       <c r="V194" s="49"/>
     </row>
-    <row r="195" spans="19:22">
+    <row r="195" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S195" s="49"/>
       <c r="T195" s="49"/>
       <c r="U195" s="49"/>
       <c r="V195" s="49"/>
     </row>
-    <row r="196" spans="19:22">
+    <row r="196" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S196" s="49"/>
       <c r="T196" s="49"/>
       <c r="U196" s="49"/>
       <c r="V196" s="49"/>
     </row>
-    <row r="197" spans="19:22">
+    <row r="197" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S197" s="49"/>
       <c r="T197" s="49"/>
       <c r="U197" s="49"/>
       <c r="V197" s="49"/>
     </row>
-    <row r="198" spans="19:22">
+    <row r="198" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S198" s="49"/>
       <c r="T198" s="49"/>
       <c r="U198" s="49"/>
       <c r="V198" s="49"/>
     </row>
-    <row r="199" spans="19:22">
+    <row r="199" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S199" s="49"/>
       <c r="T199" s="49"/>
       <c r="U199" s="49"/>
       <c r="V199" s="49"/>
     </row>
-    <row r="200" spans="19:22">
+    <row r="200" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S200" s="49"/>
       <c r="T200" s="49"/>
       <c r="U200" s="49"/>
       <c r="V200" s="49"/>
     </row>
-    <row r="201" spans="19:22">
+    <row r="201" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S201" s="49"/>
       <c r="T201" s="49"/>
       <c r="U201" s="49"/>
       <c r="V201" s="49"/>
     </row>
-    <row r="202" spans="19:22">
+    <row r="202" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S202" s="49"/>
       <c r="T202" s="49"/>
       <c r="U202" s="49"/>
       <c r="V202" s="49"/>
     </row>
-    <row r="203" spans="19:22">
+    <row r="203" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S203" s="49"/>
       <c r="T203" s="49"/>
       <c r="U203" s="49"/>
       <c r="V203" s="49"/>
     </row>
-    <row r="204" spans="19:22">
+    <row r="204" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S204" s="49"/>
       <c r="T204" s="49"/>
       <c r="U204" s="49"/>
       <c r="V204" s="49"/>
     </row>
-    <row r="205" spans="19:22">
+    <row r="205" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S205" s="49"/>
       <c r="T205" s="49"/>
       <c r="U205" s="49"/>
       <c r="V205" s="49"/>
     </row>
-    <row r="206" spans="19:22">
+    <row r="206" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S206" s="49"/>
       <c r="T206" s="49"/>
       <c r="U206" s="49"/>
       <c r="V206" s="49"/>
     </row>
-    <row r="207" spans="19:22">
+    <row r="207" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S207" s="49"/>
       <c r="T207" s="49"/>
       <c r="U207" s="49"/>
       <c r="V207" s="49"/>
     </row>
-    <row r="208" spans="19:22">
+    <row r="208" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S208" s="49"/>
       <c r="T208" s="49"/>
       <c r="U208" s="49"/>
       <c r="V208" s="49"/>
     </row>
-    <row r="209" spans="19:22">
+    <row r="209" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S209" s="49"/>
       <c r="T209" s="49"/>
       <c r="U209" s="49"/>
       <c r="V209" s="49"/>
     </row>
-    <row r="210" spans="19:22">
+    <row r="210" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S210" s="49"/>
       <c r="T210" s="49"/>
       <c r="U210" s="49"/>
       <c r="V210" s="49"/>
     </row>
-    <row r="211" spans="19:22">
+    <row r="211" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S211" s="49"/>
       <c r="T211" s="49"/>
       <c r="U211" s="49"/>
       <c r="V211" s="49"/>
     </row>
-    <row r="212" spans="19:22">
+    <row r="212" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S212" s="49"/>
       <c r="T212" s="49"/>
       <c r="U212" s="49"/>
       <c r="V212" s="49"/>
     </row>
-    <row r="213" spans="19:22">
+    <row r="213" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S213" s="49"/>
       <c r="T213" s="49"/>
       <c r="U213" s="49"/>
       <c r="V213" s="49"/>
     </row>
-    <row r="214" spans="19:22">
+    <row r="214" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S214" s="49"/>
       <c r="T214" s="49"/>
       <c r="U214" s="49"/>
       <c r="V214" s="49"/>
     </row>
-    <row r="215" spans="19:22">
+    <row r="215" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S215" s="49"/>
       <c r="T215" s="49"/>
       <c r="U215" s="49"/>
       <c r="V215" s="49"/>
     </row>
-    <row r="216" spans="19:22">
+    <row r="216" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S216" s="49"/>
       <c r="T216" s="49"/>
       <c r="U216" s="49"/>
       <c r="V216" s="49"/>
     </row>
-    <row r="217" spans="19:22">
+    <row r="217" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S217" s="49"/>
       <c r="T217" s="49"/>
       <c r="U217" s="49"/>
       <c r="V217" s="49"/>
     </row>
-    <row r="218" spans="19:22">
+    <row r="218" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S218" s="49"/>
       <c r="T218" s="49"/>
       <c r="U218" s="49"/>
       <c r="V218" s="49"/>
     </row>
-    <row r="219" spans="19:22">
+    <row r="219" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S219" s="49"/>
       <c r="T219" s="49"/>
       <c r="U219" s="49"/>
       <c r="V219" s="49"/>
     </row>
-    <row r="220" spans="19:22">
+    <row r="220" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S220" s="49"/>
       <c r="T220" s="49"/>
       <c r="U220" s="49"/>
       <c r="V220" s="49"/>
     </row>
-    <row r="221" spans="19:22">
+    <row r="221" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S221" s="49"/>
       <c r="T221" s="49"/>
       <c r="U221" s="49"/>
       <c r="V221" s="49"/>
     </row>
-    <row r="222" spans="19:22">
+    <row r="222" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S222" s="49"/>
       <c r="T222" s="49"/>
       <c r="U222" s="49"/>
       <c r="V222" s="49"/>
     </row>
-    <row r="223" spans="19:22">
+    <row r="223" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S223" s="49"/>
       <c r="T223" s="49"/>
       <c r="U223" s="49"/>
       <c r="V223" s="49"/>
     </row>
-    <row r="224" spans="19:22">
+    <row r="224" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S224" s="49"/>
       <c r="T224" s="49"/>
       <c r="U224" s="49"/>
       <c r="V224" s="49"/>
     </row>
-    <row r="225" spans="19:22">
+    <row r="225" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S225" s="49"/>
       <c r="T225" s="49"/>
       <c r="U225" s="49"/>
       <c r="V225" s="49"/>
     </row>
-    <row r="226" spans="19:22">
+    <row r="226" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S226" s="49"/>
       <c r="T226" s="49"/>
       <c r="U226" s="49"/>
       <c r="V226" s="49"/>
     </row>
-    <row r="227" spans="19:22">
+    <row r="227" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S227" s="49"/>
       <c r="T227" s="49"/>
       <c r="U227" s="49"/>
       <c r="V227" s="49"/>
     </row>
-    <row r="228" spans="19:22">
+    <row r="228" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S228" s="49"/>
       <c r="T228" s="49"/>
       <c r="U228" s="49"/>
       <c r="V228" s="49"/>
     </row>
-    <row r="229" spans="19:22">
+    <row r="229" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S229" s="49"/>
       <c r="T229" s="49"/>
       <c r="U229" s="49"/>
       <c r="V229" s="49"/>
     </row>
-    <row r="230" spans="19:22">
+    <row r="230" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S230" s="49"/>
       <c r="T230" s="49"/>
       <c r="U230" s="49"/>
       <c r="V230" s="49"/>
     </row>
-    <row r="231" spans="19:22">
+    <row r="231" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S231" s="49"/>
       <c r="T231" s="49"/>
       <c r="U231" s="49"/>
       <c r="V231" s="49"/>
     </row>
-    <row r="232" spans="19:22">
+    <row r="232" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S232" s="49"/>
       <c r="T232" s="49"/>
       <c r="U232" s="49"/>
       <c r="V232" s="49"/>
     </row>
-    <row r="233" spans="19:22">
+    <row r="233" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S233" s="49"/>
       <c r="T233" s="49"/>
       <c r="U233" s="49"/>
       <c r="V233" s="49"/>
     </row>
-    <row r="234" spans="19:22">
+    <row r="234" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S234" s="49"/>
       <c r="T234" s="49"/>
       <c r="U234" s="49"/>
       <c r="V234" s="49"/>
     </row>
-    <row r="235" spans="19:22">
+    <row r="235" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S235" s="49"/>
       <c r="T235" s="49"/>
       <c r="U235" s="49"/>
       <c r="V235" s="49"/>
     </row>
-    <row r="236" spans="19:22">
+    <row r="236" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S236" s="49"/>
       <c r="T236" s="49"/>
       <c r="U236" s="49"/>
       <c r="V236" s="49"/>
     </row>
-    <row r="237" spans="19:22">
+    <row r="237" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S237" s="49"/>
       <c r="T237" s="49"/>
       <c r="U237" s="49"/>
       <c r="V237" s="49"/>
     </row>
-    <row r="238" spans="19:22">
+    <row r="238" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S238" s="49"/>
       <c r="T238" s="49"/>
       <c r="U238" s="49"/>
       <c r="V238" s="49"/>
     </row>
-    <row r="239" spans="19:22">
+    <row r="239" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S239" s="49"/>
       <c r="T239" s="49"/>
       <c r="U239" s="49"/>
       <c r="V239" s="49"/>
     </row>
-    <row r="240" spans="19:22">
+    <row r="240" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S240" s="49"/>
       <c r="T240" s="49"/>
       <c r="U240" s="49"/>
       <c r="V240" s="49"/>
     </row>
-    <row r="241" spans="19:22">
+    <row r="241" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S241" s="49"/>
       <c r="T241" s="49"/>
       <c r="U241" s="49"/>
       <c r="V241" s="49"/>
     </row>
-    <row r="242" spans="19:22">
+    <row r="242" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S242" s="49"/>
       <c r="T242" s="49"/>
       <c r="U242" s="49"/>
       <c r="V242" s="49"/>
     </row>
-    <row r="243" spans="19:22">
+    <row r="243" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S243" s="49"/>
       <c r="T243" s="49"/>
       <c r="U243" s="49"/>
       <c r="V243" s="49"/>
     </row>
-    <row r="244" spans="19:22">
+    <row r="244" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S244" s="49"/>
       <c r="T244" s="49"/>
       <c r="U244" s="49"/>
       <c r="V244" s="49"/>
     </row>
-    <row r="245" spans="19:22">
+    <row r="245" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S245" s="49"/>
       <c r="T245" s="49"/>
       <c r="U245" s="49"/>
       <c r="V245" s="49"/>
     </row>
-    <row r="246" spans="19:22">
+    <row r="246" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S246" s="49"/>
       <c r="T246" s="49"/>
       <c r="U246" s="49"/>
       <c r="V246" s="49"/>
     </row>
-    <row r="247" spans="19:22">
+    <row r="247" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S247" s="49"/>
       <c r="T247" s="49"/>
       <c r="U247" s="49"/>
       <c r="V247" s="49"/>
     </row>
-    <row r="248" spans="19:22">
+    <row r="248" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S248" s="49"/>
       <c r="T248" s="49"/>
       <c r="U248" s="49"/>
       <c r="V248" s="49"/>
     </row>
-    <row r="249" spans="19:22">
+    <row r="249" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S249" s="49"/>
       <c r="T249" s="49"/>
       <c r="U249" s="49"/>
       <c r="V249" s="49"/>
     </row>
-    <row r="250" spans="19:22">
+    <row r="250" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S250" s="49"/>
       <c r="T250" s="49"/>
       <c r="U250" s="49"/>
       <c r="V250" s="49"/>
     </row>
-    <row r="251" spans="19:22">
+    <row r="251" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S251" s="49"/>
       <c r="T251" s="49"/>
       <c r="U251" s="49"/>
       <c r="V251" s="49"/>
     </row>
-    <row r="252" spans="19:22">
+    <row r="252" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S252" s="49"/>
       <c r="T252" s="49"/>
       <c r="U252" s="49"/>
       <c r="V252" s="49"/>
     </row>
-    <row r="253" spans="19:22">
+    <row r="253" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S253" s="49"/>
       <c r="T253" s="49"/>
       <c r="U253" s="49"/>
       <c r="V253" s="49"/>
     </row>
-    <row r="254" spans="19:22">
+    <row r="254" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S254" s="49"/>
       <c r="T254" s="49"/>
       <c r="U254" s="49"/>
       <c r="V254" s="49"/>
     </row>
-    <row r="255" spans="19:22">
+    <row r="255" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S255" s="49"/>
       <c r="T255" s="49"/>
       <c r="U255" s="49"/>
       <c r="V255" s="49"/>
     </row>
-    <row r="256" spans="19:22">
+    <row r="256" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S256" s="49"/>
       <c r="T256" s="49"/>
       <c r="U256" s="49"/>
       <c r="V256" s="49"/>
     </row>
-    <row r="257" spans="19:22">
+    <row r="257" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S257" s="49"/>
       <c r="T257" s="49"/>
       <c r="U257" s="49"/>
       <c r="V257" s="49"/>
     </row>
-    <row r="258" spans="19:22">
+    <row r="258" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S258" s="49"/>
       <c r="T258" s="49"/>
       <c r="U258" s="49"/>
       <c r="V258" s="49"/>
     </row>
-    <row r="259" spans="19:22">
+    <row r="259" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S259" s="49"/>
       <c r="T259" s="49"/>
       <c r="U259" s="49"/>
       <c r="V259" s="49"/>
     </row>
-    <row r="260" spans="19:22">
+    <row r="260" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S260" s="49"/>
       <c r="T260" s="49"/>
       <c r="U260" s="49"/>
       <c r="V260" s="49"/>
     </row>
-    <row r="261" spans="19:22">
+    <row r="261" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S261" s="49"/>
       <c r="T261" s="49"/>
       <c r="U261" s="49"/>
       <c r="V261" s="49"/>
     </row>
-    <row r="262" spans="19:22">
+    <row r="262" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S262" s="49"/>
       <c r="T262" s="49"/>
       <c r="U262" s="49"/>
       <c r="V262" s="49"/>
     </row>
-    <row r="263" spans="19:22">
+    <row r="263" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S263" s="49"/>
       <c r="T263" s="49"/>
       <c r="U263" s="49"/>
       <c r="V263" s="49"/>
     </row>
-    <row r="264" spans="19:22">
+    <row r="264" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S264" s="49"/>
       <c r="T264" s="49"/>
       <c r="U264" s="49"/>
       <c r="V264" s="49"/>
     </row>
-    <row r="265" spans="19:22">
+    <row r="265" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S265" s="49"/>
       <c r="T265" s="49"/>
       <c r="U265" s="49"/>
       <c r="V265" s="49"/>
     </row>
-    <row r="266" spans="19:22">
+    <row r="266" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S266" s="49"/>
       <c r="T266" s="49"/>
       <c r="U266" s="49"/>
       <c r="V266" s="49"/>
     </row>
-    <row r="267" spans="19:22">
+    <row r="267" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S267" s="49"/>
       <c r="T267" s="49"/>
       <c r="U267" s="49"/>
       <c r="V267" s="49"/>
     </row>
-    <row r="268" spans="19:22">
+    <row r="268" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S268" s="49"/>
       <c r="T268" s="49"/>
       <c r="U268" s="49"/>
       <c r="V268" s="49"/>
     </row>
-    <row r="269" spans="19:22">
+    <row r="269" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S269" s="49"/>
       <c r="T269" s="49"/>
       <c r="U269" s="49"/>
       <c r="V269" s="49"/>
     </row>
-    <row r="270" spans="19:22">
+    <row r="270" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S270" s="49"/>
       <c r="T270" s="49"/>
       <c r="U270" s="49"/>
       <c r="V270" s="49"/>
     </row>
-    <row r="271" spans="19:22">
+    <row r="271" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S271" s="49"/>
       <c r="T271" s="49"/>
       <c r="U271" s="49"/>
       <c r="V271" s="49"/>
     </row>
-    <row r="272" spans="19:22">
+    <row r="272" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S272" s="49"/>
       <c r="T272" s="49"/>
       <c r="U272" s="49"/>
       <c r="V272" s="49"/>
     </row>
-    <row r="273" spans="19:22">
+    <row r="273" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S273" s="49"/>
       <c r="T273" s="49"/>
       <c r="U273" s="49"/>
       <c r="V273" s="49"/>
     </row>
-    <row r="274" spans="19:22">
+    <row r="274" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S274" s="49"/>
       <c r="T274" s="49"/>
       <c r="U274" s="49"/>
       <c r="V274" s="49"/>
     </row>
-    <row r="275" spans="19:22">
+    <row r="275" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S275" s="49"/>
       <c r="T275" s="49"/>
       <c r="U275" s="49"/>
       <c r="V275" s="49"/>
     </row>
-    <row r="276" spans="19:22">
+    <row r="276" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S276" s="49"/>
       <c r="T276" s="49"/>
       <c r="U276" s="49"/>
       <c r="V276" s="49"/>
     </row>
-    <row r="277" spans="19:22">
+    <row r="277" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S277" s="49"/>
       <c r="T277" s="49"/>
       <c r="U277" s="49"/>
       <c r="V277" s="49"/>
     </row>
-    <row r="278" spans="19:22">
+    <row r="278" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S278" s="49"/>
       <c r="T278" s="49"/>
       <c r="U278" s="49"/>
       <c r="V278" s="49"/>
     </row>
-    <row r="279" spans="19:22">
+    <row r="279" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S279" s="49"/>
       <c r="T279" s="49"/>
       <c r="U279" s="49"/>
       <c r="V279" s="49"/>
     </row>
-    <row r="280" spans="19:22">
+    <row r="280" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S280" s="49"/>
       <c r="T280" s="49"/>
       <c r="U280" s="49"/>
       <c r="V280" s="49"/>
     </row>
-    <row r="281" spans="19:22">
+    <row r="281" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S281" s="49"/>
       <c r="T281" s="49"/>
       <c r="U281" s="49"/>
       <c r="V281" s="49"/>
     </row>
-    <row r="282" spans="19:22">
+    <row r="282" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S282" s="49"/>
       <c r="T282" s="49"/>
       <c r="U282" s="49"/>
       <c r="V282" s="49"/>
     </row>
-    <row r="283" spans="19:22">
+    <row r="283" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S283" s="49"/>
       <c r="T283" s="49"/>
       <c r="U283" s="49"/>
       <c r="V283" s="49"/>
     </row>
-    <row r="284" spans="19:22">
+    <row r="284" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S284" s="49"/>
       <c r="T284" s="49"/>
       <c r="U284" s="49"/>
       <c r="V284" s="49"/>
     </row>
-    <row r="285" spans="19:22">
+    <row r="285" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S285" s="49"/>
       <c r="T285" s="49"/>
       <c r="U285" s="49"/>
       <c r="V285" s="49"/>
     </row>
-    <row r="286" spans="19:22">
+    <row r="286" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S286" s="49"/>
       <c r="T286" s="49"/>
       <c r="U286" s="49"/>
       <c r="V286" s="49"/>
     </row>
-    <row r="287" spans="19:22">
+    <row r="287" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S287" s="49"/>
       <c r="T287" s="49"/>
       <c r="U287" s="49"/>
       <c r="V287" s="49"/>
     </row>
-    <row r="288" spans="19:22">
+    <row r="288" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S288" s="49"/>
       <c r="T288" s="49"/>
       <c r="U288" s="49"/>
       <c r="V288" s="49"/>
     </row>
-    <row r="289" spans="19:22">
+    <row r="289" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S289" s="49"/>
       <c r="T289" s="49"/>
       <c r="U289" s="49"/>
       <c r="V289" s="49"/>
     </row>
-    <row r="290" spans="19:22">
+    <row r="290" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S290" s="49"/>
       <c r="T290" s="49"/>
       <c r="U290" s="49"/>
       <c r="V290" s="49"/>
     </row>
-    <row r="291" spans="19:22">
+    <row r="291" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S291" s="49"/>
       <c r="T291" s="49"/>
       <c r="U291" s="49"/>
       <c r="V291" s="49"/>
     </row>
-    <row r="292" spans="19:22">
+    <row r="292" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S292" s="49"/>
       <c r="T292" s="49"/>
       <c r="U292" s="49"/>
       <c r="V292" s="49"/>
     </row>
-    <row r="293" spans="19:22">
+    <row r="293" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S293" s="49"/>
       <c r="T293" s="49"/>
       <c r="U293" s="49"/>
       <c r="V293" s="49"/>
     </row>
-    <row r="294" spans="19:22">
+    <row r="294" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S294" s="49"/>
       <c r="T294" s="49"/>
       <c r="U294" s="49"/>
       <c r="V294" s="49"/>
     </row>
-    <row r="295" spans="19:22">
+    <row r="295" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S295" s="49"/>
       <c r="T295" s="49"/>
       <c r="U295" s="49"/>
       <c r="V295" s="49"/>
     </row>
-    <row r="296" spans="19:22">
+    <row r="296" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S296" s="49"/>
       <c r="T296" s="49"/>
       <c r="U296" s="49"/>
       <c r="V296" s="49"/>
     </row>
-    <row r="297" spans="19:22">
+    <row r="297" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S297" s="49"/>
       <c r="T297" s="49"/>
       <c r="U297" s="49"/>
       <c r="V297" s="49"/>
     </row>
-    <row r="298" spans="19:22">
+    <row r="298" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S298" s="49"/>
       <c r="T298" s="49"/>
       <c r="U298" s="49"/>
       <c r="V298" s="49"/>
     </row>
-    <row r="299" spans="19:22">
+    <row r="299" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S299" s="49"/>
       <c r="T299" s="49"/>
       <c r="U299" s="49"/>
       <c r="V299" s="49"/>
     </row>
-    <row r="300" spans="19:22">
+    <row r="300" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S300" s="49"/>
       <c r="T300" s="49"/>
       <c r="U300" s="49"/>
       <c r="V300" s="49"/>
     </row>
-    <row r="301" spans="19:22">
+    <row r="301" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S301" s="49"/>
       <c r="T301" s="49"/>
       <c r="U301" s="49"/>
       <c r="V301" s="49"/>
     </row>
-    <row r="302" spans="19:22">
+    <row r="302" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S302" s="49"/>
       <c r="T302" s="49"/>
       <c r="U302" s="49"/>
       <c r="V302" s="49"/>
     </row>
-    <row r="303" spans="19:22">
+    <row r="303" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S303" s="49"/>
       <c r="T303" s="49"/>
       <c r="U303" s="49"/>
       <c r="V303" s="49"/>
     </row>
-    <row r="304" spans="19:22">
+    <row r="304" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S304" s="49"/>
       <c r="T304" s="49"/>
       <c r="U304" s="49"/>
       <c r="V304" s="49"/>
     </row>
-    <row r="305" spans="19:22">
+    <row r="305" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S305" s="49"/>
       <c r="T305" s="49"/>
       <c r="U305" s="49"/>
       <c r="V305" s="49"/>
     </row>
-    <row r="306" spans="19:22">
+    <row r="306" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S306" s="49"/>
       <c r="T306" s="49"/>
       <c r="U306" s="49"/>
       <c r="V306" s="49"/>
     </row>
-    <row r="307" spans="19:22">
+    <row r="307" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S307" s="49"/>
       <c r="T307" s="49"/>
       <c r="U307" s="49"/>
       <c r="V307" s="49"/>
     </row>
-    <row r="308" spans="19:22">
+    <row r="308" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S308" s="49"/>
       <c r="T308" s="49"/>
       <c r="U308" s="49"/>
       <c r="V308" s="49"/>
     </row>
-    <row r="309" spans="19:22">
+    <row r="309" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S309" s="49"/>
       <c r="T309" s="49"/>
       <c r="U309" s="49"/>
       <c r="V309" s="49"/>
     </row>
-    <row r="310" spans="19:22">
+    <row r="310" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S310" s="49"/>
       <c r="T310" s="49"/>
       <c r="U310" s="49"/>
       <c r="V310" s="49"/>
     </row>
-    <row r="311" spans="19:22">
+    <row r="311" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S311" s="49"/>
       <c r="T311" s="49"/>
       <c r="U311" s="49"/>
       <c r="V311" s="49"/>
     </row>
-    <row r="312" spans="19:22">
+    <row r="312" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S312" s="49"/>
       <c r="T312" s="49"/>
       <c r="U312" s="49"/>
       <c r="V312" s="49"/>
     </row>
-    <row r="313" spans="19:22">
+    <row r="313" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S313" s="49"/>
       <c r="T313" s="49"/>
       <c r="U313" s="49"/>
       <c r="V313" s="49"/>
     </row>
-    <row r="314" spans="19:22">
+    <row r="314" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S314" s="49"/>
       <c r="T314" s="49"/>
       <c r="U314" s="49"/>
       <c r="V314" s="49"/>
     </row>
-    <row r="315" spans="19:22">
+    <row r="315" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S315" s="49"/>
       <c r="T315" s="49"/>
       <c r="U315" s="49"/>
       <c r="V315" s="49"/>
     </row>
-    <row r="316" spans="19:22">
+    <row r="316" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S316" s="49"/>
       <c r="T316" s="49"/>
       <c r="U316" s="49"/>
       <c r="V316" s="49"/>
     </row>
-    <row r="317" spans="19:22">
+    <row r="317" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S317" s="49"/>
       <c r="T317" s="49"/>
       <c r="U317" s="49"/>
       <c r="V317" s="49"/>
     </row>
-    <row r="318" spans="19:22">
+    <row r="318" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S318" s="49"/>
       <c r="T318" s="49"/>
       <c r="U318" s="49"/>
       <c r="V318" s="49"/>
     </row>
-    <row r="319" spans="19:22">
+    <row r="319" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S319" s="49"/>
       <c r="T319" s="49"/>
       <c r="U319" s="49"/>
       <c r="V319" s="49"/>
     </row>
-    <row r="320" spans="19:22">
+    <row r="320" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S320" s="49"/>
       <c r="T320" s="49"/>
       <c r="U320" s="49"/>
       <c r="V320" s="49"/>
     </row>
-    <row r="321" spans="19:22">
+    <row r="321" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S321" s="49"/>
       <c r="T321" s="49"/>
       <c r="U321" s="49"/>
       <c r="V321" s="49"/>
     </row>
-    <row r="322" spans="19:22">
+    <row r="322" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S322" s="49"/>
       <c r="T322" s="49"/>
       <c r="U322" s="49"/>
       <c r="V322" s="49"/>
     </row>
-    <row r="323" spans="19:22">
+    <row r="323" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S323" s="49"/>
       <c r="T323" s="49"/>
       <c r="U323" s="49"/>
       <c r="V323" s="49"/>
     </row>
-    <row r="324" spans="19:22">
+    <row r="324" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S324" s="49"/>
       <c r="T324" s="49"/>
       <c r="U324" s="49"/>
       <c r="V324" s="49"/>
     </row>
-    <row r="325" spans="19:22">
+    <row r="325" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S325" s="49"/>
       <c r="T325" s="49"/>
       <c r="U325" s="49"/>
       <c r="V325" s="49"/>
     </row>
-    <row r="326" spans="19:22">
+    <row r="326" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S326" s="49"/>
       <c r="T326" s="49"/>
       <c r="U326" s="49"/>
       <c r="V326" s="49"/>
     </row>
-    <row r="327" spans="19:22">
+    <row r="327" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S327" s="49"/>
       <c r="T327" s="49"/>
       <c r="U327" s="49"/>
       <c r="V327" s="49"/>
     </row>
-    <row r="328" spans="19:22">
+    <row r="328" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S328" s="49"/>
       <c r="T328" s="49"/>
       <c r="U328" s="49"/>
       <c r="V328" s="49"/>
     </row>
-    <row r="329" spans="19:22">
+    <row r="329" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S329" s="49"/>
       <c r="T329" s="49"/>
       <c r="U329" s="49"/>
       <c r="V329" s="49"/>
     </row>
-    <row r="330" spans="19:22">
+    <row r="330" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S330" s="49"/>
       <c r="T330" s="49"/>
       <c r="U330" s="49"/>
       <c r="V330" s="49"/>
     </row>
-    <row r="331" spans="19:22">
+    <row r="331" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S331" s="49"/>
       <c r="T331" s="49"/>
       <c r="U331" s="49"/>
       <c r="V331" s="49"/>
     </row>
-    <row r="332" spans="19:22">
+    <row r="332" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S332" s="49"/>
       <c r="T332" s="49"/>
       <c r="U332" s="49"/>
       <c r="V332" s="49"/>
     </row>
-    <row r="333" spans="19:22">
+    <row r="333" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S333" s="49"/>
       <c r="T333" s="49"/>
       <c r="U333" s="49"/>
       <c r="V333" s="49"/>
     </row>
-    <row r="334" spans="19:22">
+    <row r="334" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S334" s="49"/>
       <c r="T334" s="49"/>
       <c r="U334" s="49"/>
       <c r="V334" s="49"/>
     </row>
-    <row r="335" spans="19:22">
+    <row r="335" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S335" s="49"/>
       <c r="T335" s="49"/>
       <c r="U335" s="49"/>
       <c r="V335" s="49"/>
     </row>
-    <row r="336" spans="19:22">
+    <row r="336" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S336" s="49"/>
       <c r="T336" s="49"/>
       <c r="U336" s="49"/>
       <c r="V336" s="49"/>
     </row>
-    <row r="337" spans="19:22">
+    <row r="337" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S337" s="49"/>
       <c r="T337" s="49"/>
       <c r="U337" s="49"/>
       <c r="V337" s="49"/>
     </row>
-    <row r="338" spans="19:22">
+    <row r="338" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S338" s="49"/>
       <c r="T338" s="49"/>
       <c r="U338" s="49"/>
       <c r="V338" s="49"/>
     </row>
-    <row r="339" spans="19:22">
+    <row r="339" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S339" s="49"/>
       <c r="T339" s="49"/>
       <c r="U339" s="49"/>
       <c r="V339" s="49"/>
     </row>
-    <row r="340" spans="19:22">
+    <row r="340" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S340" s="49"/>
       <c r="T340" s="49"/>
       <c r="U340" s="49"/>
       <c r="V340" s="49"/>
     </row>
-    <row r="341" spans="19:22">
+    <row r="341" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S341" s="49"/>
       <c r="T341" s="49"/>
       <c r="U341" s="49"/>
       <c r="V341" s="49"/>
     </row>
-    <row r="342" spans="19:22">
+    <row r="342" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S342" s="49"/>
       <c r="T342" s="49"/>
       <c r="U342" s="49"/>
       <c r="V342" s="49"/>
     </row>
-    <row r="343" spans="19:22">
+    <row r="343" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S343" s="49"/>
       <c r="T343" s="49"/>
       <c r="U343" s="49"/>
       <c r="V343" s="49"/>
     </row>
-    <row r="344" spans="19:22">
+    <row r="344" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S344" s="49"/>
       <c r="T344" s="49"/>
       <c r="U344" s="49"/>
       <c r="V344" s="49"/>
     </row>
-    <row r="345" spans="19:22">
+    <row r="345" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S345" s="49"/>
       <c r="T345" s="49"/>
       <c r="U345" s="49"/>
       <c r="V345" s="49"/>
     </row>
-    <row r="346" spans="19:22">
+    <row r="346" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S346" s="49"/>
       <c r="T346" s="49"/>
       <c r="U346" s="49"/>
       <c r="V346" s="49"/>
     </row>
-    <row r="347" spans="19:22">
+    <row r="347" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S347" s="49"/>
       <c r="T347" s="49"/>
       <c r="U347" s="49"/>
       <c r="V347" s="49"/>
     </row>
-    <row r="348" spans="19:22">
+    <row r="348" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S348" s="49"/>
       <c r="T348" s="49"/>
       <c r="U348" s="49"/>
       <c r="V348" s="49"/>
     </row>
-    <row r="349" spans="19:22">
+    <row r="349" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S349" s="49"/>
       <c r="T349" s="49"/>
       <c r="U349" s="49"/>
       <c r="V349" s="49"/>
     </row>
-    <row r="350" spans="19:22">
+    <row r="350" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S350" s="49"/>
       <c r="T350" s="49"/>
       <c r="U350" s="49"/>
       <c r="V350" s="49"/>
     </row>
-    <row r="351" spans="19:22">
+    <row r="351" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S351" s="49"/>
       <c r="T351" s="49"/>
       <c r="U351" s="49"/>
       <c r="V351" s="49"/>
     </row>
-    <row r="352" spans="19:22">
+    <row r="352" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S352" s="49"/>
       <c r="T352" s="49"/>
       <c r="U352" s="49"/>
       <c r="V352" s="49"/>
     </row>
-    <row r="353" spans="19:22">
+    <row r="353" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S353" s="49"/>
       <c r="T353" s="49"/>
       <c r="U353" s="49"/>
       <c r="V353" s="49"/>
     </row>
-    <row r="354" spans="19:22">
+    <row r="354" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S354" s="49"/>
       <c r="T354" s="49"/>
       <c r="U354" s="49"/>
       <c r="V354" s="49"/>
     </row>
-    <row r="355" spans="19:22">
+    <row r="355" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S355" s="49"/>
       <c r="T355" s="49"/>
       <c r="U355" s="49"/>
       <c r="V355" s="49"/>
     </row>
-    <row r="356" spans="19:22">
+    <row r="356" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S356" s="49"/>
       <c r="T356" s="49"/>
       <c r="U356" s="49"/>
       <c r="V356" s="49"/>
     </row>
-    <row r="357" spans="19:22">
+    <row r="357" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S357" s="49"/>
       <c r="T357" s="49"/>
       <c r="U357" s="49"/>
       <c r="V357" s="49"/>
     </row>
-    <row r="358" spans="19:22">
+    <row r="358" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S358" s="49"/>
       <c r="T358" s="49"/>
       <c r="U358" s="49"/>
       <c r="V358" s="49"/>
     </row>
-    <row r="359" spans="19:22">
+    <row r="359" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S359" s="49"/>
       <c r="T359" s="49"/>
       <c r="U359" s="49"/>
       <c r="V359" s="49"/>
     </row>
-    <row r="360" spans="19:22">
+    <row r="360" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S360" s="49"/>
       <c r="T360" s="49"/>
       <c r="U360" s="49"/>
       <c r="V360" s="49"/>
     </row>
-    <row r="361" spans="19:22">
+    <row r="361" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S361" s="49"/>
       <c r="T361" s="49"/>
       <c r="U361" s="49"/>
       <c r="V361" s="49"/>
     </row>
-    <row r="362" spans="19:22">
+    <row r="362" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S362" s="49"/>
       <c r="T362" s="49"/>
       <c r="U362" s="49"/>
       <c r="V362" s="49"/>
     </row>
-    <row r="363" spans="19:22">
+    <row r="363" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S363" s="49"/>
       <c r="T363" s="49"/>
       <c r="U363" s="49"/>
       <c r="V363" s="49"/>
     </row>
-    <row r="364" spans="19:22">
+    <row r="364" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S364" s="49"/>
       <c r="T364" s="49"/>
       <c r="U364" s="49"/>
       <c r="V364" s="49"/>
     </row>
-    <row r="365" spans="19:22">
+    <row r="365" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S365" s="49"/>
       <c r="T365" s="49"/>
       <c r="U365" s="49"/>
       <c r="V365" s="49"/>
     </row>
-    <row r="366" spans="19:22">
+    <row r="366" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S366" s="49"/>
       <c r="T366" s="49"/>
       <c r="U366" s="49"/>
       <c r="V366" s="49"/>
     </row>
-    <row r="367" spans="19:22">
+    <row r="367" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S367" s="49"/>
       <c r="T367" s="49"/>
       <c r="U367" s="49"/>
       <c r="V367" s="49"/>
     </row>
-    <row r="368" spans="19:22">
+    <row r="368" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S368" s="49"/>
       <c r="T368" s="49"/>
       <c r="U368" s="49"/>
       <c r="V368" s="49"/>
     </row>
-    <row r="369" spans="19:22">
+    <row r="369" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S369" s="49"/>
       <c r="T369" s="49"/>
       <c r="U369" s="49"/>
       <c r="V369" s="49"/>
     </row>
-    <row r="370" spans="19:22">
+    <row r="370" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S370" s="49"/>
       <c r="T370" s="49"/>
       <c r="U370" s="49"/>
       <c r="V370" s="49"/>
     </row>
-    <row r="371" spans="19:22">
+    <row r="371" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S371" s="49"/>
       <c r="T371" s="49"/>
       <c r="U371" s="49"/>
       <c r="V371" s="49"/>
     </row>
-    <row r="372" spans="19:22">
+    <row r="372" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S372" s="49"/>
       <c r="T372" s="49"/>
       <c r="U372" s="49"/>
       <c r="V372" s="49"/>
     </row>
-    <row r="373" spans="19:22">
+    <row r="373" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S373" s="49"/>
       <c r="T373" s="49"/>
       <c r="U373" s="49"/>
       <c r="V373" s="49"/>
     </row>
-    <row r="374" spans="19:22">
+    <row r="374" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S374" s="49"/>
       <c r="T374" s="49"/>
       <c r="U374" s="49"/>
       <c r="V374" s="49"/>
     </row>
-    <row r="375" spans="19:22">
+    <row r="375" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S375" s="49"/>
       <c r="T375" s="49"/>
       <c r="U375" s="49"/>
       <c r="V375" s="49"/>
     </row>
-    <row r="376" spans="19:22">
+    <row r="376" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S376" s="49"/>
       <c r="T376" s="49"/>
       <c r="U376" s="49"/>
       <c r="V376" s="49"/>
     </row>
-    <row r="377" spans="19:22">
+    <row r="377" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S377" s="49"/>
       <c r="T377" s="49"/>
       <c r="U377" s="49"/>
       <c r="V377" s="49"/>
     </row>
-    <row r="378" spans="19:22">
+    <row r="378" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S378" s="49"/>
       <c r="T378" s="49"/>
       <c r="U378" s="49"/>
       <c r="V378" s="49"/>
     </row>
-    <row r="379" spans="19:22">
+    <row r="379" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S379" s="49"/>
       <c r="T379" s="49"/>
       <c r="U379" s="49"/>
       <c r="V379" s="49"/>
     </row>
-    <row r="380" spans="19:22">
+    <row r="380" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S380" s="49"/>
       <c r="T380" s="49"/>
       <c r="U380" s="49"/>
       <c r="V380" s="49"/>
     </row>
-    <row r="381" spans="19:22">
+    <row r="381" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S381" s="49"/>
       <c r="T381" s="49"/>
       <c r="U381" s="49"/>
       <c r="V381" s="49"/>
     </row>
-    <row r="382" spans="19:22">
+    <row r="382" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S382" s="49"/>
       <c r="T382" s="49"/>
       <c r="U382" s="49"/>
       <c r="V382" s="49"/>
     </row>
-    <row r="383" spans="19:22">
+    <row r="383" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S383" s="49"/>
       <c r="T383" s="49"/>
       <c r="U383" s="49"/>
       <c r="V383" s="49"/>
     </row>
-    <row r="384" spans="19:22">
+    <row r="384" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S384" s="49"/>
       <c r="T384" s="49"/>
       <c r="U384" s="49"/>
       <c r="V384" s="49"/>
     </row>
-    <row r="385" spans="19:22">
+    <row r="385" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S385" s="49"/>
       <c r="T385" s="49"/>
       <c r="U385" s="49"/>
       <c r="V385" s="49"/>
     </row>
-    <row r="386" spans="19:22">
+    <row r="386" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S386" s="49"/>
       <c r="T386" s="49"/>
       <c r="U386" s="49"/>
       <c r="V386" s="49"/>
     </row>
-    <row r="387" spans="19:22">
+    <row r="387" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S387" s="49"/>
       <c r="T387" s="49"/>
       <c r="U387" s="49"/>
       <c r="V387" s="49"/>
     </row>
-    <row r="388" spans="19:22">
+    <row r="388" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S388" s="49"/>
       <c r="T388" s="49"/>
       <c r="U388" s="49"/>
       <c r="V388" s="49"/>
     </row>
-    <row r="389" spans="19:22">
+    <row r="389" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S389" s="49"/>
       <c r="T389" s="49"/>
       <c r="U389" s="49"/>
       <c r="V389" s="49"/>
     </row>
-    <row r="390" spans="19:22">
+    <row r="390" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S390" s="49"/>
       <c r="T390" s="49"/>
       <c r="U390" s="49"/>
       <c r="V390" s="49"/>
     </row>
-    <row r="391" spans="19:22">
+    <row r="391" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S391" s="49"/>
       <c r="T391" s="49"/>
       <c r="U391" s="49"/>
       <c r="V391" s="49"/>
     </row>
-    <row r="392" spans="19:22">
+    <row r="392" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S392" s="49"/>
       <c r="T392" s="49"/>
       <c r="U392" s="49"/>
       <c r="V392" s="49"/>
     </row>
-    <row r="393" spans="19:22">
+    <row r="393" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S393" s="49"/>
       <c r="T393" s="49"/>
       <c r="U393" s="49"/>
       <c r="V393" s="49"/>
     </row>
-    <row r="394" spans="19:22">
+    <row r="394" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S394" s="49"/>
       <c r="T394" s="49"/>
       <c r="U394" s="49"/>
       <c r="V394" s="49"/>
     </row>
-    <row r="395" spans="19:22">
+    <row r="395" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S395" s="49"/>
       <c r="T395" s="49"/>
       <c r="U395" s="49"/>
       <c r="V395" s="49"/>
     </row>
-    <row r="396" spans="19:22">
+    <row r="396" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S396" s="49"/>
       <c r="T396" s="49"/>
       <c r="U396" s="49"/>
       <c r="V396" s="49"/>
     </row>
-    <row r="397" spans="19:22">
+    <row r="397" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S397" s="49"/>
       <c r="T397" s="49"/>
       <c r="U397" s="49"/>
       <c r="V397" s="49"/>
     </row>
-    <row r="398" spans="19:22">
+    <row r="398" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S398" s="49"/>
       <c r="T398" s="49"/>
       <c r="U398" s="49"/>
       <c r="V398" s="49"/>
     </row>
-    <row r="399" spans="19:22">
+    <row r="399" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S399" s="49"/>
       <c r="T399" s="49"/>
       <c r="U399" s="49"/>
       <c r="V399" s="49"/>
     </row>
-    <row r="400" spans="19:22">
+    <row r="400" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S400" s="49"/>
       <c r="T400" s="49"/>
       <c r="U400" s="49"/>
       <c r="V400" s="49"/>
     </row>
-    <row r="401" spans="19:22">
+    <row r="401" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S401" s="49"/>
       <c r="T401" s="49"/>
       <c r="U401" s="49"/>
       <c r="V401" s="49"/>
     </row>
-    <row r="402" spans="19:22">
+    <row r="402" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S402" s="49"/>
       <c r="T402" s="49"/>
       <c r="U402" s="49"/>
       <c r="V402" s="49"/>
     </row>
-    <row r="403" spans="19:22">
+    <row r="403" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S403" s="49"/>
       <c r="T403" s="49"/>
       <c r="U403" s="49"/>
       <c r="V403" s="49"/>
     </row>
-    <row r="404" spans="19:22">
+    <row r="404" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S404" s="49"/>
       <c r="T404" s="49"/>
       <c r="U404" s="49"/>
       <c r="V404" s="49"/>
     </row>
-    <row r="405" spans="19:22">
+    <row r="405" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S405" s="49"/>
       <c r="T405" s="49"/>
       <c r="U405" s="49"/>
       <c r="V405" s="49"/>
     </row>
-    <row r="406" spans="19:22">
+    <row r="406" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S406" s="49"/>
       <c r="T406" s="49"/>
       <c r="U406" s="49"/>
       <c r="V406" s="49"/>
     </row>
-    <row r="407" spans="19:22">
+    <row r="407" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S407" s="49"/>
       <c r="T407" s="49"/>
       <c r="U407" s="49"/>
       <c r="V407" s="49"/>
     </row>
-    <row r="408" spans="19:22">
+    <row r="408" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S408" s="49"/>
       <c r="T408" s="49"/>
       <c r="U408" s="49"/>
       <c r="V408" s="49"/>
     </row>
-    <row r="409" spans="19:22">
+    <row r="409" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S409" s="49"/>
       <c r="T409" s="49"/>
       <c r="U409" s="49"/>
       <c r="V409" s="49"/>
     </row>
-    <row r="410" spans="19:22">
+    <row r="410" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S410" s="49"/>
       <c r="T410" s="49"/>
       <c r="U410" s="49"/>
       <c r="V410" s="49"/>
     </row>
-    <row r="411" spans="19:22">
+    <row r="411" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S411" s="49"/>
       <c r="T411" s="49"/>
       <c r="U411" s="49"/>
       <c r="V411" s="49"/>
     </row>
-    <row r="412" spans="19:22">
+    <row r="412" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S412" s="49"/>
       <c r="T412" s="49"/>
       <c r="U412" s="49"/>
       <c r="V412" s="49"/>
     </row>
-    <row r="413" spans="19:22">
+    <row r="413" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S413" s="49"/>
       <c r="T413" s="49"/>
       <c r="U413" s="49"/>
       <c r="V413" s="49"/>
     </row>
-    <row r="414" spans="19:22">
+    <row r="414" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S414" s="49"/>
       <c r="T414" s="49"/>
       <c r="U414" s="49"/>
       <c r="V414" s="49"/>
     </row>
-    <row r="415" spans="19:22">
+    <row r="415" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S415" s="49"/>
       <c r="T415" s="49"/>
       <c r="U415" s="49"/>
       <c r="V415" s="49"/>
     </row>
-    <row r="416" spans="19:22">
+    <row r="416" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S416" s="49"/>
       <c r="T416" s="49"/>
       <c r="U416" s="49"/>
       <c r="V416" s="49"/>
     </row>
-    <row r="417" spans="19:22">
+    <row r="417" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S417" s="49"/>
       <c r="T417" s="49"/>
       <c r="U417" s="49"/>
       <c r="V417" s="49"/>
     </row>
-    <row r="418" spans="19:22">
+    <row r="418" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S418" s="49"/>
       <c r="T418" s="49"/>
       <c r="U418" s="49"/>
       <c r="V418" s="49"/>
     </row>
-    <row r="419" spans="19:22">
+    <row r="419" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S419" s="49"/>
       <c r="T419" s="49"/>
       <c r="U419" s="49"/>
       <c r="V419" s="49"/>
     </row>
-    <row r="420" spans="19:22">
+    <row r="420" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S420" s="49"/>
       <c r="T420" s="49"/>
       <c r="U420" s="49"/>
       <c r="V420" s="49"/>
     </row>
-    <row r="421" spans="19:22">
+    <row r="421" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S421" s="49"/>
       <c r="T421" s="49"/>
       <c r="U421" s="49"/>
       <c r="V421" s="49"/>
     </row>
-    <row r="422" spans="19:22">
+    <row r="422" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S422" s="49"/>
       <c r="T422" s="49"/>
       <c r="U422" s="49"/>
       <c r="V422" s="49"/>
     </row>
-    <row r="423" spans="19:22">
+    <row r="423" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S423" s="49"/>
       <c r="T423" s="49"/>
       <c r="U423" s="49"/>
       <c r="V423" s="49"/>
     </row>
-    <row r="424" spans="19:22">
+    <row r="424" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S424" s="49"/>
       <c r="T424" s="49"/>
       <c r="U424" s="49"/>
       <c r="V424" s="49"/>
     </row>
-    <row r="425" spans="19:22">
+    <row r="425" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S425" s="49"/>
       <c r="T425" s="49"/>
       <c r="U425" s="49"/>
       <c r="V425" s="49"/>
     </row>
-    <row r="426" spans="19:22">
+    <row r="426" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S426" s="49"/>
       <c r="T426" s="49"/>
       <c r="U426" s="49"/>
       <c r="V426" s="49"/>
     </row>
-    <row r="427" spans="19:22">
+    <row r="427" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S427" s="49"/>
       <c r="T427" s="49"/>
       <c r="U427" s="49"/>
       <c r="V427" s="49"/>
     </row>
-    <row r="428" spans="19:22">
+    <row r="428" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S428" s="49"/>
       <c r="T428" s="49"/>
       <c r="U428" s="49"/>
       <c r="V428" s="49"/>
     </row>
-    <row r="429" spans="19:22">
+    <row r="429" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S429" s="49"/>
       <c r="T429" s="49"/>
       <c r="U429" s="49"/>
       <c r="V429" s="49"/>
     </row>
-    <row r="430" spans="19:22">
+    <row r="430" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S430" s="49"/>
       <c r="T430" s="49"/>
       <c r="U430" s="49"/>
       <c r="V430" s="49"/>
     </row>
-    <row r="431" spans="19:22">
+    <row r="431" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S431" s="49"/>
       <c r="T431" s="49"/>
       <c r="U431" s="49"/>
       <c r="V431" s="49"/>
     </row>
-    <row r="432" spans="19:22">
+    <row r="432" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S432" s="49"/>
       <c r="T432" s="49"/>
       <c r="U432" s="49"/>
       <c r="V432" s="49"/>
     </row>
-    <row r="433" spans="19:22">
+    <row r="433" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S433" s="49"/>
       <c r="T433" s="49"/>
       <c r="U433" s="49"/>
       <c r="V433" s="49"/>
     </row>
-    <row r="434" spans="19:22">
+    <row r="434" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S434" s="49"/>
       <c r="T434" s="49"/>
       <c r="U434" s="49"/>
       <c r="V434" s="49"/>
     </row>
-    <row r="435" spans="19:22">
+    <row r="435" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S435" s="49"/>
       <c r="T435" s="49"/>
       <c r="U435" s="49"/>
       <c r="V435" s="49"/>
     </row>
-    <row r="436" spans="19:22">
+    <row r="436" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S436" s="49"/>
       <c r="T436" s="49"/>
       <c r="U436" s="49"/>
       <c r="V436" s="49"/>
     </row>
-    <row r="437" spans="19:22">
+    <row r="437" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S437" s="49"/>
       <c r="T437" s="49"/>
       <c r="U437" s="49"/>
       <c r="V437" s="49"/>
     </row>
-    <row r="438" spans="19:22">
+    <row r="438" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S438" s="49"/>
       <c r="T438" s="49"/>
       <c r="U438" s="49"/>
       <c r="V438" s="49"/>
     </row>
-    <row r="439" spans="19:22">
+    <row r="439" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S439" s="49"/>
       <c r="T439" s="49"/>
       <c r="U439" s="49"/>
       <c r="V439" s="49"/>
     </row>
-    <row r="440" spans="19:22">
+    <row r="440" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S440" s="49"/>
       <c r="T440" s="49"/>
       <c r="U440" s="49"/>
       <c r="V440" s="49"/>
     </row>
-    <row r="441" spans="19:22">
+    <row r="441" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S441" s="49"/>
       <c r="T441" s="49"/>
       <c r="U441" s="49"/>
       <c r="V441" s="49"/>
     </row>
-    <row r="442" spans="19:22">
+    <row r="442" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S442" s="49"/>
       <c r="T442" s="49"/>
       <c r="U442" s="49"/>
       <c r="V442" s="49"/>
     </row>
-    <row r="443" spans="19:22">
+    <row r="443" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S443" s="49"/>
       <c r="T443" s="49"/>
       <c r="U443" s="49"/>
       <c r="V443" s="49"/>
     </row>
-    <row r="444" spans="19:22">
+    <row r="444" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S444" s="49"/>
       <c r="T444" s="49"/>
       <c r="U444" s="49"/>
       <c r="V444" s="49"/>
     </row>
-    <row r="445" spans="19:22">
+    <row r="445" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S445" s="49"/>
       <c r="T445" s="49"/>
       <c r="U445" s="49"/>
       <c r="V445" s="49"/>
     </row>
-    <row r="446" spans="19:22">
+    <row r="446" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S446" s="49"/>
       <c r="T446" s="49"/>
       <c r="U446" s="49"/>
       <c r="V446" s="49"/>
     </row>
-    <row r="447" spans="19:22">
+    <row r="447" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S447" s="49"/>
       <c r="T447" s="49"/>
       <c r="U447" s="49"/>
       <c r="V447" s="49"/>
     </row>
-    <row r="448" spans="19:22">
+    <row r="448" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S448" s="49"/>
       <c r="T448" s="49"/>
       <c r="U448" s="49"/>
       <c r="V448" s="49"/>
     </row>
-    <row r="449" spans="19:22">
+    <row r="449" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S449" s="49"/>
       <c r="T449" s="49"/>
       <c r="U449" s="49"/>
       <c r="V449" s="49"/>
     </row>
-    <row r="450" spans="19:22">
+    <row r="450" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S450" s="49"/>
       <c r="T450" s="49"/>
       <c r="U450" s="49"/>
       <c r="V450" s="49"/>
     </row>
-    <row r="451" spans="19:22">
+    <row r="451" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S451" s="49"/>
       <c r="T451" s="49"/>
       <c r="U451" s="49"/>
       <c r="V451" s="49"/>
     </row>
-    <row r="452" spans="19:22">
+    <row r="452" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S452" s="49"/>
       <c r="T452" s="49"/>
       <c r="U452" s="49"/>
       <c r="V452" s="49"/>
     </row>
-    <row r="453" spans="19:22">
+    <row r="453" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S453" s="49"/>
       <c r="T453" s="49"/>
       <c r="U453" s="49"/>
       <c r="V453" s="49"/>
     </row>
-    <row r="454" spans="19:22">
+    <row r="454" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S454" s="49"/>
       <c r="T454" s="49"/>
       <c r="U454" s="49"/>
       <c r="V454" s="49"/>
     </row>
-    <row r="455" spans="19:22">
+    <row r="455" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S455" s="49"/>
       <c r="T455" s="49"/>
       <c r="U455" s="49"/>
       <c r="V455" s="49"/>
     </row>
-    <row r="456" spans="19:22">
+    <row r="456" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S456" s="49"/>
       <c r="T456" s="49"/>
       <c r="U456" s="49"/>
       <c r="V456" s="49"/>
     </row>
-    <row r="457" spans="19:22">
+    <row r="457" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S457" s="49"/>
       <c r="T457" s="49"/>
       <c r="U457" s="49"/>
       <c r="V457" s="49"/>
     </row>
-    <row r="458" spans="19:22">
+    <row r="458" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S458" s="49"/>
       <c r="T458" s="49"/>
       <c r="U458" s="49"/>
       <c r="V458" s="49"/>
     </row>
-    <row r="459" spans="19:22">
+    <row r="459" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S459" s="49"/>
       <c r="T459" s="49"/>
       <c r="U459" s="49"/>
       <c r="V459" s="49"/>
     </row>
-    <row r="460" spans="19:22">
+    <row r="460" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S460" s="49"/>
       <c r="T460" s="49"/>
       <c r="U460" s="49"/>
       <c r="V460" s="49"/>
     </row>
-    <row r="461" spans="19:22">
+    <row r="461" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S461" s="49"/>
       <c r="T461" s="49"/>
       <c r="U461" s="49"/>
       <c r="V461" s="49"/>
     </row>
-    <row r="462" spans="19:22">
+    <row r="462" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S462" s="49"/>
       <c r="T462" s="49"/>
       <c r="U462" s="49"/>
       <c r="V462" s="49"/>
     </row>
-    <row r="463" spans="19:22">
+    <row r="463" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S463" s="49"/>
       <c r="T463" s="49"/>
       <c r="U463" s="49"/>
       <c r="V463" s="49"/>
     </row>
-    <row r="464" spans="19:22">
+    <row r="464" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S464" s="49"/>
       <c r="T464" s="49"/>
       <c r="U464" s="49"/>
       <c r="V464" s="49"/>
     </row>
-    <row r="465" spans="19:22">
+    <row r="465" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S465" s="49"/>
       <c r="T465" s="49"/>
       <c r="U465" s="49"/>
       <c r="V465" s="49"/>
     </row>
-    <row r="466" spans="19:22">
+    <row r="466" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S466" s="49"/>
       <c r="T466" s="49"/>
       <c r="U466" s="49"/>
       <c r="V466" s="49"/>
     </row>
-    <row r="467" spans="19:22">
+    <row r="467" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S467" s="49"/>
       <c r="T467" s="49"/>
       <c r="U467" s="49"/>
       <c r="V467" s="49"/>
     </row>
-    <row r="468" spans="19:22">
+    <row r="468" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S468" s="49"/>
       <c r="T468" s="49"/>
       <c r="U468" s="49"/>
       <c r="V468" s="49"/>
     </row>
-    <row r="469" spans="19:22">
+    <row r="469" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S469" s="49"/>
       <c r="T469" s="49"/>
       <c r="U469" s="49"/>
       <c r="V469" s="49"/>
     </row>
-    <row r="470" spans="19:22">
+    <row r="470" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S470" s="49"/>
       <c r="T470" s="49"/>
       <c r="U470" s="49"/>
       <c r="V470" s="49"/>
     </row>
-    <row r="471" spans="19:22">
+    <row r="471" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S471" s="49"/>
       <c r="T471" s="49"/>
       <c r="U471" s="49"/>
       <c r="V471" s="49"/>
     </row>
-    <row r="472" spans="19:22">
+    <row r="472" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S472" s="49"/>
       <c r="T472" s="49"/>
       <c r="U472" s="49"/>
       <c r="V472" s="49"/>
     </row>
-    <row r="473" spans="19:22">
+    <row r="473" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S473" s="49"/>
       <c r="T473" s="49"/>
       <c r="U473" s="49"/>
       <c r="V473" s="49"/>
     </row>
-    <row r="474" spans="19:22">
+    <row r="474" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S474" s="49"/>
       <c r="T474" s="49"/>
       <c r="U474" s="49"/>
       <c r="V474" s="49"/>
     </row>
-    <row r="475" spans="19:22">
+    <row r="475" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S475" s="49"/>
       <c r="T475" s="49"/>
       <c r="U475" s="49"/>
       <c r="V475" s="49"/>
     </row>
-    <row r="476" spans="19:22">
+    <row r="476" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S476" s="49"/>
       <c r="T476" s="49"/>
       <c r="U476" s="49"/>
       <c r="V476" s="49"/>
     </row>
-    <row r="477" spans="19:22">
+    <row r="477" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S477" s="49"/>
       <c r="T477" s="49"/>
       <c r="U477" s="49"/>
       <c r="V477" s="49"/>
     </row>
-    <row r="478" spans="19:22">
+    <row r="478" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S478" s="49"/>
       <c r="T478" s="49"/>
       <c r="U478" s="49"/>
       <c r="V478" s="49"/>
     </row>
-    <row r="479" spans="19:22">
+    <row r="479" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S479" s="49"/>
       <c r="T479" s="49"/>
       <c r="U479" s="49"/>
       <c r="V479" s="49"/>
     </row>
-    <row r="480" spans="19:22">
+    <row r="480" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S480" s="49"/>
       <c r="T480" s="49"/>
       <c r="U480" s="49"/>
       <c r="V480" s="49"/>
     </row>
-    <row r="481" spans="19:22">
+    <row r="481" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S481" s="49"/>
       <c r="T481" s="49"/>
       <c r="U481" s="49"/>
       <c r="V481" s="49"/>
     </row>
-    <row r="482" spans="19:22">
+    <row r="482" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S482" s="49"/>
       <c r="T482" s="49"/>
       <c r="U482" s="49"/>
       <c r="V482" s="49"/>
     </row>
-    <row r="483" spans="19:22">
+    <row r="483" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S483" s="49"/>
       <c r="T483" s="49"/>
       <c r="U483" s="49"/>
       <c r="V483" s="49"/>
     </row>
-    <row r="484" spans="19:22">
+    <row r="484" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S484" s="49"/>
       <c r="T484" s="49"/>
       <c r="U484" s="49"/>
       <c r="V484" s="49"/>
     </row>
-    <row r="485" spans="19:22">
+    <row r="485" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S485" s="49"/>
       <c r="T485" s="49"/>
       <c r="U485" s="49"/>
       <c r="V485" s="49"/>
     </row>
-    <row r="486" spans="19:22">
+    <row r="486" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S486" s="49"/>
       <c r="T486" s="49"/>
       <c r="U486" s="49"/>
       <c r="V486" s="49"/>
     </row>
-    <row r="487" spans="19:22">
+    <row r="487" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S487" s="49"/>
       <c r="T487" s="49"/>
       <c r="U487" s="49"/>
       <c r="V487" s="49"/>
     </row>
-    <row r="488" spans="19:22">
+    <row r="488" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S488" s="49"/>
       <c r="T488" s="49"/>
       <c r="U488" s="49"/>
       <c r="V488" s="49"/>
     </row>
-    <row r="489" spans="19:22">
+    <row r="489" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S489" s="49"/>
       <c r="T489" s="49"/>
       <c r="U489" s="49"/>
       <c r="V489" s="49"/>
     </row>
-    <row r="490" spans="19:22">
+    <row r="490" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S490" s="49"/>
       <c r="T490" s="49"/>
       <c r="U490" s="49"/>
       <c r="V490" s="49"/>
     </row>
-    <row r="491" spans="19:22">
+    <row r="491" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S491" s="49"/>
       <c r="T491" s="49"/>
       <c r="U491" s="49"/>
       <c r="V491" s="49"/>
     </row>
-    <row r="492" spans="19:22">
+    <row r="492" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S492" s="49"/>
       <c r="T492" s="49"/>
       <c r="U492" s="49"/>
       <c r="V492" s="49"/>
     </row>
-    <row r="493" spans="19:22">
+    <row r="493" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S493" s="49"/>
       <c r="T493" s="49"/>
       <c r="U493" s="49"/>
       <c r="V493" s="49"/>
     </row>
-    <row r="494" spans="19:22">
+    <row r="494" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S494" s="49"/>
       <c r="T494" s="49"/>
       <c r="U494" s="49"/>
       <c r="V494" s="49"/>
     </row>
-    <row r="495" spans="19:22">
+    <row r="495" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S495" s="49"/>
       <c r="T495" s="49"/>
       <c r="U495" s="49"/>
       <c r="V495" s="49"/>
     </row>
-    <row r="496" spans="19:22">
+    <row r="496" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S496" s="49"/>
       <c r="T496" s="49"/>
       <c r="U496" s="49"/>
       <c r="V496" s="49"/>
     </row>
-    <row r="497" spans="19:22">
+    <row r="497" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S497" s="49"/>
       <c r="T497" s="49"/>
       <c r="U497" s="49"/>
       <c r="V497" s="49"/>
     </row>
-    <row r="498" spans="19:22">
+    <row r="498" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S498" s="49"/>
       <c r="T498" s="49"/>
       <c r="U498" s="49"/>
       <c r="V498" s="49"/>
     </row>
-    <row r="499" spans="19:22">
+    <row r="499" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S499" s="49"/>
       <c r="T499" s="49"/>
       <c r="U499" s="49"/>
       <c r="V499" s="49"/>
     </row>
-    <row r="500" spans="19:22">
+    <row r="500" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S500" s="49"/>
       <c r="T500" s="49"/>
       <c r="U500" s="49"/>
       <c r="V500" s="49"/>
     </row>
-    <row r="501" spans="19:22">
+    <row r="501" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S501" s="49"/>
       <c r="T501" s="49"/>
       <c r="U501" s="49"/>
       <c r="V501" s="49"/>
     </row>
-    <row r="502" spans="19:22">
+    <row r="502" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S502" s="49"/>
       <c r="T502" s="49"/>
       <c r="U502" s="49"/>
       <c r="V502" s="49"/>
     </row>
-    <row r="503" spans="19:22">
+    <row r="503" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S503" s="49"/>
       <c r="T503" s="49"/>
       <c r="U503" s="49"/>
       <c r="V503" s="49"/>
     </row>
-    <row r="504" spans="19:22">
+    <row r="504" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S504" s="49"/>
       <c r="T504" s="49"/>
       <c r="U504" s="49"/>
       <c r="V504" s="49"/>
     </row>
-    <row r="505" spans="19:22">
+    <row r="505" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S505" s="49"/>
       <c r="T505" s="49"/>
       <c r="U505" s="49"/>
       <c r="V505" s="49"/>
     </row>
-    <row r="506" spans="19:22">
+    <row r="506" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S506" s="49"/>
       <c r="T506" s="49"/>
       <c r="U506" s="49"/>
       <c r="V506" s="49"/>
     </row>
-    <row r="507" spans="19:22">
+    <row r="507" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S507" s="49"/>
       <c r="T507" s="49"/>
       <c r="U507" s="49"/>
       <c r="V507" s="49"/>
     </row>
-    <row r="508" spans="19:22">
+    <row r="508" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S508" s="49"/>
       <c r="T508" s="49"/>
       <c r="U508" s="49"/>
       <c r="V508" s="49"/>
     </row>
-    <row r="509" spans="19:22">
+    <row r="509" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S509" s="49"/>
       <c r="T509" s="49"/>
       <c r="U509" s="49"/>
       <c r="V509" s="49"/>
     </row>
-    <row r="510" spans="19:22">
+    <row r="510" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S510" s="49"/>
       <c r="T510" s="49"/>
       <c r="U510" s="49"/>
       <c r="V510" s="49"/>
     </row>
-    <row r="511" spans="19:22">
+    <row r="511" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S511" s="49"/>
       <c r="T511" s="49"/>
       <c r="U511" s="49"/>
       <c r="V511" s="49"/>
     </row>
-    <row r="512" spans="19:22">
+    <row r="512" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S512" s="49"/>
       <c r="T512" s="49"/>
       <c r="U512" s="49"/>
       <c r="V512" s="49"/>
     </row>
-    <row r="513" spans="19:22">
+    <row r="513" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S513" s="49"/>
       <c r="T513" s="49"/>
       <c r="U513" s="49"/>
       <c r="V513" s="49"/>
     </row>
-    <row r="514" spans="19:22">
+    <row r="514" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S514" s="49"/>
       <c r="T514" s="49"/>
       <c r="U514" s="49"/>
       <c r="V514" s="49"/>
     </row>
-    <row r="515" spans="19:22">
+    <row r="515" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S515" s="49"/>
       <c r="T515" s="49"/>
       <c r="U515" s="49"/>
       <c r="V515" s="49"/>
     </row>
-    <row r="516" spans="19:22">
+    <row r="516" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S516" s="49"/>
       <c r="T516" s="49"/>
       <c r="U516" s="49"/>
       <c r="V516" s="49"/>
     </row>
-    <row r="517" spans="19:22">
+    <row r="517" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S517" s="49"/>
       <c r="T517" s="49"/>
       <c r="U517" s="49"/>
       <c r="V517" s="49"/>
     </row>
-    <row r="518" spans="19:22">
+    <row r="518" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S518" s="49"/>
       <c r="T518" s="49"/>
       <c r="U518" s="49"/>
       <c r="V518" s="49"/>
     </row>
-    <row r="519" spans="19:22">
+    <row r="519" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S519" s="49"/>
       <c r="T519" s="49"/>
       <c r="U519" s="49"/>
       <c r="V519" s="49"/>
     </row>
-    <row r="520" spans="19:22">
+    <row r="520" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S520" s="49"/>
       <c r="T520" s="49"/>
       <c r="U520" s="49"/>
       <c r="V520" s="49"/>
     </row>
-    <row r="521" spans="19:22">
+    <row r="521" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S521" s="49"/>
       <c r="T521" s="49"/>
       <c r="U521" s="49"/>
       <c r="V521" s="49"/>
     </row>
-    <row r="522" spans="19:22">
+    <row r="522" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S522" s="49"/>
       <c r="T522" s="49"/>
       <c r="U522" s="49"/>
       <c r="V522" s="49"/>
     </row>
-    <row r="523" spans="19:22">
+    <row r="523" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S523" s="49"/>
       <c r="T523" s="49"/>
       <c r="U523" s="49"/>
       <c r="V523" s="49"/>
     </row>
-    <row r="524" spans="19:22">
+    <row r="524" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S524" s="49"/>
       <c r="T524" s="49"/>
       <c r="U524" s="49"/>
       <c r="V524" s="49"/>
     </row>
-    <row r="525" spans="19:22">
+    <row r="525" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S525" s="49"/>
       <c r="T525" s="49"/>
       <c r="U525" s="49"/>
       <c r="V525" s="49"/>
     </row>
-    <row r="526" spans="19:22">
+    <row r="526" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S526" s="49"/>
       <c r="T526" s="49"/>
       <c r="U526" s="49"/>
       <c r="V526" s="49"/>
     </row>
-    <row r="527" spans="19:22">
+    <row r="527" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S527" s="49"/>
       <c r="T527" s="49"/>
       <c r="U527" s="49"/>
       <c r="V527" s="49"/>
     </row>
-    <row r="528" spans="19:22">
+    <row r="528" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S528" s="49"/>
       <c r="T528" s="49"/>
       <c r="U528" s="49"/>
       <c r="V528" s="49"/>
     </row>
-    <row r="529" spans="19:22">
+    <row r="529" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S529" s="49"/>
       <c r="T529" s="49"/>
       <c r="U529" s="49"/>
       <c r="V529" s="49"/>
     </row>
-    <row r="530" spans="19:22">
+    <row r="530" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S530" s="49"/>
       <c r="T530" s="49"/>
       <c r="U530" s="49"/>
       <c r="V530" s="49"/>
     </row>
-    <row r="531" spans="19:22">
+    <row r="531" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S531" s="49"/>
       <c r="T531" s="49"/>
       <c r="U531" s="49"/>
       <c r="V531" s="49"/>
     </row>
-    <row r="532" spans="19:22">
+    <row r="532" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S532" s="49"/>
       <c r="T532" s="49"/>
       <c r="U532" s="49"/>
       <c r="V532" s="49"/>
     </row>
-    <row r="533" spans="19:22">
+    <row r="533" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S533" s="49"/>
       <c r="T533" s="49"/>
       <c r="U533" s="49"/>
       <c r="V533" s="49"/>
     </row>
-    <row r="534" spans="19:22">
+    <row r="534" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S534" s="49"/>
       <c r="T534" s="49"/>
       <c r="U534" s="49"/>
       <c r="V534" s="49"/>
     </row>
-    <row r="535" spans="19:22">
+    <row r="535" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S535" s="49"/>
       <c r="T535" s="49"/>
       <c r="U535" s="49"/>
       <c r="V535" s="49"/>
     </row>
-    <row r="536" spans="19:22">
+    <row r="536" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S536" s="49"/>
       <c r="T536" s="49"/>
       <c r="U536" s="49"/>
       <c r="V536" s="49"/>
     </row>
-    <row r="537" spans="19:22">
+    <row r="537" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S537" s="49"/>
       <c r="T537" s="49"/>
       <c r="U537" s="49"/>
       <c r="V537" s="49"/>
     </row>
-    <row r="538" spans="19:22">
+    <row r="538" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S538" s="49"/>
       <c r="T538" s="49"/>
       <c r="U538" s="49"/>
       <c r="V538" s="49"/>
     </row>
-    <row r="539" spans="19:22">
+    <row r="539" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S539" s="49"/>
       <c r="T539" s="49"/>
       <c r="U539" s="49"/>
       <c r="V539" s="49"/>
     </row>
-    <row r="540" spans="19:22">
+    <row r="540" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S540" s="49"/>
       <c r="T540" s="49"/>
       <c r="U540" s="49"/>
       <c r="V540" s="49"/>
     </row>
-    <row r="541" spans="19:22">
+    <row r="541" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S541" s="49"/>
       <c r="T541" s="49"/>
       <c r="U541" s="49"/>
       <c r="V541" s="49"/>
     </row>
-    <row r="542" spans="19:22">
+    <row r="542" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S542" s="49"/>
       <c r="T542" s="49"/>
       <c r="U542" s="49"/>
       <c r="V542" s="49"/>
     </row>
-    <row r="543" spans="19:22">
+    <row r="543" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S543" s="49"/>
       <c r="T543" s="49"/>
       <c r="U543" s="49"/>
       <c r="V543" s="49"/>
     </row>
-    <row r="544" spans="19:22">
+    <row r="544" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S544" s="49"/>
       <c r="T544" s="49"/>
       <c r="U544" s="49"/>
       <c r="V544" s="49"/>
     </row>
-    <row r="545" spans="19:22">
+    <row r="545" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S545" s="49"/>
       <c r="T545" s="49"/>
       <c r="U545" s="49"/>
       <c r="V545" s="49"/>
     </row>
-    <row r="546" spans="19:22">
+    <row r="546" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S546" s="49"/>
       <c r="T546" s="49"/>
       <c r="U546" s="49"/>
       <c r="V546" s="49"/>
     </row>
-    <row r="547" spans="19:22">
+    <row r="547" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S547" s="49"/>
       <c r="T547" s="49"/>
       <c r="U547" s="49"/>
       <c r="V547" s="49"/>
     </row>
-    <row r="548" spans="19:22">
+    <row r="548" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S548" s="49"/>
       <c r="T548" s="49"/>
       <c r="U548" s="49"/>
       <c r="V548" s="49"/>
     </row>
-    <row r="549" spans="19:22">
+    <row r="549" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S549" s="49"/>
       <c r="T549" s="49"/>
       <c r="U549" s="49"/>
       <c r="V549" s="49"/>
     </row>
-    <row r="550" spans="19:22">
+    <row r="550" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S550" s="49"/>
       <c r="T550" s="49"/>
       <c r="U550" s="49"/>
       <c r="V550" s="49"/>
     </row>
-    <row r="551" spans="19:22">
+    <row r="551" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S551" s="49"/>
       <c r="T551" s="49"/>
       <c r="U551" s="49"/>
       <c r="V551" s="49"/>
     </row>
-    <row r="552" spans="19:22">
+    <row r="552" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S552" s="49"/>
       <c r="T552" s="49"/>
       <c r="U552" s="49"/>
       <c r="V552" s="49"/>
     </row>
-    <row r="553" spans="19:22">
+    <row r="553" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S553" s="49"/>
       <c r="T553" s="49"/>
       <c r="U553" s="49"/>
       <c r="V553" s="49"/>
     </row>
-    <row r="554" spans="19:22">
+    <row r="554" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S554" s="49"/>
       <c r="T554" s="49"/>
       <c r="U554" s="49"/>
       <c r="V554" s="49"/>
     </row>
-    <row r="555" spans="19:22">
+    <row r="555" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S555" s="49"/>
       <c r="T555" s="49"/>
       <c r="U555" s="49"/>
       <c r="V555" s="49"/>
     </row>
-    <row r="556" spans="19:22">
+    <row r="556" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S556" s="49"/>
       <c r="T556" s="49"/>
       <c r="U556" s="49"/>
       <c r="V556" s="49"/>
     </row>
-    <row r="557" spans="19:22">
+    <row r="557" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S557" s="49"/>
       <c r="T557" s="49"/>
       <c r="U557" s="49"/>
       <c r="V557" s="49"/>
     </row>
-    <row r="558" spans="19:22">
+    <row r="558" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S558" s="49"/>
       <c r="T558" s="49"/>
       <c r="U558" s="49"/>
       <c r="V558" s="49"/>
     </row>
-    <row r="559" spans="19:22">
+    <row r="559" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S559" s="49"/>
       <c r="T559" s="49"/>
       <c r="U559" s="49"/>
       <c r="V559" s="49"/>
     </row>
-    <row r="560" spans="19:22">
+    <row r="560" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S560" s="49"/>
       <c r="T560" s="49"/>
       <c r="U560" s="49"/>
       <c r="V560" s="49"/>
     </row>
-    <row r="561" spans="19:22">
+    <row r="561" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S561" s="49"/>
       <c r="T561" s="49"/>
       <c r="U561" s="49"/>
       <c r="V561" s="49"/>
     </row>
-    <row r="562" spans="19:22">
+    <row r="562" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S562" s="49"/>
       <c r="T562" s="49"/>
       <c r="U562" s="49"/>
       <c r="V562" s="49"/>
     </row>
-    <row r="563" spans="19:22">
+    <row r="563" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S563" s="49"/>
       <c r="T563" s="49"/>
       <c r="U563" s="49"/>
       <c r="V563" s="49"/>
     </row>
-    <row r="564" spans="19:22">
+    <row r="564" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S564" s="49"/>
       <c r="T564" s="49"/>
       <c r="U564" s="49"/>
       <c r="V564" s="49"/>
     </row>
-    <row r="565" spans="19:22">
+    <row r="565" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S565" s="49"/>
       <c r="T565" s="49"/>
       <c r="U565" s="49"/>
       <c r="V565" s="49"/>
     </row>
-    <row r="566" spans="19:22">
+    <row r="566" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S566" s="49"/>
       <c r="T566" s="49"/>
       <c r="U566" s="49"/>
       <c r="V566" s="49"/>
     </row>
-    <row r="567" spans="19:22">
+    <row r="567" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S567" s="49"/>
       <c r="T567" s="49"/>
       <c r="U567" s="49"/>
       <c r="V567" s="49"/>
     </row>
-    <row r="568" spans="19:22">
+    <row r="568" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S568" s="49"/>
       <c r="T568" s="49"/>
       <c r="U568" s="49"/>
       <c r="V568" s="49"/>
     </row>
-    <row r="569" spans="19:22">
+    <row r="569" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S569" s="49"/>
       <c r="T569" s="49"/>
       <c r="U569" s="49"/>
       <c r="V569" s="49"/>
     </row>
-    <row r="570" spans="19:22">
+    <row r="570" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S570" s="49"/>
       <c r="T570" s="49"/>
       <c r="U570" s="49"/>
       <c r="V570" s="49"/>
     </row>
-    <row r="571" spans="19:22">
+    <row r="571" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S571" s="49"/>
       <c r="T571" s="49"/>
       <c r="U571" s="49"/>
       <c r="V571" s="49"/>
     </row>
-    <row r="572" spans="19:22">
+    <row r="572" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S572" s="49"/>
       <c r="T572" s="49"/>
       <c r="U572" s="49"/>
       <c r="V572" s="49"/>
     </row>
-    <row r="573" spans="19:22">
+    <row r="573" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S573" s="49"/>
       <c r="T573" s="49"/>
       <c r="U573" s="49"/>
       <c r="V573" s="49"/>
     </row>
-    <row r="574" spans="19:22">
+    <row r="574" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S574" s="49"/>
       <c r="T574" s="49"/>
       <c r="U574" s="49"/>
       <c r="V574" s="49"/>
     </row>
-    <row r="575" spans="19:22">
+    <row r="575" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S575" s="49"/>
       <c r="T575" s="49"/>
       <c r="U575" s="49"/>
       <c r="V575" s="49"/>
     </row>
-    <row r="576" spans="19:22">
+    <row r="576" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S576" s="49"/>
       <c r="T576" s="49"/>
       <c r="U576" s="49"/>
       <c r="V576" s="49"/>
     </row>
-    <row r="577" spans="19:22">
+    <row r="577" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S577" s="49"/>
       <c r="T577" s="49"/>
       <c r="U577" s="49"/>
       <c r="V577" s="49"/>
     </row>
-    <row r="578" spans="19:22">
+    <row r="578" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S578" s="49"/>
       <c r="T578" s="49"/>
       <c r="U578" s="49"/>
       <c r="V578" s="49"/>
     </row>
-    <row r="579" spans="19:22">
+    <row r="579" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S579" s="49"/>
       <c r="T579" s="49"/>
       <c r="U579" s="49"/>
       <c r="V579" s="49"/>
     </row>
-    <row r="580" spans="19:22">
+    <row r="580" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S580" s="49"/>
       <c r="T580" s="49"/>
       <c r="U580" s="49"/>
       <c r="V580" s="49"/>
     </row>
-    <row r="581" spans="19:22">
+    <row r="581" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S581" s="49"/>
       <c r="T581" s="49"/>
       <c r="U581" s="49"/>
       <c r="V581" s="49"/>
     </row>
-    <row r="582" spans="19:22">
+    <row r="582" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S582" s="49"/>
       <c r="T582" s="49"/>
       <c r="U582" s="49"/>
       <c r="V582" s="49"/>
     </row>
-    <row r="583" spans="19:22">
+    <row r="583" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S583" s="49"/>
       <c r="T583" s="49"/>
       <c r="U583" s="49"/>
       <c r="V583" s="49"/>
     </row>
-    <row r="584" spans="19:22">
+    <row r="584" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S584" s="49"/>
       <c r="T584" s="49"/>
       <c r="U584" s="49"/>
       <c r="V584" s="49"/>
     </row>
-    <row r="585" spans="19:22">
+    <row r="585" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S585" s="49"/>
       <c r="T585" s="49"/>
       <c r="U585" s="49"/>
       <c r="V585" s="49"/>
     </row>
-    <row r="586" spans="19:22">
+    <row r="586" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S586" s="49"/>
       <c r="T586" s="49"/>
       <c r="U586" s="49"/>
       <c r="V586" s="49"/>
     </row>
-    <row r="587" spans="19:22">
+    <row r="587" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S587" s="49"/>
       <c r="T587" s="49"/>
       <c r="U587" s="49"/>
       <c r="V587" s="49"/>
     </row>
-    <row r="588" spans="19:22">
+    <row r="588" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S588" s="49"/>
       <c r="T588" s="49"/>
       <c r="U588" s="49"/>
       <c r="V588" s="49"/>
     </row>
-    <row r="589" spans="19:22">
+    <row r="589" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S589" s="49"/>
       <c r="T589" s="49"/>
       <c r="U589" s="49"/>
       <c r="V589" s="49"/>
     </row>
-    <row r="590" spans="19:22">
+    <row r="590" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S590" s="49"/>
       <c r="T590" s="49"/>
       <c r="U590" s="49"/>
       <c r="V590" s="49"/>
     </row>
-    <row r="591" spans="19:22">
+    <row r="591" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S591" s="49"/>
       <c r="T591" s="49"/>
       <c r="U591" s="49"/>
       <c r="V591" s="49"/>
     </row>
-    <row r="592" spans="19:22">
+    <row r="592" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S592" s="49"/>
       <c r="T592" s="49"/>
       <c r="U592" s="49"/>
       <c r="V592" s="49"/>
     </row>
-    <row r="593" spans="19:22">
+    <row r="593" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S593" s="49"/>
       <c r="T593" s="49"/>
       <c r="U593" s="49"/>
       <c r="V593" s="49"/>
     </row>
-    <row r="594" spans="19:22">
+    <row r="594" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S594" s="49"/>
       <c r="T594" s="49"/>
       <c r="U594" s="49"/>
       <c r="V594" s="49"/>
     </row>
-    <row r="595" spans="19:22">
+    <row r="595" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S595" s="49"/>
       <c r="T595" s="49"/>
       <c r="U595" s="49"/>
       <c r="V595" s="49"/>
     </row>
-    <row r="596" spans="19:22">
+    <row r="596" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S596" s="49"/>
       <c r="T596" s="49"/>
       <c r="U596" s="49"/>
       <c r="V596" s="49"/>
     </row>
-    <row r="597" spans="19:22">
+    <row r="597" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S597" s="49"/>
       <c r="T597" s="49"/>
       <c r="U597" s="49"/>
       <c r="V597" s="49"/>
     </row>
-    <row r="598" spans="19:22">
+    <row r="598" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S598" s="49"/>
       <c r="T598" s="49"/>
       <c r="U598" s="49"/>
       <c r="V598" s="49"/>
     </row>
-    <row r="599" spans="19:22">
+    <row r="599" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S599" s="49"/>
       <c r="T599" s="49"/>
       <c r="U599" s="49"/>
       <c r="V599" s="49"/>
     </row>
-    <row r="600" spans="19:22">
+    <row r="600" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S600" s="49"/>
       <c r="T600" s="49"/>
       <c r="U600" s="49"/>
       <c r="V600" s="49"/>
     </row>
-    <row r="601" spans="19:22">
+    <row r="601" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S601" s="49"/>
       <c r="T601" s="49"/>
       <c r="U601" s="49"/>
       <c r="V601" s="49"/>
     </row>
-    <row r="602" spans="19:22">
+    <row r="602" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S602" s="49"/>
       <c r="T602" s="49"/>
       <c r="U602" s="49"/>
       <c r="V602" s="49"/>
     </row>
-    <row r="603" spans="19:22">
+    <row r="603" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S603" s="49"/>
       <c r="T603" s="49"/>
       <c r="U603" s="49"/>
       <c r="V603" s="49"/>
     </row>
-    <row r="604" spans="19:22">
+    <row r="604" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S604" s="49"/>
       <c r="T604" s="49"/>
       <c r="U604" s="49"/>
       <c r="V604" s="49"/>
     </row>
-    <row r="605" spans="19:22">
+    <row r="605" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S605" s="49"/>
       <c r="T605" s="49"/>
       <c r="U605" s="49"/>
       <c r="V605" s="49"/>
     </row>
-    <row r="606" spans="19:22">
+    <row r="606" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S606" s="49"/>
       <c r="T606" s="49"/>
       <c r="U606" s="49"/>
       <c r="V606" s="49"/>
     </row>
-    <row r="607" spans="19:22">
+    <row r="607" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S607" s="49"/>
       <c r="T607" s="49"/>
       <c r="U607" s="49"/>
       <c r="V607" s="49"/>
     </row>
-    <row r="608" spans="19:22">
+    <row r="608" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S608" s="49"/>
       <c r="T608" s="49"/>
       <c r="U608" s="49"/>
       <c r="V608" s="49"/>
     </row>
-    <row r="609" spans="19:22">
+    <row r="609" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S609" s="49"/>
       <c r="T609" s="49"/>
       <c r="U609" s="49"/>
       <c r="V609" s="49"/>
     </row>
-    <row r="610" spans="19:22">
+    <row r="610" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S610" s="49"/>
       <c r="T610" s="49"/>
       <c r="U610" s="49"/>
       <c r="V610" s="49"/>
     </row>
-    <row r="611" spans="19:22">
+    <row r="611" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S611" s="49"/>
       <c r="T611" s="49"/>
       <c r="U611" s="49"/>
       <c r="V611" s="49"/>
     </row>
-    <row r="612" spans="19:22">
+    <row r="612" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S612" s="49"/>
       <c r="T612" s="49"/>
       <c r="U612" s="49"/>
       <c r="V612" s="49"/>
     </row>
-    <row r="613" spans="19:22">
+    <row r="613" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S613" s="49"/>
       <c r="T613" s="49"/>
       <c r="U613" s="49"/>
       <c r="V613" s="49"/>
     </row>
-    <row r="614" spans="19:22">
+    <row r="614" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S614" s="49"/>
       <c r="T614" s="49"/>
       <c r="U614" s="49"/>
       <c r="V614" s="49"/>
     </row>
-    <row r="615" spans="19:22">
+    <row r="615" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S615" s="49"/>
       <c r="T615" s="49"/>
       <c r="U615" s="49"/>
       <c r="V615" s="49"/>
     </row>
-    <row r="616" spans="19:22">
+    <row r="616" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S616" s="49"/>
       <c r="T616" s="49"/>
       <c r="U616" s="49"/>
       <c r="V616" s="49"/>
     </row>
-    <row r="617" spans="19:22">
+    <row r="617" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S617" s="49"/>
       <c r="T617" s="49"/>
       <c r="U617" s="49"/>
       <c r="V617" s="49"/>
     </row>
-    <row r="618" spans="19:22">
+    <row r="618" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S618" s="49"/>
       <c r="T618" s="49"/>
       <c r="U618" s="49"/>
       <c r="V618" s="49"/>
     </row>
-    <row r="619" spans="19:22">
+    <row r="619" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S619" s="49"/>
       <c r="T619" s="49"/>
       <c r="U619" s="49"/>
       <c r="V619" s="49"/>
     </row>
-    <row r="620" spans="19:22">
+    <row r="620" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S620" s="49"/>
       <c r="T620" s="49"/>
       <c r="U620" s="49"/>
       <c r="V620" s="49"/>
     </row>
-    <row r="621" spans="19:22">
+    <row r="621" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S621" s="49"/>
       <c r="T621" s="49"/>
       <c r="U621" s="49"/>
       <c r="V621" s="49"/>
     </row>
-    <row r="622" spans="19:22">
+    <row r="622" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S622" s="49"/>
       <c r="T622" s="49"/>
       <c r="U622" s="49"/>
       <c r="V622" s="49"/>
     </row>
-    <row r="623" spans="19:22">
+    <row r="623" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S623" s="49"/>
       <c r="T623" s="49"/>
       <c r="U623" s="49"/>
       <c r="V623" s="49"/>
     </row>
-    <row r="624" spans="19:22">
+    <row r="624" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S624" s="49"/>
       <c r="T624" s="49"/>
       <c r="U624" s="49"/>
       <c r="V624" s="49"/>
     </row>
-    <row r="625" spans="19:22">
+    <row r="625" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S625" s="49"/>
       <c r="T625" s="49"/>
       <c r="U625" s="49"/>
       <c r="V625" s="49"/>
     </row>
-    <row r="626" spans="19:22">
+    <row r="626" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S626" s="49"/>
       <c r="T626" s="49"/>
       <c r="U626" s="49"/>
       <c r="V626" s="49"/>
     </row>
-    <row r="627" spans="19:22">
+    <row r="627" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S627" s="49"/>
       <c r="T627" s="49"/>
       <c r="U627" s="49"/>
       <c r="V627" s="49"/>
     </row>
-    <row r="628" spans="19:22">
+    <row r="628" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S628" s="49"/>
       <c r="T628" s="49"/>
       <c r="U628" s="49"/>
       <c r="V628" s="49"/>
     </row>
-    <row r="629" spans="19:22">
+    <row r="629" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S629" s="49"/>
       <c r="T629" s="49"/>
       <c r="U629" s="49"/>
       <c r="V629" s="49"/>
     </row>
-    <row r="630" spans="19:22">
+    <row r="630" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S630" s="49"/>
       <c r="T630" s="49"/>
       <c r="U630" s="49"/>
       <c r="V630" s="49"/>
     </row>
-    <row r="631" spans="19:22">
+    <row r="631" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S631" s="49"/>
       <c r="T631" s="49"/>
       <c r="U631" s="49"/>
       <c r="V631" s="49"/>
     </row>
-    <row r="632" spans="19:22">
+    <row r="632" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S632" s="49"/>
       <c r="T632" s="49"/>
       <c r="U632" s="49"/>
       <c r="V632" s="49"/>
     </row>
-    <row r="633" spans="19:22">
+    <row r="633" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S633" s="49"/>
       <c r="T633" s="49"/>
       <c r="U633" s="49"/>
       <c r="V633" s="49"/>
     </row>
-    <row r="634" spans="19:22">
+    <row r="634" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S634" s="49"/>
       <c r="T634" s="49"/>
       <c r="U634" s="49"/>
       <c r="V634" s="49"/>
     </row>
-    <row r="635" spans="19:22">
+    <row r="635" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S635" s="49"/>
       <c r="T635" s="49"/>
       <c r="U635" s="49"/>
       <c r="V635" s="49"/>
     </row>
-    <row r="636" spans="19:22">
+    <row r="636" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S636" s="49"/>
       <c r="T636" s="49"/>
       <c r="U636" s="49"/>
       <c r="V636" s="49"/>
     </row>
-    <row r="637" spans="19:22">
+    <row r="637" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S637" s="49"/>
       <c r="T637" s="49"/>
       <c r="U637" s="49"/>
       <c r="V637" s="49"/>
     </row>
-    <row r="638" spans="19:22">
+    <row r="638" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S638" s="49"/>
       <c r="T638" s="49"/>
       <c r="U638" s="49"/>
       <c r="V638" s="49"/>
     </row>
-    <row r="639" spans="19:22">
+    <row r="639" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S639" s="49"/>
       <c r="T639" s="49"/>
       <c r="U639" s="49"/>
       <c r="V639" s="49"/>
     </row>
-    <row r="640" spans="19:22">
+    <row r="640" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S640" s="49"/>
       <c r="T640" s="49"/>
       <c r="U640" s="49"/>
       <c r="V640" s="49"/>
     </row>
-    <row r="641" spans="19:22">
+    <row r="641" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S641" s="49"/>
       <c r="T641" s="49"/>
       <c r="U641" s="49"/>
       <c r="V641" s="49"/>
     </row>
-    <row r="642" spans="19:22">
+    <row r="642" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S642" s="49"/>
       <c r="T642" s="49"/>
       <c r="U642" s="49"/>
       <c r="V642" s="49"/>
     </row>
-    <row r="643" spans="19:22">
+    <row r="643" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S643" s="49"/>
       <c r="T643" s="49"/>
       <c r="U643" s="49"/>
       <c r="V643" s="49"/>
     </row>
-    <row r="644" spans="19:22">
+    <row r="644" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S644" s="49"/>
       <c r="T644" s="49"/>
       <c r="U644" s="49"/>
       <c r="V644" s="49"/>
     </row>
-    <row r="645" spans="19:22">
+    <row r="645" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S645" s="49"/>
       <c r="T645" s="49"/>
       <c r="U645" s="49"/>
       <c r="V645" s="49"/>
     </row>
-    <row r="646" spans="19:22">
+    <row r="646" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S646" s="49"/>
       <c r="T646" s="49"/>
       <c r="U646" s="49"/>
       <c r="V646" s="49"/>
     </row>
-    <row r="647" spans="19:22">
+    <row r="647" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S647" s="49"/>
       <c r="T647" s="49"/>
       <c r="U647" s="49"/>
       <c r="V647" s="49"/>
     </row>
-    <row r="648" spans="19:22">
+    <row r="648" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S648" s="49"/>
       <c r="T648" s="49"/>
       <c r="U648" s="49"/>
       <c r="V648" s="49"/>
     </row>
-    <row r="649" spans="19:22">
+    <row r="649" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S649" s="49"/>
       <c r="T649" s="49"/>
       <c r="U649" s="49"/>
       <c r="V649" s="49"/>
     </row>
-    <row r="650" spans="19:22">
+    <row r="650" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S650" s="49"/>
       <c r="T650" s="49"/>
       <c r="U650" s="49"/>
       <c r="V650" s="49"/>
     </row>
-    <row r="651" spans="19:22">
+    <row r="651" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S651" s="49"/>
       <c r="T651" s="49"/>
       <c r="U651" s="49"/>
       <c r="V651" s="49"/>
     </row>
-    <row r="652" spans="19:22">
+    <row r="652" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S652" s="49"/>
       <c r="T652" s="49"/>
       <c r="U652" s="49"/>
       <c r="V652" s="49"/>
     </row>
-    <row r="653" spans="19:22">
+    <row r="653" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S653" s="49"/>
       <c r="T653" s="49"/>
       <c r="U653" s="49"/>
       <c r="V653" s="49"/>
     </row>
-    <row r="654" spans="19:22">
+    <row r="654" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S654" s="49"/>
       <c r="T654" s="49"/>
       <c r="U654" s="49"/>
       <c r="V654" s="49"/>
     </row>
-    <row r="655" spans="19:22">
+    <row r="655" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S655" s="49"/>
       <c r="T655" s="49"/>
       <c r="U655" s="49"/>
       <c r="V655" s="49"/>
     </row>
-    <row r="656" spans="19:22">
+    <row r="656" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S656" s="49"/>
       <c r="T656" s="49"/>
       <c r="U656" s="49"/>
       <c r="V656" s="49"/>
     </row>
-    <row r="657" spans="19:22">
+    <row r="657" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S657" s="49"/>
       <c r="T657" s="49"/>
       <c r="U657" s="49"/>
       <c r="V657" s="49"/>
     </row>
-    <row r="658" spans="19:22">
+    <row r="658" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S658" s="49"/>
       <c r="T658" s="49"/>
       <c r="U658" s="49"/>
       <c r="V658" s="49"/>
     </row>
-    <row r="659" spans="19:22">
+    <row r="659" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S659" s="49"/>
       <c r="T659" s="49"/>
       <c r="U659" s="49"/>
       <c r="V659" s="49"/>
     </row>
-    <row r="660" spans="19:22">
+    <row r="660" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S660" s="49"/>
       <c r="T660" s="49"/>
       <c r="U660" s="49"/>
       <c r="V660" s="49"/>
     </row>
-    <row r="661" spans="19:22">
+    <row r="661" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S661" s="49"/>
       <c r="T661" s="49"/>
       <c r="U661" s="49"/>
       <c r="V661" s="49"/>
     </row>
-    <row r="662" spans="19:22">
+    <row r="662" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S662" s="49"/>
       <c r="T662" s="49"/>
       <c r="U662" s="49"/>
       <c r="V662" s="49"/>
     </row>
-    <row r="663" spans="19:22">
+    <row r="663" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S663" s="49"/>
       <c r="T663" s="49"/>
       <c r="U663" s="49"/>
       <c r="V663" s="49"/>
     </row>
-    <row r="664" spans="19:22">
+    <row r="664" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S664" s="49"/>
       <c r="T664" s="49"/>
       <c r="U664" s="49"/>
       <c r="V664" s="49"/>
     </row>
-    <row r="665" spans="19:22">
+    <row r="665" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S665" s="49"/>
       <c r="T665" s="49"/>
       <c r="U665" s="49"/>
       <c r="V665" s="49"/>
     </row>
-    <row r="666" spans="19:22">
+    <row r="666" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S666" s="49"/>
       <c r="T666" s="49"/>
       <c r="U666" s="49"/>
       <c r="V666" s="49"/>
     </row>
-    <row r="667" spans="19:22">
+    <row r="667" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S667" s="49"/>
       <c r="T667" s="49"/>
       <c r="U667" s="49"/>
       <c r="V667" s="49"/>
     </row>
-    <row r="668" spans="19:22">
+    <row r="668" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S668" s="49"/>
       <c r="T668" s="49"/>
       <c r="U668" s="49"/>
       <c r="V668" s="49"/>
     </row>
-    <row r="669" spans="19:22">
+    <row r="669" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S669" s="49"/>
       <c r="T669" s="49"/>
       <c r="U669" s="49"/>
       <c r="V669" s="49"/>
     </row>
-    <row r="670" spans="19:22">
+    <row r="670" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S670" s="49"/>
       <c r="T670" s="49"/>
       <c r="U670" s="49"/>
       <c r="V670" s="49"/>
     </row>
-    <row r="671" spans="19:22">
+    <row r="671" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S671" s="49"/>
       <c r="T671" s="49"/>
       <c r="U671" s="49"/>
       <c r="V671" s="49"/>
     </row>
-    <row r="672" spans="19:22">
+    <row r="672" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S672" s="49"/>
       <c r="T672" s="49"/>
       <c r="U672" s="49"/>
       <c r="V672" s="49"/>
     </row>
-    <row r="673" spans="19:22">
+    <row r="673" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S673" s="49"/>
       <c r="T673" s="49"/>
       <c r="U673" s="49"/>
       <c r="V673" s="49"/>
     </row>
-    <row r="674" spans="19:22">
+    <row r="674" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S674" s="49"/>
       <c r="T674" s="49"/>
       <c r="U674" s="49"/>
       <c r="V674" s="49"/>
     </row>
-    <row r="675" spans="19:22">
+    <row r="675" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S675" s="49"/>
       <c r="T675" s="49"/>
       <c r="U675" s="49"/>
       <c r="V675" s="49"/>
     </row>
-    <row r="676" spans="19:22">
+    <row r="676" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S676" s="49"/>
       <c r="T676" s="49"/>
       <c r="U676" s="49"/>
       <c r="V676" s="49"/>
     </row>
-    <row r="677" spans="19:22">
+    <row r="677" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S677" s="49"/>
       <c r="T677" s="49"/>
       <c r="U677" s="49"/>
       <c r="V677" s="49"/>
     </row>
-    <row r="678" spans="19:22">
+    <row r="678" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S678" s="49"/>
       <c r="T678" s="49"/>
       <c r="U678" s="49"/>
       <c r="V678" s="49"/>
     </row>
-    <row r="679" spans="19:22">
+    <row r="679" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S679" s="49"/>
       <c r="T679" s="49"/>
       <c r="U679" s="49"/>
       <c r="V679" s="49"/>
     </row>
-    <row r="680" spans="19:22">
+    <row r="680" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S680" s="49"/>
       <c r="T680" s="49"/>
       <c r="U680" s="49"/>
       <c r="V680" s="49"/>
     </row>
-    <row r="681" spans="19:22">
+    <row r="681" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S681" s="49"/>
       <c r="T681" s="49"/>
       <c r="U681" s="49"/>
       <c r="V681" s="49"/>
     </row>
-    <row r="682" spans="19:22">
+    <row r="682" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S682" s="49"/>
       <c r="T682" s="49"/>
       <c r="U682" s="49"/>
       <c r="V682" s="49"/>
     </row>
-    <row r="683" spans="19:22">
+    <row r="683" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S683" s="49"/>
       <c r="T683" s="49"/>
       <c r="U683" s="49"/>
       <c r="V683" s="49"/>
     </row>
-    <row r="684" spans="19:22">
+    <row r="684" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S684" s="49"/>
       <c r="T684" s="49"/>
       <c r="U684" s="49"/>
       <c r="V684" s="49"/>
     </row>
-    <row r="685" spans="19:22">
+    <row r="685" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S685" s="49"/>
       <c r="T685" s="49"/>
       <c r="U685" s="49"/>
       <c r="V685" s="49"/>
     </row>
-    <row r="686" spans="19:22">
+    <row r="686" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S686" s="49"/>
       <c r="T686" s="49"/>
       <c r="U686" s="49"/>
       <c r="V686" s="49"/>
     </row>
-    <row r="687" spans="19:22">
+    <row r="687" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S687" s="49"/>
       <c r="T687" s="49"/>
       <c r="U687" s="49"/>
       <c r="V687" s="49"/>
     </row>
-    <row r="688" spans="19:22">
+    <row r="688" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S688" s="49"/>
       <c r="T688" s="49"/>
       <c r="U688" s="49"/>
       <c r="V688" s="49"/>
     </row>
-    <row r="689" spans="19:22">
+    <row r="689" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S689" s="49"/>
       <c r="T689" s="49"/>
       <c r="U689" s="49"/>
       <c r="V689" s="49"/>
     </row>
-    <row r="690" spans="19:22">
+    <row r="690" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S690" s="49"/>
       <c r="T690" s="49"/>
       <c r="U690" s="49"/>
       <c r="V690" s="49"/>
     </row>
-    <row r="691" spans="19:22">
+    <row r="691" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S691" s="49"/>
       <c r="T691" s="49"/>
       <c r="U691" s="49"/>
       <c r="V691" s="49"/>
     </row>
-    <row r="692" spans="19:22">
+    <row r="692" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S692" s="49"/>
       <c r="T692" s="49"/>
       <c r="U692" s="49"/>
       <c r="V692" s="49"/>
     </row>
-    <row r="693" spans="19:22">
+    <row r="693" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S693" s="49"/>
       <c r="T693" s="49"/>
       <c r="U693" s="49"/>
       <c r="V693" s="49"/>
     </row>
-    <row r="694" spans="19:22">
+    <row r="694" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S694" s="49"/>
       <c r="T694" s="49"/>
       <c r="U694" s="49"/>
       <c r="V694" s="49"/>
     </row>
-    <row r="695" spans="19:22">
+    <row r="695" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S695" s="49"/>
       <c r="T695" s="49"/>
       <c r="U695" s="49"/>
       <c r="V695" s="49"/>
     </row>
-    <row r="696" spans="19:22">
+    <row r="696" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S696" s="49"/>
       <c r="T696" s="49"/>
       <c r="U696" s="49"/>
       <c r="V696" s="49"/>
     </row>
-    <row r="697" spans="19:22">
+    <row r="697" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S697" s="49"/>
       <c r="T697" s="49"/>
       <c r="U697" s="49"/>
       <c r="V697" s="49"/>
     </row>
-    <row r="698" spans="19:22">
+    <row r="698" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S698" s="49"/>
       <c r="T698" s="49"/>
       <c r="U698" s="49"/>
       <c r="V698" s="49"/>
     </row>
-    <row r="699" spans="19:22">
+    <row r="699" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S699" s="49"/>
       <c r="T699" s="49"/>
       <c r="U699" s="49"/>
       <c r="V699" s="49"/>
     </row>
-    <row r="700" spans="19:22">
+    <row r="700" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S700" s="49"/>
       <c r="T700" s="49"/>
       <c r="U700" s="49"/>
       <c r="V700" s="49"/>
     </row>
-    <row r="701" spans="19:22">
+    <row r="701" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S701" s="49"/>
       <c r="T701" s="49"/>
       <c r="U701" s="49"/>
       <c r="V701" s="49"/>
     </row>
-    <row r="702" spans="19:22">
+    <row r="702" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S702" s="49"/>
       <c r="T702" s="49"/>
       <c r="U702" s="49"/>
       <c r="V702" s="49"/>
     </row>
-    <row r="703" spans="19:22">
+    <row r="703" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S703" s="49"/>
       <c r="T703" s="49"/>
       <c r="U703" s="49"/>
       <c r="V703" s="49"/>
     </row>
-    <row r="704" spans="19:22">
+    <row r="704" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S704" s="49"/>
       <c r="T704" s="49"/>
       <c r="U704" s="49"/>
       <c r="V704" s="49"/>
     </row>
-    <row r="705" spans="19:22">
+    <row r="705" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S705" s="49"/>
       <c r="T705" s="49"/>
       <c r="U705" s="49"/>
       <c r="V705" s="49"/>
     </row>
-    <row r="706" spans="19:22">
+    <row r="706" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S706" s="49"/>
       <c r="T706" s="49"/>
       <c r="U706" s="49"/>
       <c r="V706" s="49"/>
     </row>
-    <row r="707" spans="19:22">
+    <row r="707" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S707" s="49"/>
       <c r="T707" s="49"/>
       <c r="U707" s="49"/>
       <c r="V707" s="49"/>
     </row>
-    <row r="708" spans="19:22">
+    <row r="708" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S708" s="49"/>
       <c r="T708" s="49"/>
       <c r="U708" s="49"/>
       <c r="V708" s="49"/>
     </row>
-    <row r="709" spans="19:22">
+    <row r="709" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S709" s="49"/>
       <c r="T709" s="49"/>
       <c r="U709" s="49"/>
       <c r="V709" s="49"/>
     </row>
-    <row r="710" spans="19:22">
+    <row r="710" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S710" s="49"/>
       <c r="T710" s="49"/>
       <c r="U710" s="49"/>
       <c r="V710" s="49"/>
     </row>
-    <row r="711" spans="19:22">
+    <row r="711" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S711" s="49"/>
       <c r="T711" s="49"/>
       <c r="U711" s="49"/>
       <c r="V711" s="49"/>
     </row>
-    <row r="712" spans="19:22">
+    <row r="712" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S712" s="49"/>
       <c r="T712" s="49"/>
       <c r="U712" s="49"/>
       <c r="V712" s="49"/>
     </row>
-    <row r="713" spans="19:22">
+    <row r="713" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S713" s="49"/>
       <c r="T713" s="49"/>
       <c r="U713" s="49"/>
       <c r="V713" s="49"/>
     </row>
-    <row r="714" spans="19:22">
+    <row r="714" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S714" s="49"/>
       <c r="T714" s="49"/>
       <c r="U714" s="49"/>
       <c r="V714" s="49"/>
     </row>
-    <row r="715" spans="19:22">
+    <row r="715" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S715" s="49"/>
       <c r="T715" s="49"/>
       <c r="U715" s="49"/>
       <c r="V715" s="49"/>
     </row>
-    <row r="716" spans="19:22">
+    <row r="716" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S716" s="49"/>
       <c r="T716" s="49"/>
       <c r="U716" s="49"/>
       <c r="V716" s="49"/>
     </row>
-    <row r="717" spans="19:22">
+    <row r="717" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S717" s="49"/>
       <c r="T717" s="49"/>
       <c r="U717" s="49"/>
       <c r="V717" s="49"/>
     </row>
-    <row r="718" spans="19:22">
+    <row r="718" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S718" s="49"/>
       <c r="T718" s="49"/>
       <c r="U718" s="49"/>
       <c r="V718" s="49"/>
     </row>
-    <row r="719" spans="19:22">
+    <row r="719" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S719" s="49"/>
       <c r="T719" s="49"/>
       <c r="U719" s="49"/>
       <c r="V719" s="49"/>
     </row>
-    <row r="720" spans="19:22">
+    <row r="720" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S720" s="49"/>
       <c r="T720" s="49"/>
       <c r="U720" s="49"/>
       <c r="V720" s="49"/>
     </row>
-    <row r="721" spans="19:22">
+    <row r="721" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S721" s="49"/>
       <c r="T721" s="49"/>
       <c r="U721" s="49"/>
       <c r="V721" s="49"/>
     </row>
-    <row r="722" spans="19:22">
+    <row r="722" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S722" s="49"/>
       <c r="T722" s="49"/>
       <c r="U722" s="49"/>
       <c r="V722" s="49"/>
     </row>
-    <row r="723" spans="19:22">
+    <row r="723" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S723" s="49"/>
       <c r="T723" s="49"/>
       <c r="U723" s="49"/>
       <c r="V723" s="49"/>
     </row>
-    <row r="724" spans="19:22">
+    <row r="724" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S724" s="49"/>
       <c r="T724" s="49"/>
       <c r="U724" s="49"/>
       <c r="V724" s="49"/>
     </row>
-    <row r="725" spans="19:22">
+    <row r="725" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S725" s="49"/>
       <c r="T725" s="49"/>
       <c r="U725" s="49"/>
       <c r="V725" s="49"/>
     </row>
-    <row r="726" spans="19:22">
+    <row r="726" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S726" s="49"/>
       <c r="T726" s="49"/>
       <c r="U726" s="49"/>
       <c r="V726" s="49"/>
     </row>
-    <row r="727" spans="19:22">
+    <row r="727" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S727" s="49"/>
       <c r="T727" s="49"/>
       <c r="U727" s="49"/>
       <c r="V727" s="49"/>
     </row>
-    <row r="728" spans="19:22">
+    <row r="728" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S728" s="49"/>
       <c r="T728" s="49"/>
       <c r="U728" s="49"/>
       <c r="V728" s="49"/>
     </row>
-    <row r="729" spans="19:22">
+    <row r="729" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S729" s="49"/>
       <c r="T729" s="49"/>
       <c r="U729" s="49"/>
       <c r="V729" s="49"/>
     </row>
-    <row r="730" spans="19:22">
+    <row r="730" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S730" s="49"/>
       <c r="T730" s="49"/>
       <c r="U730" s="49"/>
       <c r="V730" s="49"/>
     </row>
-    <row r="731" spans="19:22">
+    <row r="731" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S731" s="49"/>
       <c r="T731" s="49"/>
       <c r="U731" s="49"/>
       <c r="V731" s="49"/>
     </row>
-    <row r="732" spans="19:22">
+    <row r="732" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S732" s="49"/>
       <c r="T732" s="49"/>
       <c r="U732" s="49"/>
       <c r="V732" s="49"/>
     </row>
-    <row r="733" spans="19:22">
+    <row r="733" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S733" s="49"/>
       <c r="T733" s="49"/>
       <c r="U733" s="49"/>
       <c r="V733" s="49"/>
     </row>
-    <row r="734" spans="19:22">
+    <row r="734" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S734" s="49"/>
       <c r="T734" s="49"/>
       <c r="U734" s="49"/>
       <c r="V734" s="49"/>
     </row>
-    <row r="735" spans="19:22">
+    <row r="735" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S735" s="49"/>
       <c r="T735" s="49"/>
       <c r="U735" s="49"/>
       <c r="V735" s="49"/>
     </row>
-    <row r="736" spans="19:22">
+    <row r="736" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S736" s="49"/>
       <c r="T736" s="49"/>
       <c r="U736" s="49"/>
       <c r="V736" s="49"/>
     </row>
-    <row r="737" spans="19:22">
+    <row r="737" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S737" s="49"/>
       <c r="T737" s="49"/>
       <c r="U737" s="49"/>
       <c r="V737" s="49"/>
     </row>
-    <row r="738" spans="19:22">
+    <row r="738" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S738" s="49"/>
       <c r="T738" s="49"/>
       <c r="U738" s="49"/>
       <c r="V738" s="49"/>
     </row>
-    <row r="739" spans="19:22">
+    <row r="739" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S739" s="49"/>
       <c r="T739" s="49"/>
       <c r="U739" s="49"/>
       <c r="V739" s="49"/>
     </row>
-    <row r="740" spans="19:22">
+    <row r="740" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S740" s="49"/>
       <c r="T740" s="49"/>
       <c r="U740" s="49"/>
       <c r="V740" s="49"/>
     </row>
-    <row r="741" spans="19:22">
+    <row r="741" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S741" s="49"/>
       <c r="T741" s="49"/>
       <c r="U741" s="49"/>
       <c r="V741" s="49"/>
     </row>
-    <row r="742" spans="19:22">
+    <row r="742" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S742" s="49"/>
       <c r="T742" s="49"/>
       <c r="U742" s="49"/>
       <c r="V742" s="49"/>
     </row>
-    <row r="743" spans="19:22">
+    <row r="743" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S743" s="49"/>
       <c r="T743" s="49"/>
       <c r="U743" s="49"/>
       <c r="V743" s="49"/>
     </row>
-    <row r="744" spans="19:22">
+    <row r="744" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S744" s="49"/>
       <c r="T744" s="49"/>
       <c r="U744" s="49"/>
       <c r="V744" s="49"/>
     </row>
-    <row r="745" spans="19:22">
+    <row r="745" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S745" s="49"/>
       <c r="T745" s="49"/>
       <c r="U745" s="49"/>
       <c r="V745" s="49"/>
     </row>
-    <row r="746" spans="19:22">
+    <row r="746" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S746" s="49"/>
       <c r="T746" s="49"/>
       <c r="U746" s="49"/>
       <c r="V746" s="49"/>
     </row>
-    <row r="747" spans="19:22">
+    <row r="747" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S747" s="49"/>
       <c r="T747" s="49"/>
       <c r="U747" s="49"/>
       <c r="V747" s="49"/>
     </row>
-    <row r="748" spans="19:22">
+    <row r="748" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S748" s="49"/>
       <c r="T748" s="49"/>
       <c r="U748" s="49"/>
       <c r="V748" s="49"/>
     </row>
-    <row r="749" spans="19:22">
+    <row r="749" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S749" s="49"/>
       <c r="T749" s="49"/>
       <c r="U749" s="49"/>
       <c r="V749" s="49"/>
     </row>
-    <row r="750" spans="19:22">
+    <row r="750" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S750" s="49"/>
       <c r="T750" s="49"/>
       <c r="U750" s="49"/>
       <c r="V750" s="49"/>
     </row>
-    <row r="751" spans="19:22">
+    <row r="751" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S751" s="49"/>
       <c r="T751" s="49"/>
       <c r="U751" s="49"/>
       <c r="V751" s="49"/>
     </row>
-    <row r="752" spans="19:22">
+    <row r="752" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S752" s="49"/>
       <c r="T752" s="49"/>
       <c r="U752" s="49"/>
       <c r="V752" s="49"/>
     </row>
-    <row r="753" spans="19:22">
+    <row r="753" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S753" s="49"/>
       <c r="T753" s="49"/>
       <c r="U753" s="49"/>
       <c r="V753" s="49"/>
     </row>
-    <row r="754" spans="19:22">
+    <row r="754" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S754" s="49"/>
       <c r="T754" s="49"/>
       <c r="U754" s="49"/>
       <c r="V754" s="49"/>
     </row>
-    <row r="755" spans="19:22">
+    <row r="755" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S755" s="49"/>
       <c r="T755" s="49"/>
       <c r="U755" s="49"/>
       <c r="V755" s="49"/>
     </row>
-    <row r="756" spans="19:22">
+    <row r="756" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S756" s="49"/>
       <c r="T756" s="49"/>
       <c r="U756" s="49"/>
       <c r="V756" s="49"/>
     </row>
-    <row r="757" spans="19:22">
+    <row r="757" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S757" s="49"/>
       <c r="T757" s="49"/>
       <c r="U757" s="49"/>
       <c r="V757" s="49"/>
     </row>
-    <row r="758" spans="19:22">
+    <row r="758" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S758" s="49"/>
       <c r="T758" s="49"/>
       <c r="U758" s="49"/>
       <c r="V758" s="49"/>
     </row>
-    <row r="759" spans="19:22">
+    <row r="759" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S759" s="49"/>
       <c r="T759" s="49"/>
       <c r="U759" s="49"/>
       <c r="V759" s="49"/>
     </row>
-    <row r="760" spans="19:22">
+    <row r="760" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S760" s="49"/>
       <c r="T760" s="49"/>
       <c r="U760" s="49"/>
       <c r="V760" s="49"/>
     </row>
-    <row r="761" spans="19:22">
+    <row r="761" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S761" s="49"/>
       <c r="T761" s="49"/>
       <c r="U761" s="49"/>
       <c r="V761" s="49"/>
     </row>
-    <row r="762" spans="19:22">
+    <row r="762" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S762" s="49"/>
       <c r="T762" s="49"/>
       <c r="U762" s="49"/>
       <c r="V762" s="49"/>
     </row>
-    <row r="763" spans="19:22">
+    <row r="763" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S763" s="49"/>
       <c r="T763" s="49"/>
       <c r="U763" s="49"/>
       <c r="V763" s="49"/>
     </row>
-    <row r="764" spans="19:22">
+    <row r="764" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S764" s="49"/>
       <c r="T764" s="49"/>
       <c r="U764" s="49"/>
       <c r="V764" s="49"/>
     </row>
-    <row r="765" spans="19:22">
+    <row r="765" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S765" s="49"/>
       <c r="T765" s="49"/>
       <c r="U765" s="49"/>
       <c r="V765" s="49"/>
     </row>
-    <row r="766" spans="19:22">
+    <row r="766" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S766" s="49"/>
       <c r="T766" s="49"/>
       <c r="U766" s="49"/>
       <c r="V766" s="49"/>
     </row>
-    <row r="767" spans="19:22">
+    <row r="767" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S767" s="49"/>
       <c r="T767" s="49"/>
       <c r="U767" s="49"/>
       <c r="V767" s="49"/>
     </row>
-    <row r="768" spans="19:22">
+    <row r="768" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S768" s="49"/>
       <c r="T768" s="49"/>
       <c r="U768" s="49"/>
       <c r="V768" s="49"/>
     </row>
-    <row r="769" spans="19:22">
+    <row r="769" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S769" s="49"/>
       <c r="T769" s="49"/>
       <c r="U769" s="49"/>
       <c r="V769" s="49"/>
     </row>
-    <row r="770" spans="19:22">
+    <row r="770" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S770" s="49"/>
       <c r="T770" s="49"/>
       <c r="U770" s="49"/>
       <c r="V770" s="49"/>
     </row>
-    <row r="771" spans="19:22">
+    <row r="771" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S771" s="49"/>
       <c r="T771" s="49"/>
       <c r="U771" s="49"/>
       <c r="V771" s="49"/>
     </row>
-    <row r="772" spans="19:22">
+    <row r="772" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S772" s="49"/>
       <c r="T772" s="49"/>
       <c r="U772" s="49"/>
       <c r="V772" s="49"/>
     </row>
-    <row r="773" spans="19:22">
+    <row r="773" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S773" s="49"/>
       <c r="T773" s="49"/>
       <c r="U773" s="49"/>
       <c r="V773" s="49"/>
     </row>
-    <row r="774" spans="19:22">
+    <row r="774" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S774" s="49"/>
       <c r="T774" s="49"/>
       <c r="U774" s="49"/>
       <c r="V774" s="49"/>
     </row>
-    <row r="775" spans="19:22">
+    <row r="775" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S775" s="49"/>
       <c r="T775" s="49"/>
       <c r="U775" s="49"/>
       <c r="V775" s="49"/>
     </row>
-    <row r="776" spans="19:22">
+    <row r="776" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S776" s="49"/>
       <c r="T776" s="49"/>
       <c r="U776" s="49"/>
       <c r="V776" s="49"/>
     </row>
-    <row r="777" spans="19:22">
+    <row r="777" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S777" s="49"/>
       <c r="T777" s="49"/>
       <c r="U777" s="49"/>
       <c r="V777" s="49"/>
     </row>
-    <row r="778" spans="19:22">
+    <row r="778" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S778" s="49"/>
       <c r="T778" s="49"/>
       <c r="U778" s="49"/>
       <c r="V778" s="49"/>
     </row>
-    <row r="779" spans="19:22">
+    <row r="779" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S779" s="49"/>
       <c r="T779" s="49"/>
       <c r="U779" s="49"/>
       <c r="V779" s="49"/>
     </row>
-    <row r="780" spans="19:22">
+    <row r="780" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S780" s="49"/>
       <c r="T780" s="49"/>
       <c r="U780" s="49"/>
       <c r="V780" s="49"/>
     </row>
-    <row r="781" spans="19:22">
+    <row r="781" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S781" s="49"/>
       <c r="T781" s="49"/>
       <c r="U781" s="49"/>
       <c r="V781" s="49"/>
     </row>
-    <row r="782" spans="19:22">
+    <row r="782" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S782" s="49"/>
       <c r="T782" s="49"/>
       <c r="U782" s="49"/>
       <c r="V782" s="49"/>
     </row>
-    <row r="783" spans="19:22">
+    <row r="783" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S783" s="49"/>
       <c r="T783" s="49"/>
       <c r="U783" s="49"/>
       <c r="V783" s="49"/>
     </row>
-    <row r="784" spans="19:22">
+    <row r="784" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S784" s="49"/>
       <c r="T784" s="49"/>
       <c r="U784" s="49"/>
       <c r="V784" s="49"/>
     </row>
-    <row r="785" spans="19:22">
+    <row r="785" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S785" s="49"/>
       <c r="T785" s="49"/>
       <c r="U785" s="49"/>
       <c r="V785" s="49"/>
     </row>
-    <row r="786" spans="19:22">
+    <row r="786" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S786" s="49"/>
       <c r="T786" s="49"/>
       <c r="U786" s="49"/>
       <c r="V786" s="49"/>
     </row>
-    <row r="787" spans="19:22">
+    <row r="787" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S787" s="49"/>
       <c r="T787" s="49"/>
       <c r="U787" s="49"/>
       <c r="V787" s="49"/>
     </row>
-    <row r="788" spans="19:22">
+    <row r="788" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S788" s="49"/>
       <c r="T788" s="49"/>
       <c r="U788" s="49"/>
       <c r="V788" s="49"/>
     </row>
-    <row r="789" spans="19:22">
+    <row r="789" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S789" s="49"/>
       <c r="T789" s="49"/>
       <c r="U789" s="49"/>
       <c r="V789" s="49"/>
     </row>
-    <row r="790" spans="19:22">
+    <row r="790" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S790" s="49"/>
       <c r="T790" s="49"/>
       <c r="U790" s="49"/>
       <c r="V790" s="49"/>
     </row>
-    <row r="791" spans="19:22">
+    <row r="791" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S791" s="49"/>
       <c r="T791" s="49"/>
       <c r="U791" s="49"/>
       <c r="V791" s="49"/>
     </row>
-    <row r="792" spans="19:22">
+    <row r="792" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S792" s="49"/>
       <c r="T792" s="49"/>
       <c r="U792" s="49"/>
       <c r="V792" s="49"/>
     </row>
-    <row r="793" spans="19:22">
+    <row r="793" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S793" s="49"/>
       <c r="T793" s="49"/>
       <c r="U793" s="49"/>
       <c r="V793" s="49"/>
     </row>
-    <row r="794" spans="19:22">
+    <row r="794" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S794" s="49"/>
       <c r="T794" s="49"/>
       <c r="U794" s="49"/>
       <c r="V794" s="49"/>
     </row>
-    <row r="795" spans="19:22">
+    <row r="795" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S795" s="49"/>
       <c r="T795" s="49"/>
       <c r="U795" s="49"/>
       <c r="V795" s="49"/>
     </row>
-    <row r="796" spans="19:22">
+    <row r="796" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S796" s="49"/>
       <c r="T796" s="49"/>
       <c r="U796" s="49"/>
       <c r="V796" s="49"/>
     </row>
-    <row r="797" spans="19:22">
+    <row r="797" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S797" s="49"/>
       <c r="T797" s="49"/>
       <c r="U797" s="49"/>
       <c r="V797" s="49"/>
     </row>
-    <row r="798" spans="19:22">
+    <row r="798" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S798" s="49"/>
       <c r="T798" s="49"/>
       <c r="U798" s="49"/>
       <c r="V798" s="49"/>
     </row>
-    <row r="799" spans="19:22">
+    <row r="799" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S799" s="49"/>
       <c r="T799" s="49"/>
       <c r="U799" s="49"/>
       <c r="V799" s="49"/>
     </row>
-    <row r="800" spans="19:22">
+    <row r="800" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S800" s="49"/>
       <c r="T800" s="49"/>
       <c r="U800" s="49"/>
       <c r="V800" s="49"/>
     </row>
-    <row r="801" spans="19:22">
+    <row r="801" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S801" s="49"/>
       <c r="T801" s="49"/>
       <c r="U801" s="49"/>
       <c r="V801" s="49"/>
     </row>
-    <row r="802" spans="19:22">
+    <row r="802" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S802" s="49"/>
       <c r="T802" s="49"/>
       <c r="U802" s="49"/>
       <c r="V802" s="49"/>
     </row>
-    <row r="803" spans="19:22">
+    <row r="803" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S803" s="49"/>
       <c r="T803" s="49"/>
       <c r="U803" s="49"/>
       <c r="V803" s="49"/>
     </row>
-    <row r="804" spans="19:22">
+    <row r="804" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S804" s="49"/>
       <c r="T804" s="49"/>
       <c r="U804" s="49"/>
       <c r="V804" s="49"/>
     </row>
-    <row r="805" spans="19:22">
+    <row r="805" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S805" s="49"/>
       <c r="T805" s="49"/>
       <c r="U805" s="49"/>
       <c r="V805" s="49"/>
     </row>
-    <row r="806" spans="19:22">
+    <row r="806" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S806" s="49"/>
       <c r="T806" s="49"/>
       <c r="U806" s="49"/>
       <c r="V806" s="49"/>
     </row>
-    <row r="807" spans="19:22">
+    <row r="807" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S807" s="49"/>
       <c r="T807" s="49"/>
       <c r="U807" s="49"/>
       <c r="V807" s="49"/>
     </row>
-    <row r="808" spans="19:22">
+    <row r="808" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S808" s="49"/>
       <c r="T808" s="49"/>
       <c r="U808" s="49"/>
       <c r="V808" s="49"/>
     </row>
-    <row r="809" spans="19:22">
+    <row r="809" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S809" s="49"/>
       <c r="T809" s="49"/>
       <c r="U809" s="49"/>
       <c r="V809" s="49"/>
     </row>
-    <row r="810" spans="19:22">
+    <row r="810" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S810" s="49"/>
       <c r="T810" s="49"/>
       <c r="U810" s="49"/>
       <c r="V810" s="49"/>
     </row>
-    <row r="811" spans="19:22">
+    <row r="811" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S811" s="49"/>
       <c r="T811" s="49"/>
       <c r="U811" s="49"/>
       <c r="V811" s="49"/>
     </row>
-    <row r="812" spans="19:22">
+    <row r="812" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S812" s="49"/>
       <c r="T812" s="49"/>
       <c r="U812" s="49"/>
       <c r="V812" s="49"/>
     </row>
-    <row r="813" spans="19:22">
+    <row r="813" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S813" s="49"/>
       <c r="T813" s="49"/>
       <c r="U813" s="49"/>
       <c r="V813" s="49"/>
     </row>
-    <row r="814" spans="19:22">
+    <row r="814" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S814" s="49"/>
       <c r="T814" s="49"/>
       <c r="U814" s="49"/>
       <c r="V814" s="49"/>
     </row>
-    <row r="815" spans="19:22">
+    <row r="815" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S815" s="49"/>
       <c r="T815" s="49"/>
       <c r="U815" s="49"/>
       <c r="V815" s="49"/>
     </row>
-    <row r="816" spans="19:22">
+    <row r="816" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S816" s="49"/>
       <c r="T816" s="49"/>
       <c r="U816" s="49"/>
       <c r="V816" s="49"/>
     </row>
-    <row r="817" spans="19:22">
+    <row r="817" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S817" s="49"/>
       <c r="T817" s="49"/>
       <c r="U817" s="49"/>
       <c r="V817" s="49"/>
     </row>
-    <row r="818" spans="19:22">
+    <row r="818" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S818" s="49"/>
       <c r="T818" s="49"/>
       <c r="U818" s="49"/>
       <c r="V818" s="49"/>
     </row>
-    <row r="819" spans="19:22">
+    <row r="819" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S819" s="49"/>
       <c r="T819" s="49"/>
       <c r="U819" s="49"/>
       <c r="V819" s="49"/>
     </row>
-    <row r="820" spans="19:22">
+    <row r="820" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S820" s="49"/>
       <c r="T820" s="49"/>
       <c r="U820" s="49"/>
       <c r="V820" s="49"/>
     </row>
-    <row r="821" spans="19:22">
+    <row r="821" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S821" s="49"/>
       <c r="T821" s="49"/>
       <c r="U821" s="49"/>
       <c r="V821" s="49"/>
     </row>
-    <row r="822" spans="19:22">
+    <row r="822" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S822" s="49"/>
       <c r="T822" s="49"/>
       <c r="U822" s="49"/>
       <c r="V822" s="49"/>
     </row>
-    <row r="823" spans="19:22">
+    <row r="823" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S823" s="49"/>
       <c r="T823" s="49"/>
       <c r="U823" s="49"/>
       <c r="V823" s="49"/>
     </row>
-    <row r="824" spans="19:22">
+    <row r="824" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S824" s="49"/>
       <c r="T824" s="49"/>
       <c r="U824" s="49"/>
       <c r="V824" s="49"/>
     </row>
-    <row r="825" spans="19:22">
+    <row r="825" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S825" s="49"/>
       <c r="T825" s="49"/>
       <c r="U825" s="49"/>
       <c r="V825" s="49"/>
     </row>
-    <row r="826" spans="19:22">
+    <row r="826" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S826" s="49"/>
       <c r="T826" s="49"/>
       <c r="U826" s="49"/>
       <c r="V826" s="49"/>
     </row>
-    <row r="827" spans="19:22">
+    <row r="827" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S827" s="49"/>
       <c r="T827" s="49"/>
       <c r="U827" s="49"/>
       <c r="V827" s="49"/>
     </row>
-    <row r="828" spans="19:22">
+    <row r="828" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S828" s="49"/>
       <c r="T828" s="49"/>
       <c r="U828" s="49"/>
       <c r="V828" s="49"/>
     </row>
-    <row r="829" spans="19:22">
+    <row r="829" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S829" s="49"/>
       <c r="T829" s="49"/>
       <c r="U829" s="49"/>
       <c r="V829" s="49"/>
     </row>
-    <row r="830" spans="19:22">
+    <row r="830" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S830" s="49"/>
       <c r="T830" s="49"/>
       <c r="U830" s="49"/>
       <c r="V830" s="49"/>
     </row>
-    <row r="831" spans="19:22">
+    <row r="831" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S831" s="49"/>
       <c r="T831" s="49"/>
       <c r="U831" s="49"/>
       <c r="V831" s="49"/>
     </row>
-    <row r="832" spans="19:22">
+    <row r="832" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S832" s="49"/>
       <c r="T832" s="49"/>
       <c r="U832" s="49"/>
       <c r="V832" s="49"/>
     </row>
-    <row r="833" spans="19:22">
+    <row r="833" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S833" s="49"/>
       <c r="T833" s="49"/>
       <c r="U833" s="49"/>
       <c r="V833" s="49"/>
     </row>
-    <row r="834" spans="19:22">
+    <row r="834" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S834" s="49"/>
       <c r="T834" s="49"/>
       <c r="U834" s="49"/>
       <c r="V834" s="49"/>
     </row>
-    <row r="835" spans="19:22">
+    <row r="835" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S835" s="49"/>
       <c r="T835" s="49"/>
       <c r="U835" s="49"/>
       <c r="V835" s="49"/>
     </row>
-    <row r="836" spans="19:22">
+    <row r="836" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S836" s="49"/>
       <c r="T836" s="49"/>
       <c r="U836" s="49"/>
       <c r="V836" s="49"/>
     </row>
-    <row r="837" spans="19:22">
+    <row r="837" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S837" s="49"/>
       <c r="T837" s="49"/>
       <c r="U837" s="49"/>
       <c r="V837" s="49"/>
     </row>
-    <row r="838" spans="19:22">
+    <row r="838" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S838" s="49"/>
       <c r="T838" s="49"/>
       <c r="U838" s="49"/>
       <c r="V838" s="49"/>
     </row>
-    <row r="839" spans="19:22">
+    <row r="839" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S839" s="49"/>
       <c r="T839" s="49"/>
       <c r="U839" s="49"/>
       <c r="V839" s="49"/>
     </row>
-    <row r="840" spans="19:22">
+    <row r="840" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S840" s="49"/>
       <c r="T840" s="49"/>
       <c r="U840" s="49"/>
       <c r="V840" s="49"/>
     </row>
-    <row r="841" spans="19:22">
+    <row r="841" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S841" s="49"/>
       <c r="T841" s="49"/>
       <c r="U841" s="49"/>
       <c r="V841" s="49"/>
     </row>
-    <row r="842" spans="19:22">
+    <row r="842" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S842" s="49"/>
       <c r="T842" s="49"/>
       <c r="U842" s="49"/>
       <c r="V842" s="49"/>
     </row>
-    <row r="843" spans="19:22">
+    <row r="843" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S843" s="49"/>
       <c r="T843" s="49"/>
       <c r="U843" s="49"/>
       <c r="V843" s="49"/>
     </row>
-    <row r="844" spans="19:22">
+    <row r="844" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S844" s="49"/>
       <c r="T844" s="49"/>
       <c r="U844" s="49"/>
       <c r="V844" s="49"/>
     </row>
-    <row r="845" spans="19:22">
+    <row r="845" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S845" s="49"/>
       <c r="T845" s="49"/>
       <c r="U845" s="49"/>
       <c r="V845" s="49"/>
     </row>
-    <row r="846" spans="19:22">
+    <row r="846" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S846" s="49"/>
       <c r="T846" s="49"/>
       <c r="U846" s="49"/>
       <c r="V846" s="49"/>
     </row>
-    <row r="847" spans="19:22">
+    <row r="847" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S847" s="49"/>
       <c r="T847" s="49"/>
       <c r="U847" s="49"/>
       <c r="V847" s="49"/>
     </row>
-    <row r="848" spans="19:22">
+    <row r="848" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S848" s="49"/>
       <c r="T848" s="49"/>
       <c r="U848" s="49"/>
       <c r="V848" s="49"/>
     </row>
-    <row r="849" spans="19:22">
+    <row r="849" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S849" s="49"/>
       <c r="T849" s="49"/>
       <c r="U849" s="49"/>
       <c r="V849" s="49"/>
     </row>
-    <row r="850" spans="19:22">
+    <row r="850" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S850" s="49"/>
       <c r="T850" s="49"/>
       <c r="U850" s="49"/>
       <c r="V850" s="49"/>
     </row>
-    <row r="851" spans="19:22">
+    <row r="851" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S851" s="49"/>
       <c r="T851" s="49"/>
       <c r="U851" s="49"/>
       <c r="V851" s="49"/>
     </row>
-    <row r="852" spans="19:22">
+    <row r="852" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S852" s="49"/>
       <c r="T852" s="49"/>
       <c r="U852" s="49"/>
       <c r="V852" s="49"/>
     </row>
-    <row r="853" spans="19:22">
+    <row r="853" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S853" s="49"/>
       <c r="T853" s="49"/>
       <c r="U853" s="49"/>
       <c r="V853" s="49"/>
     </row>
-    <row r="854" spans="19:22">
+    <row r="854" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S854" s="49"/>
       <c r="T854" s="49"/>
       <c r="U854" s="49"/>
       <c r="V854" s="49"/>
     </row>
-    <row r="855" spans="19:22">
+    <row r="855" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S855" s="49"/>
       <c r="T855" s="49"/>
       <c r="U855" s="49"/>
       <c r="V855" s="49"/>
     </row>
-    <row r="856" spans="19:22">
+    <row r="856" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S856" s="49"/>
       <c r="T856" s="49"/>
       <c r="U856" s="49"/>
       <c r="V856" s="49"/>
     </row>
-    <row r="857" spans="19:22">
+    <row r="857" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S857" s="49"/>
       <c r="T857" s="49"/>
       <c r="U857" s="49"/>
       <c r="V857" s="49"/>
     </row>
-    <row r="858" spans="19:22">
+    <row r="858" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S858" s="49"/>
       <c r="T858" s="49"/>
       <c r="U858" s="49"/>
       <c r="V858" s="49"/>
     </row>
-    <row r="859" spans="19:22">
+    <row r="859" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S859" s="49"/>
       <c r="T859" s="49"/>
       <c r="U859" s="49"/>
       <c r="V859" s="49"/>
     </row>
-    <row r="860" spans="19:22">
+    <row r="860" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S860" s="49"/>
       <c r="T860" s="49"/>
       <c r="U860" s="49"/>
       <c r="V860" s="49"/>
     </row>
-    <row r="861" spans="19:22">
+    <row r="861" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S861" s="49"/>
       <c r="T861" s="49"/>
       <c r="U861" s="49"/>
       <c r="V861" s="49"/>
     </row>
-    <row r="862" spans="19:22">
+    <row r="862" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S862" s="49"/>
       <c r="T862" s="49"/>
       <c r="U862" s="49"/>
       <c r="V862" s="49"/>
     </row>
-    <row r="863" spans="19:22">
+    <row r="863" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S863" s="49"/>
       <c r="T863" s="49"/>
       <c r="U863" s="49"/>
       <c r="V863" s="49"/>
     </row>
-    <row r="864" spans="19:22">
+    <row r="864" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S864" s="49"/>
       <c r="T864" s="49"/>
       <c r="U864" s="49"/>
       <c r="V864" s="49"/>
     </row>
-    <row r="865" spans="19:22">
+    <row r="865" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S865" s="49"/>
       <c r="T865" s="49"/>
       <c r="U865" s="49"/>
       <c r="V865" s="49"/>
     </row>
-    <row r="866" spans="19:22">
+    <row r="866" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S866" s="49"/>
       <c r="T866" s="49"/>
       <c r="U866" s="49"/>
       <c r="V866" s="49"/>
     </row>
-    <row r="867" spans="19:22">
+    <row r="867" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S867" s="49"/>
       <c r="T867" s="49"/>
       <c r="U867" s="49"/>
       <c r="V867" s="49"/>
     </row>
-    <row r="868" spans="19:22">
+    <row r="868" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S868" s="49"/>
       <c r="T868" s="49"/>
       <c r="U868" s="49"/>
       <c r="V868" s="49"/>
     </row>
-    <row r="869" spans="19:22">
+    <row r="869" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S869" s="49"/>
       <c r="T869" s="49"/>
       <c r="U869" s="49"/>
       <c r="V869" s="49"/>
     </row>
-    <row r="870" spans="19:22">
+    <row r="870" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S870" s="49"/>
       <c r="T870" s="49"/>
       <c r="U870" s="49"/>
       <c r="V870" s="49"/>
     </row>
-    <row r="871" spans="19:22">
+    <row r="871" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S871" s="49"/>
       <c r="T871" s="49"/>
       <c r="U871" s="49"/>
       <c r="V871" s="49"/>
     </row>
-    <row r="872" spans="19:22">
+    <row r="872" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S872" s="49"/>
       <c r="T872" s="49"/>
       <c r="U872" s="49"/>
       <c r="V872" s="49"/>
     </row>
-    <row r="873" spans="19:22">
+    <row r="873" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S873" s="49"/>
       <c r="T873" s="49"/>
       <c r="U873" s="49"/>
       <c r="V873" s="49"/>
     </row>
-    <row r="874" spans="19:22">
+    <row r="874" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S874" s="49"/>
       <c r="T874" s="49"/>
       <c r="U874" s="49"/>
       <c r="V874" s="49"/>
     </row>
-    <row r="875" spans="19:22">
+    <row r="875" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S875" s="49"/>
       <c r="T875" s="49"/>
       <c r="U875" s="49"/>
       <c r="V875" s="49"/>
     </row>
-    <row r="876" spans="19:22">
+    <row r="876" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S876" s="49"/>
       <c r="T876" s="49"/>
       <c r="U876" s="49"/>
       <c r="V876" s="49"/>
     </row>
-    <row r="877" spans="19:22">
+    <row r="877" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S877" s="49"/>
       <c r="T877" s="49"/>
       <c r="U877" s="49"/>
       <c r="V877" s="49"/>
     </row>
-    <row r="878" spans="19:22">
+    <row r="878" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S878" s="49"/>
       <c r="T878" s="49"/>
       <c r="U878" s="49"/>
       <c r="V878" s="49"/>
     </row>
-    <row r="879" spans="19:22">
+    <row r="879" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S879" s="49"/>
       <c r="T879" s="49"/>
       <c r="U879" s="49"/>
       <c r="V879" s="49"/>
     </row>
-    <row r="880" spans="19:22">
+    <row r="880" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S880" s="49"/>
       <c r="T880" s="49"/>
       <c r="U880" s="49"/>
       <c r="V880" s="49"/>
     </row>
-    <row r="881" spans="19:22">
+    <row r="881" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S881" s="49"/>
       <c r="T881" s="49"/>
       <c r="U881" s="49"/>
       <c r="V881" s="49"/>
     </row>
-    <row r="882" spans="19:22">
+    <row r="882" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S882" s="49"/>
       <c r="T882" s="49"/>
       <c r="U882" s="49"/>
       <c r="V882" s="49"/>
     </row>
-    <row r="883" spans="19:22">
+    <row r="883" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S883" s="49"/>
       <c r="T883" s="49"/>
       <c r="U883" s="49"/>
       <c r="V883" s="49"/>
     </row>
-    <row r="884" spans="19:22">
+    <row r="884" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S884" s="49"/>
       <c r="T884" s="49"/>
       <c r="U884" s="49"/>
       <c r="V884" s="49"/>
     </row>
-    <row r="885" spans="19:22">
+    <row r="885" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S885" s="49"/>
       <c r="T885" s="49"/>
       <c r="U885" s="49"/>
       <c r="V885" s="49"/>
     </row>
-    <row r="886" spans="19:22">
+    <row r="886" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S886" s="49"/>
       <c r="T886" s="49"/>
       <c r="U886" s="49"/>
       <c r="V886" s="49"/>
     </row>
-    <row r="887" spans="19:22">
+    <row r="887" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S887" s="49"/>
       <c r="T887" s="49"/>
       <c r="U887" s="49"/>
       <c r="V887" s="49"/>
     </row>
-    <row r="888" spans="19:22">
+    <row r="888" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S888" s="49"/>
       <c r="T888" s="49"/>
       <c r="U888" s="49"/>
       <c r="V888" s="49"/>
     </row>
-    <row r="889" spans="19:22">
+    <row r="889" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S889" s="49"/>
       <c r="T889" s="49"/>
       <c r="U889" s="49"/>
       <c r="V889" s="49"/>
     </row>
-    <row r="890" spans="19:22">
+    <row r="890" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S890" s="49"/>
       <c r="T890" s="49"/>
       <c r="U890" s="49"/>
       <c r="V890" s="49"/>
     </row>
-    <row r="891" spans="19:22">
+    <row r="891" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S891" s="49"/>
       <c r="T891" s="49"/>
       <c r="U891" s="49"/>
       <c r="V891" s="49"/>
     </row>
-    <row r="892" spans="19:22">
+    <row r="892" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S892" s="49"/>
       <c r="T892" s="49"/>
       <c r="U892" s="49"/>
       <c r="V892" s="49"/>
     </row>
-    <row r="893" spans="19:22">
+    <row r="893" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S893" s="49"/>
       <c r="T893" s="49"/>
       <c r="U893" s="49"/>
       <c r="V893" s="49"/>
     </row>
-    <row r="894" spans="19:22">
+    <row r="894" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S894" s="49"/>
       <c r="T894" s="49"/>
       <c r="U894" s="49"/>
       <c r="V894" s="49"/>
     </row>
-    <row r="895" spans="19:22">
+    <row r="895" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S895" s="49"/>
       <c r="T895" s="49"/>
       <c r="U895" s="49"/>
       <c r="V895" s="49"/>
     </row>
-    <row r="896" spans="19:22">
+    <row r="896" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S896" s="49"/>
       <c r="T896" s="49"/>
       <c r="U896" s="49"/>
       <c r="V896" s="49"/>
     </row>
-    <row r="897" spans="19:22">
+    <row r="897" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S897" s="49"/>
       <c r="T897" s="49"/>
       <c r="U897" s="49"/>
       <c r="V897" s="49"/>
     </row>
-    <row r="898" spans="19:22">
+    <row r="898" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S898" s="49"/>
       <c r="T898" s="49"/>
       <c r="U898" s="49"/>
       <c r="V898" s="49"/>
     </row>
-    <row r="899" spans="19:22">
+    <row r="899" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S899" s="49"/>
       <c r="T899" s="49"/>
       <c r="U899" s="49"/>
       <c r="V899" s="49"/>
     </row>
-    <row r="900" spans="19:22">
+    <row r="900" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S900" s="49"/>
       <c r="T900" s="49"/>
       <c r="U900" s="49"/>
       <c r="V900" s="49"/>
     </row>
-    <row r="901" spans="19:22">
+    <row r="901" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S901" s="49"/>
       <c r="T901" s="49"/>
       <c r="U901" s="49"/>
       <c r="V901" s="49"/>
     </row>
-    <row r="902" spans="19:22">
+    <row r="902" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S902" s="49"/>
       <c r="T902" s="49"/>
       <c r="U902" s="49"/>
       <c r="V902" s="49"/>
     </row>
-    <row r="903" spans="19:22">
+    <row r="903" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S903" s="49"/>
       <c r="T903" s="49"/>
       <c r="U903" s="49"/>
       <c r="V903" s="49"/>
     </row>
-    <row r="904" spans="19:22">
+    <row r="904" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S904" s="49"/>
       <c r="T904" s="49"/>
       <c r="U904" s="49"/>
       <c r="V904" s="49"/>
     </row>
-    <row r="905" spans="19:22">
+    <row r="905" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S905" s="49"/>
       <c r="T905" s="49"/>
       <c r="U905" s="49"/>
       <c r="V905" s="49"/>
     </row>
-    <row r="906" spans="19:22">
+    <row r="906" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S906" s="49"/>
       <c r="T906" s="49"/>
       <c r="U906" s="49"/>
       <c r="V906" s="49"/>
     </row>
-    <row r="907" spans="19:22">
+    <row r="907" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S907" s="49"/>
       <c r="T907" s="49"/>
       <c r="U907" s="49"/>
       <c r="V907" s="49"/>
     </row>
-    <row r="908" spans="19:22">
+    <row r="908" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S908" s="49"/>
       <c r="T908" s="49"/>
       <c r="U908" s="49"/>
       <c r="V908" s="49"/>
     </row>
-    <row r="909" spans="19:22">
+    <row r="909" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S909" s="49"/>
       <c r="T909" s="49"/>
       <c r="U909" s="49"/>
       <c r="V909" s="49"/>
     </row>
-    <row r="910" spans="19:22">
+    <row r="910" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S910" s="49"/>
       <c r="T910" s="49"/>
       <c r="U910" s="49"/>
       <c r="V910" s="49"/>
     </row>
-    <row r="911" spans="19:22">
+    <row r="911" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S911" s="49"/>
       <c r="T911" s="49"/>
       <c r="U911" s="49"/>
       <c r="V911" s="49"/>
     </row>
-    <row r="912" spans="19:22">
+    <row r="912" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S912" s="49"/>
       <c r="T912" s="49"/>
       <c r="U912" s="49"/>
       <c r="V912" s="49"/>
     </row>
-    <row r="913" spans="19:22">
+    <row r="913" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S913" s="49"/>
       <c r="T913" s="49"/>
       <c r="U913" s="49"/>
       <c r="V913" s="49"/>
     </row>
-    <row r="914" spans="19:22">
+    <row r="914" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S914" s="49"/>
       <c r="T914" s="49"/>
       <c r="U914" s="49"/>
       <c r="V914" s="49"/>
     </row>
-    <row r="915" spans="19:22">
+    <row r="915" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S915" s="49"/>
       <c r="T915" s="49"/>
       <c r="U915" s="49"/>
       <c r="V915" s="49"/>
     </row>
-    <row r="916" spans="19:22">
+    <row r="916" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S916" s="49"/>
       <c r="T916" s="49"/>
       <c r="U916" s="49"/>
       <c r="V916" s="49"/>
     </row>
-    <row r="917" spans="19:22">
+    <row r="917" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S917" s="49"/>
       <c r="T917" s="49"/>
       <c r="U917" s="49"/>
       <c r="V917" s="49"/>
     </row>
-    <row r="918" spans="19:22">
+    <row r="918" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S918" s="49"/>
       <c r="T918" s="49"/>
       <c r="U918" s="49"/>
       <c r="V918" s="49"/>
     </row>
-    <row r="919" spans="19:22">
+    <row r="919" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S919" s="49"/>
       <c r="T919" s="49"/>
       <c r="U919" s="49"/>
       <c r="V919" s="49"/>
     </row>
-    <row r="920" spans="19:22">
+    <row r="920" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S920" s="49"/>
       <c r="T920" s="49"/>
       <c r="U920" s="49"/>
       <c r="V920" s="49"/>
     </row>
-    <row r="921" spans="19:22">
+    <row r="921" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S921" s="49"/>
       <c r="T921" s="49"/>
       <c r="U921" s="49"/>
       <c r="V921" s="49"/>
     </row>
-    <row r="922" spans="19:22">
+    <row r="922" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S922" s="49"/>
       <c r="T922" s="49"/>
       <c r="U922" s="49"/>
       <c r="V922" s="49"/>
     </row>
-    <row r="923" spans="19:22">
+    <row r="923" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S923" s="49"/>
       <c r="T923" s="49"/>
       <c r="U923" s="49"/>
       <c r="V923" s="49"/>
     </row>
-    <row r="924" spans="19:22">
+    <row r="924" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S924" s="49"/>
       <c r="T924" s="49"/>
       <c r="U924" s="49"/>
       <c r="V924" s="49"/>
     </row>
-    <row r="925" spans="19:22">
+    <row r="925" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S925" s="49"/>
       <c r="T925" s="49"/>
       <c r="U925" s="49"/>
       <c r="V925" s="49"/>
     </row>
-    <row r="926" spans="19:22">
+    <row r="926" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S926" s="49"/>
       <c r="T926" s="49"/>
       <c r="U926" s="49"/>
       <c r="V926" s="49"/>
     </row>
-    <row r="927" spans="19:22">
+    <row r="927" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S927" s="49"/>
       <c r="T927" s="49"/>
       <c r="U927" s="49"/>
       <c r="V927" s="49"/>
     </row>
-    <row r="928" spans="19:22">
+    <row r="928" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S928" s="49"/>
       <c r="T928" s="49"/>
       <c r="U928" s="49"/>
       <c r="V928" s="49"/>
     </row>
-    <row r="929" spans="19:22">
+    <row r="929" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S929" s="49"/>
       <c r="T929" s="49"/>
       <c r="U929" s="49"/>
       <c r="V929" s="49"/>
     </row>
-    <row r="930" spans="19:22">
+    <row r="930" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S930" s="49"/>
       <c r="T930" s="49"/>
       <c r="U930" s="49"/>
       <c r="V930" s="49"/>
     </row>
-    <row r="931" spans="19:22">
+    <row r="931" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S931" s="49"/>
       <c r="T931" s="49"/>
       <c r="U931" s="49"/>
       <c r="V931" s="49"/>
     </row>
-    <row r="932" spans="19:22">
+    <row r="932" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S932" s="49"/>
       <c r="T932" s="49"/>
       <c r="U932" s="49"/>
       <c r="V932" s="49"/>
     </row>
-    <row r="933" spans="19:22">
+    <row r="933" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S933" s="49"/>
       <c r="T933" s="49"/>
       <c r="U933" s="49"/>
       <c r="V933" s="49"/>
     </row>
-    <row r="934" spans="19:22">
+    <row r="934" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S934" s="49"/>
       <c r="T934" s="49"/>
       <c r="U934" s="49"/>
       <c r="V934" s="49"/>
     </row>
-    <row r="935" spans="19:22">
+    <row r="935" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S935" s="49"/>
       <c r="T935" s="49"/>
       <c r="U935" s="49"/>
       <c r="V935" s="49"/>
     </row>
-    <row r="936" spans="19:22">
+    <row r="936" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S936" s="49"/>
       <c r="T936" s="49"/>
       <c r="U936" s="49"/>
       <c r="V936" s="49"/>
     </row>
-    <row r="937" spans="19:22">
+    <row r="937" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S937" s="49"/>
       <c r="T937" s="49"/>
       <c r="U937" s="49"/>
       <c r="V937" s="49"/>
     </row>
-    <row r="938" spans="19:22">
+    <row r="938" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S938" s="49"/>
       <c r="T938" s="49"/>
       <c r="U938" s="49"/>
       <c r="V938" s="49"/>
     </row>
-    <row r="939" spans="19:22">
+    <row r="939" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S939" s="49"/>
       <c r="T939" s="49"/>
       <c r="U939" s="49"/>
       <c r="V939" s="49"/>
     </row>
-    <row r="940" spans="19:22">
+    <row r="940" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S940" s="49"/>
       <c r="T940" s="49"/>
       <c r="U940" s="49"/>
       <c r="V940" s="49"/>
     </row>
-    <row r="941" spans="19:22">
+    <row r="941" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S941" s="49"/>
       <c r="T941" s="49"/>
       <c r="U941" s="49"/>
       <c r="V941" s="49"/>
     </row>
-    <row r="942" spans="19:22">
+    <row r="942" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S942" s="49"/>
       <c r="T942" s="49"/>
       <c r="U942" s="49"/>
       <c r="V942" s="49"/>
     </row>
-    <row r="943" spans="19:22">
+    <row r="943" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S943" s="49"/>
       <c r="T943" s="49"/>
       <c r="U943" s="49"/>
       <c r="V943" s="49"/>
     </row>
-    <row r="944" spans="19:22">
+    <row r="944" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S944" s="49"/>
       <c r="T944" s="49"/>
       <c r="U944" s="49"/>
       <c r="V944" s="49"/>
     </row>
-    <row r="945" spans="19:22">
+    <row r="945" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S945" s="49"/>
       <c r="T945" s="49"/>
       <c r="U945" s="49"/>
       <c r="V945" s="49"/>
     </row>
-    <row r="946" spans="19:22">
+    <row r="946" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S946" s="49"/>
       <c r="T946" s="49"/>
       <c r="U946" s="49"/>
       <c r="V946" s="49"/>
     </row>
-    <row r="947" spans="19:22">
+    <row r="947" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S947" s="49"/>
       <c r="T947" s="49"/>
       <c r="U947" s="49"/>
       <c r="V947" s="49"/>
     </row>
-    <row r="948" spans="19:22">
+    <row r="948" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S948" s="49"/>
       <c r="T948" s="49"/>
       <c r="U948" s="49"/>
       <c r="V948" s="49"/>
     </row>
-    <row r="949" spans="19:22">
+    <row r="949" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S949" s="49"/>
       <c r="T949" s="49"/>
       <c r="U949" s="49"/>
       <c r="V949" s="49"/>
     </row>
-    <row r="950" spans="19:22">
+    <row r="950" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S950" s="49"/>
       <c r="T950" s="49"/>
       <c r="U950" s="49"/>
       <c r="V950" s="49"/>
     </row>
-    <row r="951" spans="19:22">
+    <row r="951" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S951" s="49"/>
       <c r="T951" s="49"/>
       <c r="U951" s="49"/>
       <c r="V951" s="49"/>
     </row>
-    <row r="952" spans="19:22">
+    <row r="952" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S952" s="49"/>
       <c r="T952" s="49"/>
       <c r="U952" s="49"/>
       <c r="V952" s="49"/>
     </row>
-    <row r="953" spans="19:22">
+    <row r="953" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S953" s="49"/>
       <c r="T953" s="49"/>
       <c r="U953" s="49"/>
       <c r="V953" s="49"/>
     </row>
-    <row r="954" spans="19:22">
+    <row r="954" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S954" s="49"/>
       <c r="T954" s="49"/>
       <c r="U954" s="49"/>
       <c r="V954" s="49"/>
     </row>
-    <row r="955" spans="19:22">
+    <row r="955" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S955" s="49"/>
       <c r="T955" s="49"/>
       <c r="U955" s="49"/>
       <c r="V955" s="49"/>
     </row>
-    <row r="956" spans="19:22">
+    <row r="956" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S956" s="49"/>
       <c r="T956" s="49"/>
       <c r="U956" s="49"/>
       <c r="V956" s="49"/>
     </row>
-    <row r="957" spans="19:22">
+    <row r="957" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S957" s="49"/>
       <c r="T957" s="49"/>
       <c r="U957" s="49"/>
       <c r="V957" s="49"/>
     </row>
-    <row r="958" spans="19:22">
+    <row r="958" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S958" s="49"/>
       <c r="T958" s="49"/>
       <c r="U958" s="49"/>
       <c r="V958" s="49"/>
     </row>
-    <row r="959" spans="19:22">
+    <row r="959" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S959" s="49"/>
       <c r="T959" s="49"/>
       <c r="U959" s="49"/>
       <c r="V959" s="49"/>
     </row>
-    <row r="960" spans="19:22">
+    <row r="960" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S960" s="49"/>
       <c r="T960" s="49"/>
       <c r="U960" s="49"/>
       <c r="V960" s="49"/>
     </row>
-    <row r="961" spans="19:22">
+    <row r="961" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S961" s="49"/>
       <c r="T961" s="49"/>
       <c r="U961" s="49"/>
       <c r="V961" s="49"/>
     </row>
-    <row r="962" spans="19:22">
+    <row r="962" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S962" s="49"/>
       <c r="T962" s="49"/>
       <c r="U962" s="49"/>
       <c r="V962" s="49"/>
     </row>
-    <row r="963" spans="19:22">
+    <row r="963" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S963" s="49"/>
       <c r="T963" s="49"/>
       <c r="U963" s="49"/>
       <c r="V963" s="49"/>
     </row>
-    <row r="964" spans="19:22">
+    <row r="964" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S964" s="49"/>
       <c r="T964" s="49"/>
       <c r="U964" s="49"/>
       <c r="V964" s="49"/>
     </row>
-    <row r="965" spans="19:22">
+    <row r="965" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S965" s="49"/>
       <c r="T965" s="49"/>
       <c r="U965" s="49"/>
       <c r="V965" s="49"/>
     </row>
-    <row r="966" spans="19:22">
+    <row r="966" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S966" s="49"/>
       <c r="T966" s="49"/>
       <c r="U966" s="49"/>
       <c r="V966" s="49"/>
     </row>
-    <row r="967" spans="19:22">
+    <row r="967" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S967" s="49"/>
       <c r="T967" s="49"/>
       <c r="U967" s="49"/>
       <c r="V967" s="49"/>
     </row>
-    <row r="968" spans="19:22">
+    <row r="968" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S968" s="49"/>
       <c r="T968" s="49"/>
       <c r="U968" s="49"/>
       <c r="V968" s="49"/>
     </row>
-    <row r="969" spans="19:22">
+    <row r="969" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S969" s="49"/>
       <c r="T969" s="49"/>
       <c r="U969" s="49"/>
       <c r="V969" s="49"/>
     </row>
-    <row r="970" spans="19:22">
+    <row r="970" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S970" s="49"/>
       <c r="T970" s="49"/>
       <c r="U970" s="49"/>
       <c r="V970" s="49"/>
     </row>
-    <row r="971" spans="19:22">
+    <row r="971" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S971" s="49"/>
       <c r="T971" s="49"/>
       <c r="U971" s="49"/>
       <c r="V971" s="49"/>
     </row>
-    <row r="972" spans="19:22">
+    <row r="972" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S972" s="49"/>
       <c r="T972" s="49"/>
       <c r="U972" s="49"/>
       <c r="V972" s="49"/>
     </row>
-    <row r="973" spans="19:22">
+    <row r="973" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S973" s="49"/>
       <c r="T973" s="49"/>
       <c r="U973" s="49"/>
       <c r="V973" s="49"/>
     </row>
-    <row r="974" spans="19:22">
+    <row r="974" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S974" s="49"/>
       <c r="T974" s="49"/>
       <c r="U974" s="49"/>
       <c r="V974" s="49"/>
     </row>
-    <row r="975" spans="19:22">
+    <row r="975" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S975" s="49"/>
       <c r="T975" s="49"/>
       <c r="U975" s="49"/>
       <c r="V975" s="49"/>
     </row>
-    <row r="976" spans="19:22">
+    <row r="976" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S976" s="49"/>
       <c r="T976" s="49"/>
       <c r="U976" s="49"/>
       <c r="V976" s="49"/>
     </row>
-    <row r="977" spans="19:22">
+    <row r="977" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S977" s="49"/>
       <c r="T977" s="49"/>
       <c r="U977" s="49"/>
       <c r="V977" s="49"/>
     </row>
-    <row r="978" spans="19:22">
+    <row r="978" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S978" s="49"/>
       <c r="T978" s="49"/>
       <c r="U978" s="49"/>
       <c r="V978" s="49"/>
     </row>
-    <row r="979" spans="19:22">
+    <row r="979" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S979" s="49"/>
       <c r="T979" s="49"/>
       <c r="U979" s="49"/>
       <c r="V979" s="49"/>
     </row>
-    <row r="980" spans="19:22">
+    <row r="980" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S980" s="49"/>
       <c r="T980" s="49"/>
       <c r="U980" s="49"/>
       <c r="V980" s="49"/>
     </row>
-    <row r="981" spans="19:22">
+    <row r="981" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S981" s="49"/>
       <c r="T981" s="49"/>
       <c r="U981" s="49"/>
       <c r="V981" s="49"/>
     </row>
-    <row r="982" spans="19:22">
+    <row r="982" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S982" s="49"/>
       <c r="T982" s="49"/>
       <c r="U982" s="49"/>
       <c r="V982" s="49"/>
     </row>
-    <row r="983" spans="19:22">
+    <row r="983" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S983" s="49"/>
       <c r="T983" s="49"/>
       <c r="U983" s="49"/>
       <c r="V983" s="49"/>
     </row>
-    <row r="984" spans="19:22">
+    <row r="984" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S984" s="49"/>
       <c r="T984" s="49"/>
       <c r="U984" s="49"/>
       <c r="V984" s="49"/>
     </row>
-    <row r="985" spans="19:22">
+    <row r="985" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S985" s="49"/>
       <c r="T985" s="49"/>
       <c r="U985" s="49"/>
       <c r="V985" s="49"/>
     </row>
-    <row r="986" spans="19:22">
+    <row r="986" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S986" s="49"/>
       <c r="T986" s="49"/>
       <c r="U986" s="49"/>
       <c r="V986" s="49"/>
     </row>
-    <row r="987" spans="19:22">
+    <row r="987" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S987" s="49"/>
       <c r="T987" s="49"/>
       <c r="U987" s="49"/>
       <c r="V987" s="49"/>
     </row>
-    <row r="988" spans="19:22">
+    <row r="988" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S988" s="49"/>
       <c r="T988" s="49"/>
       <c r="U988" s="49"/>
       <c r="V988" s="49"/>
     </row>
-    <row r="989" spans="19:22">
+    <row r="989" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S989" s="49"/>
       <c r="T989" s="49"/>
       <c r="U989" s="49"/>
       <c r="V989" s="49"/>
     </row>
-    <row r="990" spans="19:22">
+    <row r="990" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S990" s="49"/>
       <c r="T990" s="49"/>
       <c r="U990" s="49"/>
       <c r="V990" s="49"/>
     </row>
-    <row r="991" spans="19:22">
+    <row r="991" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S991" s="49"/>
       <c r="T991" s="49"/>
       <c r="U991" s="49"/>
       <c r="V991" s="49"/>
     </row>
-    <row r="992" spans="19:22">
+    <row r="992" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S992" s="49"/>
       <c r="T992" s="49"/>
       <c r="U992" s="49"/>
       <c r="V992" s="49"/>
     </row>
-    <row r="993" spans="19:22">
+    <row r="993" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S993" s="49"/>
       <c r="T993" s="49"/>
       <c r="U993" s="49"/>
       <c r="V993" s="49"/>
     </row>
-    <row r="994" spans="19:22">
+    <row r="994" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S994" s="49"/>
       <c r="T994" s="49"/>
       <c r="U994" s="49"/>
       <c r="V994" s="49"/>
     </row>
-    <row r="995" spans="19:22">
+    <row r="995" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S995" s="49"/>
       <c r="T995" s="49"/>
       <c r="U995" s="49"/>
       <c r="V995" s="49"/>
     </row>
-    <row r="996" spans="19:22">
+    <row r="996" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S996" s="49"/>
       <c r="T996" s="49"/>
       <c r="U996" s="49"/>
       <c r="V996" s="49"/>
     </row>
-    <row r="997" spans="19:22">
+    <row r="997" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S997" s="49"/>
       <c r="T997" s="49"/>
       <c r="U997" s="49"/>
       <c r="V997" s="49"/>
     </row>
-    <row r="998" spans="19:22">
+    <row r="998" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S998" s="49"/>
       <c r="T998" s="49"/>
       <c r="U998" s="49"/>
       <c r="V998" s="49"/>
     </row>
-    <row r="999" spans="19:22">
+    <row r="999" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S999" s="49"/>
       <c r="T999" s="49"/>
       <c r="U999" s="49"/>
       <c r="V999" s="49"/>
     </row>
-    <row r="1000" spans="19:22">
+    <row r="1000" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1000" s="49"/>
       <c r="T1000" s="49"/>
       <c r="U1000" s="49"/>
       <c r="V1000" s="49"/>
     </row>
-    <row r="1001" spans="19:22">
+    <row r="1001" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1001" s="49"/>
       <c r="T1001" s="49"/>
       <c r="U1001" s="49"/>
       <c r="V1001" s="49"/>
     </row>
-    <row r="1002" spans="19:22">
+    <row r="1002" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1002" s="49"/>
       <c r="T1002" s="49"/>
       <c r="U1002" s="49"/>
       <c r="V1002" s="49"/>
     </row>
-    <row r="1003" spans="19:22">
+    <row r="1003" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1003" s="49"/>
       <c r="T1003" s="49"/>
       <c r="U1003" s="49"/>
       <c r="V1003" s="49"/>
     </row>
-    <row r="1004" spans="19:22">
+    <row r="1004" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1004" s="49"/>
       <c r="T1004" s="49"/>
       <c r="U1004" s="49"/>
       <c r="V1004" s="49"/>
     </row>
-    <row r="1005" spans="19:22">
+    <row r="1005" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1005" s="49"/>
       <c r="T1005" s="49"/>
       <c r="U1005" s="49"/>
       <c r="V1005" s="49"/>
     </row>
-    <row r="1006" spans="19:22">
+    <row r="1006" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1006" s="49"/>
       <c r="T1006" s="49"/>
       <c r="U1006" s="49"/>
       <c r="V1006" s="49"/>
     </row>
-    <row r="1007" spans="19:22">
+    <row r="1007" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1007" s="49"/>
       <c r="T1007" s="49"/>
       <c r="U1007" s="49"/>
       <c r="V1007" s="49"/>
     </row>
-    <row r="1008" spans="19:22">
+    <row r="1008" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1008" s="49"/>
       <c r="T1008" s="49"/>
       <c r="U1008" s="49"/>
       <c r="V1008" s="49"/>
     </row>
-    <row r="1009" spans="19:22">
+    <row r="1009" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1009" s="49"/>
       <c r="T1009" s="49"/>
       <c r="U1009" s="49"/>
       <c r="V1009" s="49"/>
     </row>
-    <row r="1010" spans="19:22">
+    <row r="1010" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1010" s="49"/>
       <c r="T1010" s="49"/>
       <c r="U1010" s="49"/>
       <c r="V1010" s="49"/>
     </row>
-    <row r="1011" spans="19:22">
+    <row r="1011" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1011" s="49"/>
       <c r="T1011" s="49"/>
       <c r="U1011" s="49"/>
       <c r="V1011" s="49"/>
     </row>
-    <row r="1012" spans="19:22">
+    <row r="1012" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1012" s="49"/>
       <c r="T1012" s="49"/>
       <c r="U1012" s="49"/>
       <c r="V1012" s="49"/>
     </row>
-    <row r="1013" spans="19:22">
+    <row r="1013" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1013" s="49"/>
       <c r="T1013" s="49"/>
       <c r="U1013" s="49"/>
       <c r="V1013" s="49"/>
     </row>
-    <row r="1014" spans="19:22">
+    <row r="1014" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1014" s="49"/>
       <c r="T1014" s="49"/>
       <c r="U1014" s="49"/>
       <c r="V1014" s="49"/>
     </row>
-    <row r="1015" spans="19:22">
+    <row r="1015" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1015" s="49"/>
       <c r="T1015" s="49"/>
       <c r="U1015" s="49"/>
       <c r="V1015" s="49"/>
     </row>
-    <row r="1016" spans="19:22">
+    <row r="1016" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1016" s="49"/>
       <c r="T1016" s="49"/>
       <c r="U1016" s="49"/>
       <c r="V1016" s="49"/>
     </row>
-    <row r="1017" spans="19:22">
+    <row r="1017" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1017" s="49"/>
       <c r="T1017" s="49"/>
       <c r="U1017" s="49"/>
       <c r="V1017" s="49"/>
     </row>
-    <row r="1018" spans="19:22">
+    <row r="1018" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1018" s="49"/>
       <c r="T1018" s="49"/>
       <c r="U1018" s="49"/>
       <c r="V1018" s="49"/>
     </row>
-    <row r="1019" spans="19:22">
+    <row r="1019" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1019" s="49"/>
       <c r="T1019" s="49"/>
       <c r="U1019" s="49"/>
       <c r="V1019" s="49"/>
     </row>
-    <row r="1020" spans="19:22">
+    <row r="1020" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1020" s="49"/>
       <c r="T1020" s="49"/>
       <c r="U1020" s="49"/>
       <c r="V1020" s="49"/>
     </row>
-    <row r="1021" spans="19:22">
+    <row r="1021" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1021" s="49"/>
       <c r="T1021" s="49"/>
       <c r="U1021" s="49"/>
       <c r="V1021" s="49"/>
     </row>
-    <row r="1022" spans="19:22">
+    <row r="1022" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1022" s="49"/>
       <c r="T1022" s="49"/>
       <c r="U1022" s="49"/>
       <c r="V1022" s="49"/>
     </row>
-    <row r="1023" spans="19:22">
+    <row r="1023" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1023" s="49"/>
       <c r="T1023" s="49"/>
       <c r="U1023" s="49"/>
       <c r="V1023" s="49"/>
     </row>
-    <row r="1024" spans="19:22">
+    <row r="1024" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1024" s="49"/>
       <c r="T1024" s="49"/>
       <c r="U1024" s="49"/>
       <c r="V1024" s="49"/>
     </row>
-    <row r="1025" spans="19:22">
+    <row r="1025" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1025" s="49"/>
       <c r="T1025" s="49"/>
       <c r="U1025" s="49"/>
       <c r="V1025" s="49"/>
     </row>
-    <row r="1026" spans="19:22">
+    <row r="1026" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1026" s="49"/>
       <c r="T1026" s="49"/>
       <c r="U1026" s="49"/>
       <c r="V1026" s="49"/>
     </row>
-    <row r="1027" spans="19:22">
+    <row r="1027" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1027" s="49"/>
       <c r="T1027" s="49"/>
       <c r="U1027" s="49"/>
       <c r="V1027" s="49"/>
     </row>
-    <row r="1028" spans="19:22">
+    <row r="1028" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1028" s="49"/>
       <c r="T1028" s="49"/>
       <c r="U1028" s="49"/>
       <c r="V1028" s="49"/>
     </row>
-    <row r="1029" spans="19:22">
+    <row r="1029" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1029" s="49"/>
       <c r="T1029" s="49"/>
       <c r="U1029" s="49"/>
       <c r="V1029" s="49"/>
     </row>
-    <row r="1030" spans="19:22">
+    <row r="1030" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1030" s="49"/>
       <c r="T1030" s="49"/>
       <c r="U1030" s="49"/>
       <c r="V1030" s="49"/>
     </row>
-    <row r="1031" spans="19:22">
+    <row r="1031" spans="19:22" x14ac:dyDescent="0.35">
       <c r="S1031" s="49"/>
       <c r="T1031" s="49"/>
       <c r="U1031" s="49"/>
@@ -13400,9 +13403,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:S3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -13422,7 +13425,7 @@
       <c r="R1" s="5"/>
       <c r="S1" s="5"/>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -13478,7 +13481,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>115</v>
       </c>
@@ -13523,13 +13526,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A2:S3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <dimension ref="A2:S4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" s="59" t="s">
         <v>0</v>
       </c>
@@ -13586,7 +13589,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="61" t="s">
         <v>165</v>
       </c>
@@ -13623,6 +13626,31 @@
         <v>0</v>
       </c>
     </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="D4">
+        <v>1250</v>
+      </c>
+      <c r="N4">
+        <v>420</v>
+      </c>
+      <c r="R4" s="61">
+        <f>SUM(F4:Q4)</f>
+        <v>420</v>
+      </c>
+      <c r="S4" s="61">
+        <f>D4-R4</f>
+        <v>830</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
